--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="13065"/>
+    <workbookView windowWidth="19200" windowHeight="7665"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="68">
   <si>
     <t>编号</t>
   </si>
@@ -197,6 +197,30 @@
   </si>
   <si>
     <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯+动态规划</t>
+  </si>
+  <si>
+    <t>动态规划/记忆化搜索降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>动态规划/记忆化搜索</t>
   </si>
 </sst>
 </file>
@@ -204,8 +228,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -230,13 +254,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -245,6 +262,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -253,37 +321,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,8 +359,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,39 +376,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -359,20 +391,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -401,25 +425,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,151 +587,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,6 +628,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -615,15 +666,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,11 +685,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,15 +717,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -686,21 +725,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,149 +733,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,6 +916,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1242,16 +1269,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="5.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="4" customWidth="1"/>
     <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="37" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
     <col min="9" max="16383" width="18.625" style="4" customWidth="1"/>
     <col min="16384" max="16384" width="18.625" style="4"/>
   </cols>
@@ -1739,14 +1766,30 @@
       <c r="H26" s="11"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="A27" s="5">
+        <v>232</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5"/>
@@ -1789,30 +1832,14 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="5">
-        <v>232</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="5">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="5"/>
@@ -1836,13 +1863,105 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="5">
+        <v>131</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="5">
+        <v>132</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H7">
@@ -1863,7 +1982,8 @@
     <hyperlink ref="B21" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
     <hyperlink ref="B25" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B26" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B32" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B27" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7665"/>
+    <workbookView windowWidth="27870" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>编号</t>
   </si>
@@ -205,7 +205,7 @@
     <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
   </si>
   <si>
-    <t>回溯+动态规划</t>
+    <t>回文数、回溯、动态规划</t>
   </si>
   <si>
     <t>动态规划/记忆化搜索降低判断回文数的复杂度</t>
@@ -220,7 +220,22 @@
     <t>困难</t>
   </si>
   <si>
+    <t>回文数、动态规划</t>
+  </si>
+  <si>
     <t>动态规划/记忆化搜索</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>回文数、字符串操作</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
   </si>
 </sst>
 </file>
@@ -228,10 +243,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -252,6 +267,120 @@
       <color rgb="FF262626"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -270,135 +399,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,181 +440,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,6 +655,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -637,20 +679,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -670,17 +709,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,28 +735,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -733,10 +760,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -745,16 +772,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -763,119 +790,119 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -888,6 +915,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -918,7 +948,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1269,702 +1305,728 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="4" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
-    <col min="9" max="16383" width="18.625" style="4" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="4"/>
+    <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
+    <col min="9" max="16383" width="18.625" style="5" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1052</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>832</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>824</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>543</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>867</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>868</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <v>303</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>1</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
-      <c r="A11" s="7">
+      <c r="A11" s="8">
         <v>304</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>1</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:8">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>102</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="10">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:8">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>103</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="10">
         <v>1</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:8">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>104</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="10">
         <v>1</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>338</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="6">
         <v>1</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:8">
-      <c r="A26" s="11">
+      <c r="A26" s="12">
         <v>26</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="12">
         <v>1</v>
       </c>
-      <c r="H26" s="11"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>232</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="6">
         <v>1</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="5">
+      <c r="A38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" s="4" customFormat="1" spans="1:8">
+      <c r="A39" s="15">
         <v>131</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="15">
         <v>1</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5">
+    <row r="40" s="4" customFormat="1" spans="1:8">
+      <c r="A40" s="15">
         <v>132</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="E40" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="15">
         <v>1</v>
       </c>
-      <c r="H40" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="H40" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" s="4" customFormat="1" spans="1:8">
+      <c r="A41" s="15">
+        <v>125</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="15">
+        <v>1</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7">
+  <autoFilter ref="A1:H11">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -1984,6 +2046,7 @@
     <hyperlink ref="B26" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
     <hyperlink ref="B27" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B41" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -232,7 +232,7 @@
     <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
   </si>
   <si>
-    <t>回文数、字符串操作</t>
+    <t>回文数、字符串</t>
   </si>
   <si>
     <t>字符串操作</t>
@@ -243,10 +243,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -267,13 +267,6 @@
       <color rgb="FF262626"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -291,6 +284,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -307,7 +321,85 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,100 +412,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,7 +446,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,79 +500,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,91 +596,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,23 +667,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,6 +708,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -735,20 +732,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,10 +754,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -772,133 +766,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -954,7 +948,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2009,7 +2003,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>72</v>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="13065"/>
+    <workbookView windowWidth="19200" windowHeight="7665"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
   <si>
     <t>编号</t>
   </si>
@@ -232,10 +232,19 @@
     <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
   </si>
   <si>
-    <t>回文数、字符串</t>
-  </si>
-  <si>
     <t>字符串操作</t>
+  </si>
+  <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>数据结构</t>
   </si>
 </sst>
 </file>
@@ -248,7 +257,7 @@
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +278,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,12 +300,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -298,8 +336,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,8 +373,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,14 +420,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -350,70 +427,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +461,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -458,25 +551,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +593,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,37 +611,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,79 +635,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,24 +685,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -712,7 +715,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -732,17 +750,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,10 +775,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -766,7 +787,7 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -775,149 +796,152 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -936,10 +960,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -948,8 +972,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1299,725 +1329,751 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
-    <col min="9" max="16383" width="18.625" style="5" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="5"/>
+    <col min="1" max="1" width="5.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="6" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="6" customWidth="1"/>
+    <col min="9" max="16383" width="18.625" style="6" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>1052</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="7">
         <v>1</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>832</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>824</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>543</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>867</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>1</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>868</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>1</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <v>303</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <v>304</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="9">
         <v>1</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:8">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <v>102</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <v>1</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:8">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <v>103</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <v>1</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:8">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <v>104</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <v>1</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="6">
+      <c r="A25" s="7">
         <v>338</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="7">
         <v>1</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:8">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>26</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="13">
         <v>1</v>
       </c>
-      <c r="H26" s="12"/>
+      <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="6">
+      <c r="A27" s="7">
         <v>232</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="7">
         <v>1</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:8">
-      <c r="A39" s="15">
+      <c r="A39" s="16">
         <v>131</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="16">
         <v>1</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H39" s="16" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:8">
-      <c r="A40" s="15">
+      <c r="A40" s="16">
         <v>132</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="16">
         <v>1</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H40" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="1" spans="1:8">
-      <c r="A41" s="15">
+    <row r="41" s="5" customFormat="1" spans="1:8">
+      <c r="A41" s="18">
         <v>125</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="18">
+        <v>2</v>
+      </c>
+      <c r="H41" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F41" s="15" t="s">
+    </row>
+    <row r="42" s="5" customFormat="1" spans="1:8">
+      <c r="A42" s="18">
+        <v>1047</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="15">
-        <v>2</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
+      <c r="G42" s="18">
+        <v>1</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H11">
@@ -2041,6 +2097,7 @@
     <hyperlink ref="B27" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B41" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B42" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t>编号</t>
   </si>
@@ -245,6 +245,18 @@
   </si>
   <si>
     <t>数据结构</t>
+  </si>
+  <si>
+    <t>旋转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>链表</t>
+  </si>
+  <si>
+    <t>循环链表</t>
   </si>
 </sst>
 </file>
@@ -253,8 +265,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
@@ -291,6 +303,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -299,8 +318,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,13 +344,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,6 +357,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -337,7 +388,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -345,7 +396,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,16 +409,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,54 +433,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,7 +479,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,7 +509,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,49 +581,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,103 +647,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -685,17 +691,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -707,6 +707,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,6 +744,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -749,24 +773,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -775,10 +781,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -787,137 +793,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -939,47 +945,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1344,736 +1329,554 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1052</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>1</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>832</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>1</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>824</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>543</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>1</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>867</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>868</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>1</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="9">
+      <c r="A10" s="1">
         <v>303</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
-      <c r="A11" s="9">
+      <c r="A11" s="1">
         <v>304</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
     <row r="19" s="2" customFormat="1" spans="1:8">
-      <c r="A19" s="11">
+      <c r="A19" s="2">
         <v>102</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="2">
         <v>1</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:8">
-      <c r="A20" s="11">
+      <c r="A20" s="2">
         <v>103</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="2">
         <v>1</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:8">
-      <c r="A21" s="11">
+      <c r="A21" s="2">
         <v>104</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="2">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>338</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="6">
         <v>1</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:8">
-      <c r="A26" s="13">
+    <row r="26" s="3" customFormat="1" spans="1:7">
+      <c r="A26" s="3">
         <v>26</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="3">
         <v>1</v>
       </c>
-      <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>232</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>1</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="7"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="7"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="7"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="7"/>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="7"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="7"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="7"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="7"/>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:8">
-      <c r="A39" s="16">
+      <c r="A39" s="4">
         <v>131</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="4">
         <v>1</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:8">
-      <c r="A40" s="16">
+      <c r="A40" s="4">
         <v>132</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="4">
         <v>1</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="41" s="5" customFormat="1" spans="1:8">
-      <c r="A41" s="18">
+      <c r="A41" s="5">
         <v>125</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="5">
         <v>2</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" s="5" customFormat="1" spans="1:8">
-      <c r="A42" s="18">
+      <c r="A42" s="5">
         <v>1047</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="5">
         <v>1</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
+    <row r="43" s="5" customFormat="1" spans="1:8">
+      <c r="A43" s="5">
+        <v>61</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="5">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H11">
@@ -2098,6 +1901,7 @@
     <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B41" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
     <hyperlink ref="B42" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B43" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7665"/>
+    <workbookView windowWidth="27870" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,10 +205,10 @@
     <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
   </si>
   <si>
-    <t>回文数、回溯、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划/记忆化搜索降低判断回文数的复杂度</t>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
   </si>
   <si>
     <t>分割回文串 II</t>
@@ -223,7 +223,7 @@
     <t>回文数、动态规划</t>
   </si>
   <si>
-    <t>动态规划/记忆化搜索</t>
+    <t>两个动态规划</t>
   </si>
   <si>
     <t>验证回文串</t>
@@ -264,9 +264,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
@@ -297,14 +297,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,6 +364,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -343,66 +418,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -424,21 +439,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="36">
     <fill>
@@ -467,13 +467,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,13 +509,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,19 +527,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -528,126 +648,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,6 +676,56 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -687,44 +737,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -744,32 +756,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -781,10 +781,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -793,133 +793,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -963,7 +963,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1768,113 +1768,113 @@
         <v>12</v>
       </c>
       <c r="G39" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" spans="1:8">
-      <c r="A40" s="4">
+    <row r="40" s="5" customFormat="1" spans="1:8">
+      <c r="A40" s="5">
         <v>132</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="5">
         <v>1</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" s="5" customFormat="1" spans="1:8">
-      <c r="A41" s="5">
+    <row r="41" s="4" customFormat="1" spans="1:8">
+      <c r="A41" s="4">
         <v>125</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="4">
         <v>2</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="42" s="5" customFormat="1" spans="1:8">
-      <c r="A42" s="5">
+    <row r="42" s="4" customFormat="1" spans="1:8">
+      <c r="A42" s="4">
         <v>1047</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="4">
         <v>1</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" s="5" customFormat="1" spans="1:8">
-      <c r="A43" s="5">
+    <row r="43" s="4" customFormat="1" spans="1:8">
+      <c r="A43" s="4">
         <v>61</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="4">
         <v>1</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="4" t="s">
         <v>79</v>
       </c>
     </row>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>编号</t>
   </si>
@@ -218,9 +218,6 @@
   </si>
   <si>
     <t>困难</t>
-  </si>
-  <si>
-    <t>回文数、动态规划</t>
   </si>
   <si>
     <t>两个动态规划</t>
@@ -264,8 +261,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -303,6 +300,80 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +382,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,122 +436,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,7 +470,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,13 +548,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,145 +632,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,10 +669,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -704,24 +693,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -765,6 +741,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -781,149 +772,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -939,9 +930,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -958,9 +946,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1317,196 +1302,196 @@
   <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="6" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="6" customWidth="1"/>
-    <col min="9" max="16383" width="18.625" style="6" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="6"/>
+    <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="25.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
+    <col min="9" max="16383" width="18.625" style="5" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1052</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>1</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>832</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>824</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>543</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>867</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>868</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>1</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1514,7 +1499,7 @@
       <c r="A10" s="1">
         <v>303</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1540,7 +1525,7 @@
       <c r="A11" s="1">
         <v>304</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1566,7 +1551,7 @@
       <c r="A19" s="2">
         <v>102</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1592,7 +1577,7 @@
       <c r="A20" s="2">
         <v>103</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1618,7 +1603,7 @@
       <c r="A21" s="2">
         <v>104</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1641,28 +1626,28 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>338</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>1</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1670,7 +1655,7 @@
       <c r="A26" s="3">
         <v>26</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1690,69 +1675,69 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>232</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>1</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="7"/>
+      <c r="B28" s="6"/>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" s="7"/>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" s="7"/>
+      <c r="B30" s="6"/>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" s="7"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" spans="2:2">
-      <c r="B32" s="7"/>
+      <c r="B32" s="6"/>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="7"/>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="7"/>
+      <c r="B34" s="6"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="7"/>
+      <c r="B35" s="6"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="7"/>
+      <c r="B36" s="6"/>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="7"/>
+      <c r="B37" s="6"/>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="7"/>
+      <c r="B38" s="6"/>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:8">
       <c r="A39" s="4">
         <v>131</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -1774,41 +1759,41 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" s="5" customFormat="1" spans="1:8">
-      <c r="A40" s="5">
+    <row r="40" s="4" customFormat="1" spans="1:8">
+      <c r="A40" s="4">
         <v>132</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="5">
-        <v>1</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="41" s="4" customFormat="1" spans="1:8">
       <c r="A41" s="4">
         <v>125</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>16</v>
@@ -1823,24 +1808,24 @@
         <v>2</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:8">
       <c r="A42" s="4">
         <v>1047</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>12</v>
@@ -1849,24 +1834,24 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:8">
       <c r="A43" s="4">
         <v>61</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>12</v>
@@ -1875,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -261,9 +261,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
@@ -301,14 +301,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,8 +360,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,14 +414,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -374,17 +422,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -397,45 +436,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -476,42 +476,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -524,121 +626,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,11 +667,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -702,6 +708,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -713,6 +728,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -731,39 +764,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -772,145 +772,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1779,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="G40" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>67</v>
@@ -1831,7 +1831,7 @@
         <v>12</v>
       </c>
       <c r="G42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>74</v>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="13065"/>
+    <workbookView windowWidth="19200" windowHeight="7665"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
   <si>
     <t>编号</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>循环链表</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
   </si>
 </sst>
 </file>
@@ -266,7 +275,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,12 +293,6 @@
       <sz val="11"/>
       <color rgb="FF262626"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF262626"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -772,10 +775,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -784,133 +787,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -948,7 +951,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1299,17 +1302,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="25.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="5" customWidth="1"/>
     <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
     <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
     <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
     <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
-    <col min="9" max="16383" width="18.625" style="5" customWidth="1"/>
+    <col min="9" max="32" width="18.625" style="5" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="5" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="5" customWidth="1"/>
     <col min="16384" max="16384" width="18.625" style="5"/>
   </cols>
   <sheetData>
@@ -1521,7 +1526,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" spans="1:8">
       <c r="A11" s="1">
         <v>304</v>
       </c>
@@ -1815,7 +1820,7 @@
       <c r="A42" s="4">
         <v>1047</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -1841,7 +1846,7 @@
       <c r="A43" s="4">
         <v>61</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -1857,10 +1862,36 @@
         <v>12</v>
       </c>
       <c r="G43" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="44" s="4" customFormat="1" spans="1:8">
+      <c r="A44" s="4">
+        <v>227</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1887,6 +1918,7 @@
     <hyperlink ref="B41" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
     <hyperlink ref="B42" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B43" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B44" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
   <si>
     <t>编号</t>
   </si>
@@ -263,6 +263,15 @@
   </si>
   <si>
     <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>递归</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -1892,6 +1901,32 @@
       </c>
       <c r="H44" s="4" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" spans="1:8">
+      <c r="A45" s="4">
+        <v>226</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1919,6 +1954,7 @@
     <hyperlink ref="B42" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B43" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
     <hyperlink ref="B44" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B45" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
   <si>
     <t>编号</t>
   </si>
@@ -193,7 +193,7 @@
     <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
   </si>
   <si>
-    <t>堆栈</t>
+    <t>栈</t>
   </si>
   <si>
     <t>双栈模拟</t>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>栈</t>
   </si>
   <si>
     <t>数据结构</t>
@@ -280,8 +277,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -306,21 +303,105 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,10 +416,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,103 +432,19 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -482,37 +479,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,133 +635,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,17 +676,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -709,26 +700,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -740,24 +711,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -776,6 +729,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -784,10 +781,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -796,133 +793,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -960,7 +957,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1311,7 +1308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -1688,31 +1685,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="5">
-        <v>232</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="5">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>59</v>
-      </c>
+    <row r="27" spans="2:2">
+      <c r="B27" s="6"/>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="6"/>
@@ -1741,27 +1715,73 @@
     <row r="36" spans="2:2">
       <c r="B36" s="6"/>
     </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="6"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="6"/>
+    <row r="37" s="4" customFormat="1" spans="1:8">
+      <c r="A37" s="4">
+        <v>232</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" spans="1:8">
+      <c r="A38" s="4">
+        <v>131</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:8">
       <c r="A39" s="4">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>12</v>
@@ -1770,24 +1790,24 @@
         <v>2</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:8">
       <c r="A40" s="4">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>12</v>
@@ -1796,24 +1816,24 @@
         <v>2</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" s="4" customFormat="1" spans="1:8">
       <c r="A41" s="4">
-        <v>125</v>
+        <v>1047</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>12</v>
@@ -1822,24 +1842,24 @@
         <v>2</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:8">
       <c r="A42" s="4">
-        <v>1047</v>
+        <v>61</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>12</v>
@@ -1848,24 +1868,24 @@
         <v>2</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:8">
       <c r="A43" s="4">
-        <v>61</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>75</v>
+        <v>227</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>12</v>
@@ -1874,24 +1894,24 @@
         <v>2</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:8">
       <c r="A44" s="4">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>12</v>
@@ -1900,33 +1920,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" s="4" customFormat="1" spans="1:8">
-      <c r="A45" s="4">
-        <v>226</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="4">
-        <v>2</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1948,13 +1942,13 @@
     <hyperlink ref="B21" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
     <hyperlink ref="B25" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B26" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B27" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B41" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B42" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
-    <hyperlink ref="B43" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B44" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B45" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B37" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B38" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B40" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B41" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B42" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B43" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B44" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="88">
   <si>
     <t>编号</t>
   </si>
@@ -185,6 +185,18 @@
   </si>
   <si>
     <t>快慢指针</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
   </si>
   <si>
     <t>用栈实现队列</t>
@@ -1712,24 +1724,47 @@
     <row r="35" spans="2:2">
       <c r="B35" s="6"/>
     </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="6"/>
+    <row r="36" s="4" customFormat="1" spans="1:8">
+      <c r="A36" s="4">
+        <v>225</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="37" s="4" customFormat="1" spans="1:8">
       <c r="A37" s="4">
         <v>232</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>12</v>
@@ -1738,7 +1773,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:8">
@@ -1746,16 +1781,16 @@
         <v>131</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>12</v>
@@ -1764,7 +1799,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:8">
@@ -1772,13 +1807,13 @@
         <v>132</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>36</v>
@@ -1790,7 +1825,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:8">
@@ -1798,10 +1833,10 @@
         <v>125</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
@@ -1816,7 +1851,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" s="4" customFormat="1" spans="1:8">
@@ -1824,16 +1859,16 @@
         <v>1047</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>12</v>
@@ -1842,7 +1877,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:8">
@@ -1850,16 +1885,16 @@
         <v>61</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>12</v>
@@ -1868,7 +1903,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:8">
@@ -1876,16 +1911,16 @@
         <v>227</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>12</v>
@@ -1894,7 +1929,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:8">
@@ -1902,10 +1937,10 @@
         <v>226</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>16</v>
@@ -1920,7 +1955,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1949,6 +1984,7 @@
     <hyperlink ref="B42" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
     <hyperlink ref="B43" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
     <hyperlink ref="B44" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B36" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
   <si>
     <t>编号</t>
   </si>
@@ -61,15 +61,48 @@
     <t>长度为X的连续子区间元素之和的最大值</t>
   </si>
   <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>二进制间距</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-gap/</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>进制运算（右移位、与一）</t>
+  </si>
+  <si>
+    <t>转置矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
+  </si>
+  <si>
+    <t>二维数组</t>
+  </si>
+  <si>
     <t>翻转图像</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
   </si>
   <si>
-    <t>简单</t>
-  </si>
-  <si>
     <t>双指针</t>
   </si>
   <si>
@@ -100,25 +133,25 @@
     <t>子树深度</t>
   </si>
   <si>
-    <t>转置矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
-  </si>
-  <si>
-    <t>基础</t>
-  </si>
-  <si>
-    <t>二维数组</t>
-  </si>
-  <si>
-    <t>二进制间距</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-gap/</t>
-  </si>
-  <si>
-    <t>进制运算（右移位、与一）</t>
+    <t>比特位计数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/counting-bits/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>动态规划、位运算</t>
+  </si>
+  <si>
+    <t>二维区域和检索 - 矩阵不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
+  </si>
+  <si>
+    <t>二维动态规划——矩阵前缀和</t>
   </si>
   <si>
     <t>区域和检索 - 数组不可变</t>
@@ -127,19 +160,100 @@
     <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
   </si>
   <si>
-    <t>动态规划</t>
-  </si>
-  <si>
     <t>一维动态规划——数组前缀和</t>
   </si>
   <si>
-    <t>二维区域和检索 - 矩阵不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
-  </si>
-  <si>
-    <t>二维动态规划——矩阵前缀和</t>
+    <t>用栈实现队列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>二叉树</t>
+  </si>
+  <si>
+    <t>递归</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>两个动态规划</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
+  </si>
+  <si>
+    <t>二叉树的最大深度</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>广度优先搜索/深度优先搜索</t>
+  </si>
+  <si>
+    <t>二叉树的锯齿形层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>列表头插/列表反转/双端队列</t>
   </si>
   <si>
     <t>二叉树的层序遍历</t>
@@ -148,34 +262,16 @@
     <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
   </si>
   <si>
-    <t>二叉树</t>
-  </si>
-  <si>
-    <t>广度优先搜索/深度优先搜索</t>
-  </si>
-  <si>
-    <t>二叉树的锯齿形层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>列表头插/列表反转/双端队列</t>
-  </si>
-  <si>
-    <t>二叉树的最大深度</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>比特位计数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/counting-bits/</t>
-  </si>
-  <si>
-    <t>动态规划、位运算</t>
+    <t>旋转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>链表</t>
+  </si>
+  <si>
+    <t>循环链表</t>
   </si>
   <si>
     <t>删除排序数组中的重复项</t>
@@ -185,102 +281,6 @@
   </si>
   <si>
     <t>快慢指针</t>
-  </si>
-  <si>
-    <t>用队列实现栈</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
-  </si>
-  <si>
-    <t>队列</t>
-  </si>
-  <si>
-    <t>单/双队列</t>
-  </si>
-  <si>
-    <t>用栈实现队列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
-  </si>
-  <si>
-    <t>栈</t>
-  </si>
-  <si>
-    <t>双栈模拟</t>
-  </si>
-  <si>
-    <t>分割回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
-  </si>
-  <si>
-    <t>回溯搜索、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划用于降低判断回文数的复杂度</t>
-  </si>
-  <si>
-    <t>分割回文串 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
-  </si>
-  <si>
-    <t>困难</t>
-  </si>
-  <si>
-    <t>两个动态规划</t>
-  </si>
-  <si>
-    <t>验证回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
-  </si>
-  <si>
-    <t>字符串操作</t>
-  </si>
-  <si>
-    <t>删除字符串中的所有相邻重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>数据结构</t>
-  </si>
-  <si>
-    <t>旋转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/rotate-list/</t>
-  </si>
-  <si>
-    <t>链表</t>
-  </si>
-  <si>
-    <t>循环链表</t>
-  </si>
-  <si>
-    <t>基本计算器 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式</t>
-  </si>
-  <si>
-    <t>翻转二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
-  </si>
-  <si>
-    <t>递归</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,12 +474,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -793,149 +787,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -948,15 +942,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -964,12 +958,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1320,219 +1308,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
-    <col min="9" max="32" width="18.625" style="5" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="5" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="5" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="5"/>
+    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
+    <col min="9" max="32" width="18.625" style="4" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1052</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5">
-        <v>832</v>
+      <c r="A3" s="3">
+        <v>1047</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4">
+        <v>868</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5">
+      <c r="H4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4">
+        <v>867</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4">
+        <v>832</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4">
         <v>824</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="5">
+      <c r="H7" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="4">
         <v>543</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="5">
-        <v>867</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="H8" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="4">
+        <v>338</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5">
-        <v>868</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="H9" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:8">
       <c r="A10" s="1">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>12</v>
@@ -1541,24 +1581,24 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:8">
       <c r="A11" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>12</v>
@@ -1567,24 +1607,206 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
+      <c r="A12" s="3">
+        <v>232</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3">
+        <v>227</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:8">
+      <c r="A14" s="3">
+        <v>226</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:8">
+      <c r="A15" s="3">
+        <v>225</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:8">
+      <c r="A16" s="3">
+        <v>132</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:8">
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:8">
+      <c r="A17" s="3">
+        <v>131</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:8">
+      <c r="A18" s="3">
+        <v>125</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:8">
       <c r="A19" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
@@ -1593,24 +1815,24 @@
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:8">
       <c r="A20" s="2">
         <v>103</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
@@ -1619,24 +1841,24 @@
         <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:8">
       <c r="A21" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>12</v>
@@ -1645,346 +1867,91 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="5">
-        <v>338</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:8">
+      <c r="A22" s="3">
+        <v>61</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="5">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:7">
-      <c r="A26" s="3">
+      <c r="E22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:8">
+      <c r="A23" s="3">
         <v>26</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="B23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="6"/>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="6"/>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="6"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="6"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" s="4" customFormat="1" spans="1:8">
-      <c r="A36" s="4">
-        <v>225</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="4">
+      <c r="E23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="3">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" s="4" customFormat="1" spans="1:8">
-      <c r="A37" s="4">
-        <v>232</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="4">
-        <v>2</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" s="4" customFormat="1" spans="1:8">
-      <c r="A38" s="4">
-        <v>131</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="4">
-        <v>2</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" s="4" customFormat="1" spans="1:8">
-      <c r="A39" s="4">
-        <v>132</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="4">
-        <v>2</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" s="4" customFormat="1" spans="1:8">
-      <c r="A40" s="4">
-        <v>125</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="4">
-        <v>2</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" s="4" customFormat="1" spans="1:8">
-      <c r="A41" s="4">
-        <v>1047</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="4">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" s="4" customFormat="1" spans="1:8">
-      <c r="A42" s="4">
-        <v>61</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" s="4">
-        <v>2</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" s="4" customFormat="1" spans="1:8">
-      <c r="A43" s="4">
-        <v>227</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="4">
-        <v>2</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" s="4" customFormat="1" spans="1:8">
-      <c r="A44" s="4">
-        <v>226</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="4">
-        <v>2</v>
-      </c>
-      <c r="H44" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11">
+  <autoFilter ref="A1:H23">
+    <sortState ref="A2:H23">
+      <sortCondition ref="A1" descending="1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B3" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B4" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B7" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B10" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B11" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B19" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B6" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B7" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C8" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C5" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B4" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B11" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B10" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B21" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
     <hyperlink ref="B20" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="C20" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B21" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B25" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
-    <hyperlink ref="B26" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B37" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B38" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B40" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B41" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
-    <hyperlink ref="B42" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B43" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B44" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B36" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B19" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B9" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B23" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
+    <hyperlink ref="B12" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B17" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B18" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B3" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B22" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B13" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B14" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B15" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7665"/>
+    <workbookView windowWidth="27870" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,39 +43,144 @@
     <t>备注</t>
   </si>
   <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>用栈实现队列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>二叉树</t>
+  </si>
+  <si>
+    <t>递归</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>两个动态规划</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>字符串</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
+  </si>
+  <si>
+    <t>旋转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>链表</t>
+  </si>
+  <si>
+    <t>循环链表</t>
+  </si>
+  <si>
+    <t>删除排序数组中的重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/</t>
+  </si>
+  <si>
+    <t>双指针</t>
+  </si>
+  <si>
+    <t>快慢指针</t>
+  </si>
+  <si>
     <t>爱生气的书店老板</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
   </si>
   <si>
-    <t>中等</t>
-  </si>
-  <si>
     <t>滑动窗口</t>
   </si>
   <si>
-    <t>通过</t>
-  </si>
-  <si>
     <t>长度为X的连续子区间元素之和的最大值</t>
   </si>
   <si>
-    <t>删除字符串中的所有相邻重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>简单</t>
-  </si>
-  <si>
-    <t>栈</t>
-  </si>
-  <si>
-    <t>数据结构</t>
-  </si>
-  <si>
     <t>二进制间距</t>
   </si>
   <si>
@@ -103,9 +208,6 @@
     <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
   </si>
   <si>
-    <t>双指针</t>
-  </si>
-  <si>
     <t>双指针+异或取反</t>
   </si>
   <si>
@@ -115,9 +217,6 @@
     <t>https://leetcode-cn.com/problems/goat-latin/</t>
   </si>
   <si>
-    <t>字符串</t>
-  </si>
-  <si>
     <t>字符串与字符数组效率对比</t>
   </si>
   <si>
@@ -139,9 +238,6 @@
     <t>https://leetcode-cn.com/problems/counting-bits/</t>
   </si>
   <si>
-    <t>动态规划</t>
-  </si>
-  <si>
     <t>动态规划、位运算</t>
   </si>
   <si>
@@ -163,81 +259,6 @@
     <t>一维动态规划——数组前缀和</t>
   </si>
   <si>
-    <t>用栈实现队列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
-  </si>
-  <si>
-    <t>双栈模拟</t>
-  </si>
-  <si>
-    <t>基本计算器 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式</t>
-  </si>
-  <si>
-    <t>翻转二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
-  </si>
-  <si>
-    <t>二叉树</t>
-  </si>
-  <si>
-    <t>递归</t>
-  </si>
-  <si>
-    <t>用队列实现栈</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
-  </si>
-  <si>
-    <t>队列</t>
-  </si>
-  <si>
-    <t>单/双队列</t>
-  </si>
-  <si>
-    <t>分割回文串 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
-  </si>
-  <si>
-    <t>困难</t>
-  </si>
-  <si>
-    <t>两个动态规划</t>
-  </si>
-  <si>
-    <t>分割回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
-  </si>
-  <si>
-    <t>回溯搜索、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划用于降低判断回文数的复杂度</t>
-  </si>
-  <si>
-    <t>验证回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
-  </si>
-  <si>
-    <t>字符串操作</t>
-  </si>
-  <si>
     <t>二叉树的最大深度</t>
   </si>
   <si>
@@ -260,27 +281,6 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>旋转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/rotate-list/</t>
-  </si>
-  <si>
-    <t>链表</t>
-  </si>
-  <si>
-    <t>循环链表</t>
-  </si>
-  <si>
-    <t>删除排序数组中的重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/</t>
-  </si>
-  <si>
-    <t>快慢指针</t>
   </si>
 </sst>
 </file>
@@ -945,19 +945,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1351,46 +1351,46 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4">
-        <v>1052</v>
+      <c r="A2" s="3">
+        <v>1047</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3">
-        <v>1047</v>
-      </c>
-      <c r="B3" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -1399,466 +1399,466 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3">
+        <v>227</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
-        <v>868</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3">
+        <v>226</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>867</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3">
+        <v>225</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
-        <v>832</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3">
+        <v>132</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4">
-        <v>824</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="4">
-        <v>543</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="3">
+        <v>131</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="4">
-        <v>338</v>
+      <c r="A9" s="3">
+        <v>125</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:8">
+      <c r="A10" s="3">
+        <v>61</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:8">
+      <c r="A11" s="3">
+        <v>26</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
+      <c r="A12" s="4">
+        <v>1052</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4">
         <v>1</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
-      <c r="A10" s="1">
+      <c r="H12" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4">
+        <v>868</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:8">
+      <c r="A14" s="4">
+        <v>867</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:8">
+      <c r="A15" s="4">
+        <v>832</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:8">
+      <c r="A16" s="4">
+        <v>824</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:8">
+      <c r="A17" s="4">
+        <v>543</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:8">
+      <c r="A18" s="4">
+        <v>338</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:8">
+      <c r="A19" s="1">
         <v>304</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:8">
+      <c r="A20" s="1">
+        <v>303</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="E20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
-      <c r="A11" s="1">
-        <v>303</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="A12" s="3">
-        <v>232</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3">
-        <v>227</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="1:8">
-      <c r="A14" s="3">
-        <v>226</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:8">
-      <c r="A15" s="3">
-        <v>225</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:8">
-      <c r="A16" s="3">
-        <v>132</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="3">
-        <v>2</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:8">
-      <c r="A17" s="3">
-        <v>131</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:8">
-      <c r="A18" s="3">
-        <v>125</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:8">
-      <c r="A19" s="2">
-        <v>104</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:8">
-      <c r="A20" s="2">
-        <v>103</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>78</v>
+      <c r="H20" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:8">
       <c r="A21" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>12</v>
@@ -1867,91 +1867,91 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:8">
-      <c r="A22" s="3">
-        <v>61</v>
+      <c r="A22" s="2">
+        <v>103</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:8">
+      <c r="A23" s="2">
+        <v>102</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:8">
-      <c r="A23" s="3">
-        <v>26</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H23">
     <sortState ref="A2:H23">
-      <sortCondition ref="A1" descending="1"/>
+      <sortCondition ref="G1" descending="1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B6" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B7" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C8" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C5" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B4" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B11" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B10" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B21" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="B20" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="C20" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B19" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B9" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
-    <hyperlink ref="B23" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B12" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B17" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B18" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B3" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
-    <hyperlink ref="B22" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B13" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B14" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B15" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B12" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B15" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B16" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C17" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C14" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B13" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B20" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B19" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B23" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B22" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="C22" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="B21" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B18" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B11" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
+    <hyperlink ref="B3" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B8" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B9" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B2" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B10" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B4" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B5" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B6" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="13065"/>
+    <workbookView windowWidth="19200" windowHeight="7665"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="93">
   <si>
     <t>编号</t>
   </si>
@@ -281,6 +281,21 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>螺旋矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix/</t>
+  </si>
+  <si>
+    <t>数组</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>1.判断边界 2.避免重复</t>
   </si>
 </sst>
 </file>
@@ -288,10 +303,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -315,7 +330,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,13 +343,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -344,6 +375,68 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,53 +450,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -412,29 +458,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,20 +466,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -485,175 +500,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,30 +697,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -721,17 +712,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,11 +745,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -787,10 +802,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -799,137 +814,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -952,9 +967,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1308,7 +1320,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -1874,7 +1886,7 @@
       <c r="A22" s="2">
         <v>103</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1900,7 +1912,7 @@
       <c r="A23" s="2">
         <v>102</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1922,9 +1934,35 @@
         <v>82</v>
       </c>
     </row>
+    <row r="31" s="3" customFormat="1" spans="1:8">
+      <c r="A31" s="1">
+        <v>54</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H23">
-    <sortState ref="A2:H23">
+    <sortState ref="A1:H23">
       <sortCondition ref="G1" descending="1"/>
     </sortState>
     <extLst/>
@@ -1952,6 +1990,7 @@
     <hyperlink ref="B4" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
     <hyperlink ref="B5" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
     <hyperlink ref="B6" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B31" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
   <si>
     <t>编号</t>
   </si>
@@ -296,6 +296,18 @@
   </si>
   <si>
     <t>1.判断边界 2.避免重复</t>
+  </si>
+  <si>
+    <t>全排列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations/</t>
+  </si>
+  <si>
+    <t>回溯</t>
+  </si>
+  <si>
+    <t>排列组合</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -1958,6 +1970,32 @@
       </c>
       <c r="H31" s="1" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" spans="1:8">
+      <c r="A32" s="1">
+        <v>46</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1991,6 +2029,7 @@
     <hyperlink ref="B5" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
     <hyperlink ref="B6" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B31" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
+    <hyperlink ref="B32" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="100">
   <si>
     <t>编号</t>
   </si>
@@ -307,7 +307,16 @@
     <t>回溯</t>
   </si>
   <si>
-    <t>排列组合</t>
+    <t>简单排列</t>
+  </si>
+  <si>
+    <t>全排列 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations-ii/</t>
+  </si>
+  <si>
+    <t>排列去重</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -1996,6 +2005,32 @@
       </c>
       <c r="H32" s="1" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:8">
+      <c r="A33" s="1">
+        <v>47</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2030,6 +2065,7 @@
     <hyperlink ref="B6" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B31" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B32" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
+    <hyperlink ref="B33" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="107">
   <si>
     <t>编号</t>
   </si>
@@ -317,6 +317,27 @@
   </si>
   <si>
     <t>排列去重</t>
+  </si>
+  <si>
+    <t>移除元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-element/</t>
+  </si>
+  <si>
+    <t>交换or前移</t>
+  </si>
+  <si>
+    <t>两数相加</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/add-two-numbers/</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>①链表操作</t>
   </si>
 </sst>
 </file>
@@ -348,13 +369,6 @@
       <color rgb="FF262626"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -394,23 +408,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -421,6 +421,27 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -449,13 +470,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -481,14 +501,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,31 +542,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,139 +710,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,6 +765,56 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -765,56 +836,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -823,10 +844,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -835,16 +856,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -856,16 +877,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -874,94 +895,94 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1341,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -2031,6 +2052,58 @@
       </c>
       <c r="H33" s="1" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1" spans="1:8">
+      <c r="A34" s="1">
+        <v>27</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:8">
+      <c r="A38" s="1">
+        <v>2</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2066,6 +2139,8 @@
     <hyperlink ref="B31" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B32" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B33" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
+    <hyperlink ref="B34" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
+    <hyperlink ref="B38" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
   <si>
     <t>编号</t>
   </si>
@@ -338,6 +338,15 @@
   </si>
   <si>
     <t>①链表操作</t>
+  </si>
+  <si>
+    <t>螺旋矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -2104,6 +2113,32 @@
       </c>
       <c r="H38" s="1" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" spans="1:8">
+      <c r="A39" s="1">
+        <v>59</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2141,6 +2176,7 @@
     <hyperlink ref="B33" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
     <hyperlink ref="B34" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
     <hyperlink ref="B38" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
+    <hyperlink ref="B39" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="114">
   <si>
     <t>编号</t>
   </si>
@@ -347,6 +347,18 @@
   </si>
   <si>
     <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
+  </si>
+  <si>
+    <t>最大子序和</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
+  </si>
+  <si>
+    <t>动态规划、分治、线段树</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
   </si>
 </sst>
 </file>
@@ -524,7 +536,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,6 +558,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,28 +871,28 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,116 +904,116 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1008,6 +1026,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1021,6 +1042,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1371,45 +1395,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
-    <col min="9" max="32" width="18.625" style="4" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="4"/>
+    <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
+    <col min="9" max="32" width="18.625" style="5" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="5" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="5" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1417,7 +1441,7 @@
       <c r="A2" s="3">
         <v>1047</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1443,7 +1467,7 @@
       <c r="A3" s="3">
         <v>232</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1469,7 +1493,7 @@
       <c r="A4" s="3">
         <v>227</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1495,7 +1519,7 @@
       <c r="A5" s="3">
         <v>226</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1521,7 +1545,7 @@
       <c r="A6" s="3">
         <v>225</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1547,7 +1571,7 @@
       <c r="A7" s="3">
         <v>132</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1573,7 +1597,7 @@
       <c r="A8" s="3">
         <v>131</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1599,7 +1623,7 @@
       <c r="A9" s="3">
         <v>125</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1625,7 +1649,7 @@
       <c r="A10" s="3">
         <v>61</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1651,7 +1675,7 @@
       <c r="A11" s="3">
         <v>26</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1674,184 +1698,184 @@
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>1052</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5">
         <v>1</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>868</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:8">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <v>867</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:8">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>832</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5">
         <v>1</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:8">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <v>824</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
         <v>1</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:8">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
         <v>543</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:8">
-      <c r="A18" s="4">
+      <c r="A18" s="5">
         <v>338</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5">
         <v>1</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1859,7 +1883,7 @@
       <c r="A19" s="1">
         <v>304</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>74</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1885,7 +1909,7 @@
       <c r="A20" s="1">
         <v>303</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1911,7 +1935,7 @@
       <c r="A21" s="2">
         <v>104</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1937,7 +1961,7 @@
       <c r="A22" s="2">
         <v>103</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1963,7 +1987,7 @@
       <c r="A23" s="2">
         <v>102</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1989,7 +2013,7 @@
       <c r="A31" s="1">
         <v>54</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2015,7 +2039,7 @@
       <c r="A32" s="1">
         <v>46</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2041,7 +2065,7 @@
       <c r="A33" s="1">
         <v>47</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2067,7 +2091,7 @@
       <c r="A34" s="1">
         <v>27</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="8" t="s">
         <v>100</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2093,7 +2117,7 @@
       <c r="A38" s="1">
         <v>2</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -2119,7 +2143,7 @@
       <c r="A39" s="1">
         <v>59</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2139,6 +2163,32 @@
       </c>
       <c r="H39" s="1" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="47" s="4" customFormat="1" spans="1:8">
+      <c r="A47" s="4">
+        <v>53</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2177,6 +2227,7 @@
     <hyperlink ref="B34" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
     <hyperlink ref="B38" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
     <hyperlink ref="B39" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
+    <hyperlink ref="B47" r:id="rId28" display="最大子序和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="121">
   <si>
     <t>编号</t>
   </si>
@@ -349,7 +349,7 @@
     <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
   </si>
   <si>
-    <t>最大子序和</t>
+    <t>连续子数组最大和</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
@@ -359,6 +359,27 @@
   </si>
   <si>
     <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
+  </si>
+  <si>
+    <t>爬楼梯</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
+  </si>
+  <si>
+    <t>动态规划、斐波那契</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化</t>
+  </si>
+  <si>
+    <t>买卖股票的最佳时机</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②动态规划 ③存储优化</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -2189,6 +2210,58 @@
       </c>
       <c r="H47" s="4" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="48" s="4" customFormat="1" spans="1:8">
+      <c r="A48" s="4">
+        <v>70</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" s="4" customFormat="1" spans="1:8">
+      <c r="A49" s="4">
+        <v>121</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2227,7 +2300,8 @@
     <hyperlink ref="B34" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
     <hyperlink ref="B38" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
     <hyperlink ref="B39" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
-    <hyperlink ref="B47" r:id="rId28" display="最大子序和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
+    <hyperlink ref="B47" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
+    <hyperlink ref="B49" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$23</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
   <si>
     <t>编号</t>
   </si>
@@ -40,6 +40,9 @@
     <t>轮次</t>
   </si>
   <si>
+    <t>题解</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -380,6 +383,30 @@
   </si>
   <si>
     <t>①暴力搜索 ②动态规划 ③存储优化</t>
+  </si>
+  <si>
+    <t>反转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
+  </si>
+  <si>
+    <t>二叉树的前序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
+  </si>
+  <si>
+    <t>设计停车系统</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
+  </si>
+  <si>
+    <t>编程练习</t>
+  </si>
+  <si>
+    <t>①编程练习</t>
   </si>
 </sst>
 </file>
@@ -388,11 +415,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,8 +440,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -422,7 +462,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,6 +484,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -458,6 +505,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -467,21 +521,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,13 +566,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -543,14 +584,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -590,13 +623,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,31 +725,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,49 +773,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,67 +791,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,17 +820,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,16 +880,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -857,15 +899,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -892,10 +925,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -904,137 +937,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1067,6 +1100,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1416,8 +1452,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I83"/>
+  <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="28.25" style="5" customWidth="1"/>
@@ -1432,7 +1468,7 @@
     <col min="16384" max="16384" width="18.625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1456,6 +1492,9 @@
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1463,25 +1502,25 @@
         <v>1047</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3">
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1489,25 +1528,25 @@
         <v>232</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1515,25 +1554,25 @@
         <v>227</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3">
         <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1541,25 +1580,25 @@
         <v>226</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1567,25 +1606,25 @@
         <v>225</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1593,25 +1632,25 @@
         <v>132</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
@@ -1619,25 +1658,25 @@
         <v>131</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3">
         <v>2</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
@@ -1645,25 +1684,25 @@
         <v>125</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:8">
@@ -1671,25 +1710,25 @@
         <v>61</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
@@ -1697,25 +1736,25 @@
         <v>26</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3">
         <v>2</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
@@ -1723,25 +1762,25 @@
         <v>1052</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1749,25 +1788,25 @@
         <v>868</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="5">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:8">
@@ -1775,25 +1814,25 @@
         <v>867</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:8">
@@ -1801,25 +1840,25 @@
         <v>832</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="5">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:8">
@@ -1827,25 +1866,25 @@
         <v>824</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:8">
@@ -1853,25 +1892,25 @@
         <v>543</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:8">
@@ -1879,25 +1918,25 @@
         <v>338</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="5">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:8">
@@ -1905,25 +1944,25 @@
         <v>304</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:8">
@@ -1931,25 +1970,25 @@
         <v>303</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:8">
@@ -1957,25 +1996,25 @@
         <v>104</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:8">
@@ -1983,25 +2022,25 @@
         <v>103</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:8">
@@ -2009,25 +2048,25 @@
         <v>102</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:8">
@@ -2035,25 +2074,25 @@
         <v>54</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:8">
@@ -2061,25 +2100,25 @@
         <v>46</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:8">
@@ -2087,25 +2126,25 @@
         <v>47</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:8">
@@ -2113,25 +2152,25 @@
         <v>27</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:8">
@@ -2139,25 +2178,25 @@
         <v>2</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:8">
@@ -2165,25 +2204,25 @@
         <v>59</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:8">
@@ -2191,25 +2230,25 @@
         <v>53</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" s="4" customFormat="1" spans="1:8">
@@ -2217,25 +2256,25 @@
         <v>70</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" s="4" customFormat="1" spans="1:8">
@@ -2243,32 +2282,101 @@
         <v>121</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="5">
+        <v>206</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="5">
+        <v>144</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" s="4" customFormat="1" spans="1:8">
+      <c r="A83" s="4">
+        <v>1603</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23">
-    <sortState ref="A1:H23">
-      <sortCondition ref="G1" descending="1"/>
-    </sortState>
+  <autoFilter ref="A1:I23">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -2302,6 +2410,9 @@
     <hyperlink ref="B39" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B47" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
     <hyperlink ref="B49" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="B60" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B72" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="B83" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="132">
   <si>
     <t>编号</t>
   </si>
@@ -407,6 +407,12 @@
   </si>
   <si>
     <t>①编程练习</t>
+  </si>
+  <si>
+    <t>可以被一步捕获的棋子数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1458,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -2372,6 +2378,32 @@
         <v>106</v>
       </c>
       <c r="H83" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" s="4" customFormat="1" spans="1:8">
+      <c r="A92" s="4">
+        <v>999</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H92" s="4" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2413,6 +2445,7 @@
     <hyperlink ref="B60" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
     <hyperlink ref="B72" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
     <hyperlink ref="B83" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B92" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="135">
   <si>
     <t>编号</t>
   </si>
@@ -413,6 +413,15 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
+  </si>
+  <si>
+    <t>最大二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
+  </si>
+  <si>
+    <t>①递归</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1467,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -2405,6 +2414,32 @@
       </c>
       <c r="H92" s="4" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="93" s="4" customFormat="1" spans="1:8">
+      <c r="A93" s="4">
+        <v>654</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2446,6 +2481,7 @@
     <hyperlink ref="B72" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
     <hyperlink ref="B83" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
     <hyperlink ref="B92" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B93" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="138">
   <si>
     <t>编号</t>
   </si>
@@ -422,6 +422,15 @@
   </si>
   <si>
     <t>①递归</t>
+  </si>
+  <si>
+    <t>最大二叉树 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
+  </si>
+  <si>
+    <t>无官方题解，未计算复杂度</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1476,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -1477,7 +1486,8 @@
     <col min="5" max="5" width="24.5" style="5" customWidth="1"/>
     <col min="6" max="7" width="5.125" style="5" customWidth="1"/>
     <col min="8" max="8" width="41.125" style="5" customWidth="1"/>
-    <col min="9" max="32" width="18.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="5" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="5" customWidth="1"/>
     <col min="33" max="16352" width="28.125" style="5" customWidth="1"/>
     <col min="16353" max="16383" width="18.625" style="5" customWidth="1"/>
     <col min="16384" max="16384" width="18.625" style="5"/>
@@ -2440,6 +2450,35 @@
       </c>
       <c r="H93" s="4" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="94" s="4" customFormat="1" spans="1:9">
+      <c r="A94" s="4">
+        <v>998</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2482,6 +2521,7 @@
     <hyperlink ref="B83" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
     <hyperlink ref="B92" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
     <hyperlink ref="B93" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B94" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="142">
   <si>
     <t>编号</t>
   </si>
@@ -431,6 +431,18 @@
   </si>
   <si>
     <t>无官方题解，未计算复杂度</t>
+  </si>
+  <si>
+    <t>找到小镇的法官</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
+  </si>
+  <si>
+    <t>有向图</t>
+  </si>
+  <si>
+    <t>①有向图的入度/出度</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1488,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="5" customWidth="1"/>
@@ -2478,6 +2490,35 @@
         <v>134</v>
       </c>
       <c r="I94" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" s="4" customFormat="1" spans="1:9">
+      <c r="A95" s="4">
+        <v>997</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I95" s="4" t="s">
         <v>137</v>
       </c>
     </row>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="147">
   <si>
     <t>编号</t>
   </si>
@@ -446,6 +446,18 @@
   </si>
   <si>
     <t>一和零</t>
+  </si>
+  <si>
+    <t>位1的个数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-1-bits/</t>
+  </si>
+  <si>
+    <t>位运算</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④位运算优化</t>
   </si>
 </sst>
 </file>
@@ -629,12 +641,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -952,10 +970,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -964,16 +982,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -985,10 +1003,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1009,98 +1027,101 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1113,6 +1134,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1121,6 +1145,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1470,49 +1497,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="2" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="2" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="2" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="2" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="2" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="2"/>
+    <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="3" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="3" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="3" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="3" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="3" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1520,7 +1547,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1547,7 +1574,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1574,7 +1601,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1601,7 +1628,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1628,7 +1655,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1655,7 +1682,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1682,7 +1709,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1708,7 +1735,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1734,7 +1761,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1760,7 +1787,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1781,13 +1808,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1813,7 +1840,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1834,13 +1861,13 @@
       <c r="H13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1866,7 +1893,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1892,7 +1919,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1918,7 +1945,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1944,7 +1971,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1965,63 +1992,63 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="8"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>144</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="8"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>206</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:9">
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2042,13 +2069,13 @@
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="8"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2069,13 +2096,13 @@
       <c r="H22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2096,13 +2123,13 @@
       <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="8"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2123,13 +2150,13 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="8"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2150,13 +2177,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2177,67 +2204,67 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="6"/>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>338</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="F27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>543</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="2">
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="3">
         <v>1</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="6"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2260,116 +2287,116 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>824</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="2">
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3">
         <v>1</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="6"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>832</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="F31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3">
         <v>1</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>867</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="2">
+      <c r="F32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="3">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>868</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="6"/>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2398,7 +2425,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2419,7 +2446,7 @@
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="9" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2427,7 +2454,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2453,7 +2480,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2474,40 +2501,40 @@
       <c r="H37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="8"/>
+      <c r="I37" s="10"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>1052</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="3">
         <v>1</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="6"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2528,15 +2555,42 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="6"/>
+      <c r="I39" s="8"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>474</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>142</v>
       </c>
+    </row>
+    <row r="54" s="2" customFormat="1" spans="1:9">
+      <c r="A54" s="2">
+        <v>191</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I54" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2582,6 +2636,7 @@
     <hyperlink ref="B36" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
     <hyperlink ref="B29" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
     <hyperlink ref="B35" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B54" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
   <si>
     <t>编号</t>
   </si>
@@ -458,6 +458,15 @@
   </si>
   <si>
     <t>①②③位运算 ④位运算优化</t>
+  </si>
+  <si>
+    <t>矩阵置零</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/set-matrix-zeroes/</t>
+  </si>
+  <si>
+    <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1506,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
@@ -2591,6 +2600,33 @@
         <v>146</v>
       </c>
       <c r="I54" s="11"/>
+    </row>
+    <row r="55" s="2" customFormat="1" spans="1:9">
+      <c r="A55" s="2">
+        <v>73</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2637,6 +2673,7 @@
     <hyperlink ref="B29" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
     <hyperlink ref="B35" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B54" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
+    <hyperlink ref="B55" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="151">
   <si>
     <t>编号</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>位运算</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>①②③位运算 ④位运算优化</t>
@@ -659,18 +662,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -768,12 +777,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,10 +982,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -991,16 +994,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1012,7 +1015,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1036,55 +1039,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1099,10 +1102,10 @@
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1111,10 +1114,10 @@
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2594,10 +2597,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I54" s="11"/>
     </row>
@@ -2606,10 +2609,10 @@
         <v>73</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
@@ -2621,10 +2624,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I55" s="11"/>
     </row>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="154">
   <si>
     <t>编号</t>
   </si>
@@ -470,6 +470,15 @@
   </si>
   <si>
     <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
+  </si>
+  <si>
+    <t>逆波兰表达式求值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/</t>
+  </si>
+  <si>
+    <t>①逆波兰表达式</t>
   </si>
 </sst>
 </file>
@@ -653,7 +662,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +672,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -982,10 +997,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -994,16 +1009,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1015,10 +1030,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1039,92 +1054,92 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1134,6 +1149,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1149,6 +1167,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1158,7 +1179,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1509,49 +1533,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="3" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="3" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="3" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="3" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="3" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="3" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="3"/>
+    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="4" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="4" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1559,7 +1583,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1586,7 +1610,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1613,7 +1637,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1640,7 +1664,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1667,7 +1691,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1694,7 +1718,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1721,7 +1745,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1747,7 +1771,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1773,7 +1797,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1799,7 +1823,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1820,13 +1844,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1852,7 +1876,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1873,13 +1897,13 @@
       <c r="H13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1905,7 +1929,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1931,7 +1955,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1957,7 +1981,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1983,7 +2007,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2004,63 +2028,63 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>144</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="10"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>206</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="10"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:9">
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2081,13 +2105,13 @@
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="10"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2108,13 +2132,13 @@
       <c r="H22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="3"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2135,13 +2159,13 @@
       <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="10"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2162,13 +2186,13 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2189,13 +2213,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="8"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2216,67 +2240,67 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>338</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="F27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="4">
         <v>1</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="8"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>543</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="F28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="4">
         <v>1</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="8"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2299,116 +2323,116 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>824</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="F30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="8"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>832</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="F31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="4">
         <v>1</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>867</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="4">
         <v>1</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>868</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="F33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="4">
         <v>1</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="8"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2437,7 +2461,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2458,7 +2482,7 @@
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="11" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2466,7 +2490,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2492,7 +2516,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2513,40 +2537,40 @@
       <c r="H37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="10"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>1052</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="F38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4">
         <v>1</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="8"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2567,13 +2591,13 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="8"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>474</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2581,7 +2605,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2602,13 +2626,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="11"/>
+      <c r="I54" s="13"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2629,7 +2653,34 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="11"/>
+      <c r="I55" s="13"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:9">
+      <c r="A56" s="3">
+        <v>150</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I56" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2677,6 +2728,7 @@
     <hyperlink ref="B35" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B54" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
     <hyperlink ref="B55" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B56" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -662,7 +662,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,12 +672,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,149 +991,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1149,9 +1143,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1167,9 +1158,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1179,10 +1167,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1536,46 +1521,46 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="4" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="4" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="4"/>
+    <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="3" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="3" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="3" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="3" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="3" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1583,7 +1568,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1610,7 +1595,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1637,7 +1622,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1664,7 +1649,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1691,7 +1676,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1718,7 +1703,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1745,7 +1730,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1771,7 +1756,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1797,7 +1782,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1823,7 +1808,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1844,13 +1829,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1876,7 +1861,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1897,13 +1882,13 @@
       <c r="H13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1929,7 +1914,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1955,7 +1940,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1981,7 +1966,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2007,7 +1992,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2028,63 +2013,63 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>144</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="12"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>206</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="12"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:9">
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2105,13 +2090,13 @@
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="12"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2132,13 +2117,13 @@
       <c r="H22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="4"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2159,13 +2144,13 @@
       <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2186,13 +2171,13 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="12"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2213,13 +2198,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="10"/>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2240,67 +2225,67 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>338</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3">
         <v>1</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="10"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>543</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="3">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="10"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2323,116 +2308,116 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>824</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3">
         <v>1</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="10"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>832</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="F31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3">
         <v>1</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>867</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="F32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="3">
         <v>1</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>868</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3">
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="10"/>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2461,7 +2446,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2482,7 +2467,7 @@
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="9" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2490,7 +2475,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2516,7 +2501,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2537,40 +2522,40 @@
       <c r="H37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="12"/>
+      <c r="I37" s="10"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>1052</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="3">
         <v>1</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="10"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2591,13 +2576,13 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="10"/>
+      <c r="I39" s="8"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>474</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2605,7 +2590,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2626,13 +2611,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="13"/>
+      <c r="I54" s="11"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2653,34 +2638,34 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="13"/>
-    </row>
-    <row r="56" s="3" customFormat="1" spans="1:9">
-      <c r="A56" s="3">
+      <c r="I55" s="11"/>
+    </row>
+    <row r="56" s="2" customFormat="1" spans="1:9">
+      <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="F56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="14"/>
+      <c r="I56" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="158">
   <si>
     <t>编号</t>
   </si>
@@ -479,6 +479,18 @@
   </si>
   <si>
     <t>①逆波兰表达式</t>
+  </si>
+  <si>
+    <t>整数转罗马数字</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/integer-to-roman/</t>
+  </si>
+  <si>
+    <t>①贪心 ②编码表</t>
+  </si>
+  <si>
+    <t>暂缺负雪明烛</t>
   </si>
 </sst>
 </file>
@@ -662,7 +674,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,6 +684,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -991,10 +1009,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1003,16 +1021,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1024,10 +1042,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1048,92 +1066,92 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,6 +1161,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1150,7 +1171,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1158,8 +1179,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1167,8 +1191,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1518,49 +1545,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="3" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="3" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="3" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="3" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="3" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="3" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="3"/>
+    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="4" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="4" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1568,7 +1595,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1595,7 +1622,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1622,7 +1649,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1649,7 +1676,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1676,7 +1703,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1703,7 +1730,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1730,7 +1757,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1756,7 +1783,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1782,7 +1809,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1808,7 +1835,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1829,13 +1856,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1861,7 +1888,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1882,13 +1909,13 @@
       <c r="H13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1914,7 +1941,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1940,7 +1967,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1966,7 +1993,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1992,7 +2019,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2013,63 +2040,63 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>144</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="10"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>206</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="10"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:9">
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2090,13 +2117,13 @@
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="10"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2117,13 +2144,13 @@
       <c r="H22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="3"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2144,13 +2171,13 @@
       <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="10"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2171,13 +2198,13 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2198,13 +2225,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="8"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2225,67 +2252,67 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>338</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="F27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="4">
         <v>1</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="8"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>543</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="F28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="4">
         <v>1</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="8"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2308,116 +2335,116 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>824</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="F30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="8"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>832</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="F31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="4">
         <v>1</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>867</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="4">
         <v>1</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>868</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="F33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="4">
         <v>1</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="8"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2446,7 +2473,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2467,7 +2494,7 @@
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="11" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2475,7 +2502,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2501,7 +2528,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2522,40 +2549,40 @@
       <c r="H37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="10"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>1052</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="F38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4">
         <v>1</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="8"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2576,13 +2603,13 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="8"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>474</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2590,7 +2617,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2611,13 +2638,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="11"/>
+      <c r="I54" s="13"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2638,13 +2665,13 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="11"/>
+      <c r="I55" s="13"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2665,7 +2692,36 @@
       <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="11"/>
+      <c r="I56" s="13"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:9">
+      <c r="A57" s="3">
+        <v>12</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>157</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2714,6 +2770,7 @@
     <hyperlink ref="B54" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
     <hyperlink ref="B55" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B56" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
+    <hyperlink ref="B57" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="162">
   <si>
     <t>编号</t>
   </si>
@@ -491,6 +491,18 @@
   </si>
   <si>
     <t>暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>数字转换为十六进制数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
+  </si>
+  <si>
+    <t>①位运算</t>
+  </si>
+  <si>
+    <t>暂缺官方题解 暂缺负雪明烛</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -2721,6 +2733,35 @@
       </c>
       <c r="I57" s="14" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" spans="1:9">
+      <c r="A58" s="3">
+        <v>405</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2771,6 +2812,7 @@
     <hyperlink ref="B55" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B56" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B57" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
+    <hyperlink ref="B58" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="165">
   <si>
     <t>编号</t>
   </si>
@@ -503,6 +503,15 @@
   </si>
   <si>
     <t>暂缺官方题解 暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>二叉搜索树的最近公共祖先</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
+  </si>
+  <si>
+    <t>①一趟遍历 ②两趟遍历</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1566,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -2762,6 +2771,35 @@
       </c>
       <c r="I58" s="14" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:9">
+      <c r="A59" s="3">
+        <v>235</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2813,6 +2851,7 @@
     <hyperlink ref="B56" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B57" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
     <hyperlink ref="B58" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B59" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="171">
   <si>
     <t>编号</t>
   </si>
@@ -512,6 +512,24 @@
   </si>
   <si>
     <t>①一趟遍历 ②两趟遍历</t>
+  </si>
+  <si>
+    <t>合并二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
+  </si>
+  <si>
+    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
+  </si>
+  <si>
+    <t>电话号码的字母组合</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/</t>
+  </si>
+  <si>
+    <t>①回溯</t>
   </si>
 </sst>
 </file>
@@ -520,9 +538,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -552,14 +570,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -567,7 +585,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -589,13 +607,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -604,14 +615,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -626,7 +630,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -664,8 +675,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -687,15 +706,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,13 +734,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,169 +800,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,9 +933,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -945,26 +962,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1022,6 +1019,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1030,10 +1036,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1042,137 +1048,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1185,18 +1191,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1206,16 +1206,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1566,57 +1560,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="4" customWidth="1"/>
-    <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="4" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="4" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="4" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="4" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="4"/>
+    <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="1" customWidth="1"/>
+    <col min="6" max="7" width="5.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="1" customWidth="1"/>
+    <col min="10" max="32" width="18.625" style="1" customWidth="1"/>
+    <col min="33" max="16352" width="28.125" style="1" customWidth="1"/>
+    <col min="16353" max="16383" width="18.625" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="18.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1637,13 +1631,12 @@
       <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1664,13 +1657,12 @@
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1691,13 +1683,12 @@
       <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1718,13 +1709,12 @@
       <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9">
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1745,13 +1735,12 @@
       <c r="H6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1772,13 +1761,12 @@
       <c r="H7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="1"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1804,7 +1792,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1830,7 +1818,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1856,7 +1844,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1877,13 +1865,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1905,11 +1893,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1930,13 +1918,12 @@
       <c r="H13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1962,7 +1949,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1988,7 +1975,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2014,7 +2001,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2036,11 +2023,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:9">
+    <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2061,63 +2048,58 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="4">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="A19" s="1">
         <v>144</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="4">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="A20" s="1">
         <v>206</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:9">
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:8">
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2138,13 +2120,12 @@
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:9">
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:8">
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2165,13 +2146,12 @@
       <c r="H22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:9">
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:8">
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2192,13 +2172,12 @@
       <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:9">
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:8">
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2219,13 +2198,12 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="12"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2246,13 +2224,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="10"/>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2273,67 +2251,67 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="4">
+      <c r="A27" s="1">
         <v>338</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1">
         <v>1</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="10"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
-      <c r="A28" s="4">
+      <c r="A28" s="1">
         <v>543</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="F28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="10"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2356,116 +2334,116 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="4">
+      <c r="A30" s="1">
         <v>824</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1">
         <v>1</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="10"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="4">
+      <c r="A31" s="1">
         <v>832</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="4">
+      <c r="A32" s="1">
         <v>867</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1">
         <v>1</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="4">
+      <c r="A33" s="1">
         <v>868</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1">
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="10"/>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2494,7 +2472,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2515,7 +2493,7 @@
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="1" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2523,7 +2501,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2545,11 +2523,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="1:9">
+    <row r="37" s="1" customFormat="1" spans="1:8">
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2570,40 +2548,39 @@
       <c r="H37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="12"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="4">
+      <c r="A38" s="1">
         <v>1052</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="1">
         <v>1</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="10"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2624,13 +2601,13 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="10"/>
+      <c r="I39" s="8"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="4">
+      <c r="A46" s="1">
         <v>474</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2638,7 +2615,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2659,13 +2636,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="13"/>
+      <c r="I54" s="9"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2686,13 +2663,13 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="13"/>
+      <c r="I55" s="9"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2713,13 +2690,13 @@
       <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="13"/>
+      <c r="I56" s="9"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:9">
       <c r="A57" s="3">
         <v>12</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="7" t="s">
         <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -2740,7 +2717,7 @@
       <c r="H57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="I57" s="10" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2748,7 +2725,7 @@
       <c r="A58" s="3">
         <v>405</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -2769,7 +2746,7 @@
       <c r="H58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="14" t="s">
+      <c r="I58" s="10" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2777,7 +2754,7 @@
       <c r="A59" s="3">
         <v>235</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -2798,13 +2775,71 @@
       <c r="H59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I59" s="14" t="s">
+      <c r="I59" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:9">
+      <c r="A60" s="3">
+        <v>617</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:9">
+      <c r="A68" s="3">
+        <v>17</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I68" s="10" t="s">
         <v>157</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
-    <sortState ref="A2:I39">
+    <sortState ref="A1:I39">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -2852,6 +2887,8 @@
     <hyperlink ref="B57" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
     <hyperlink ref="B58" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
     <hyperlink ref="B59" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B60" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B68" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="174">
   <si>
     <t>编号</t>
   </si>
@@ -530,6 +530,15 @@
   </si>
   <si>
     <t>①回溯</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
+  </si>
+  <si>
+    <t>①两个变量 ①一个变量</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2836,6 +2845,33 @@
       <c r="I68" s="10" t="s">
         <v>157</v>
       </c>
+    </row>
+    <row r="74" s="3" customFormat="1" spans="1:9">
+      <c r="A74" s="3">
+        <v>83</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I74" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2889,6 +2925,7 @@
     <hyperlink ref="B59" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
     <hyperlink ref="B60" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B68" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
+    <hyperlink ref="B74" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="180">
   <si>
     <t>编号</t>
   </si>
@@ -532,6 +532,12 @@
     <t>①回溯</t>
   </si>
   <si>
+    <t>删除排序链表中的重复元素 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
+  </si>
+  <si>
     <t>删除排序链表中的重复元素</t>
   </si>
   <si>
@@ -539,6 +545,18 @@
   </si>
   <si>
     <t>①两个变量 ①一个变量</t>
+  </si>
+  <si>
+    <t>颠倒二进制位</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④分治</t>
   </si>
 </sst>
 </file>
@@ -722,7 +740,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,6 +756,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1045,10 +1069,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1057,137 +1081,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1200,6 +1224,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1219,6 +1246,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1569,7 +1602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1619,7 +1652,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1645,7 +1678,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1671,7 +1704,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1697,7 +1730,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1723,7 +1756,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1749,7 +1782,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1775,7 +1808,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1801,7 +1834,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1827,7 +1860,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1853,7 +1886,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1874,13 +1907,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1906,7 +1939,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1932,7 +1965,7 @@
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1958,7 +1991,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1984,7 +2017,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2010,7 +2043,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2036,7 +2069,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2062,7 +2095,7 @@
       <c r="A19" s="1">
         <v>144</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2085,7 +2118,7 @@
       <c r="A20" s="1">
         <v>206</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2108,7 +2141,7 @@
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2134,7 +2167,7 @@
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2160,7 +2193,7 @@
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2186,7 +2219,7 @@
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2212,7 +2245,7 @@
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2233,13 +2266,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="8"/>
+      <c r="I25" s="9"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2260,13 +2293,13 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="9"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
       <c r="A27" s="1">
         <v>338</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2287,7 +2320,7 @@
       <c r="H27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="8"/>
+      <c r="I27" s="9"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
@@ -2314,13 +2347,13 @@
       <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="8"/>
+      <c r="I28" s="9"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2346,7 +2379,7 @@
       <c r="A30" s="1">
         <v>824</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2367,13 +2400,13 @@
       <c r="H30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="8"/>
+      <c r="I30" s="9"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1">
         <v>832</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2425,7 +2458,7 @@
       <c r="A33" s="1">
         <v>868</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2446,13 +2479,13 @@
       <c r="H33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="8"/>
+      <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2481,7 +2514,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2510,7 +2543,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2536,7 +2569,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2562,7 +2595,7 @@
       <c r="A38" s="1">
         <v>1052</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -2583,13 +2616,13 @@
       <c r="H38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="8"/>
+      <c r="I38" s="9"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2610,7 +2643,7 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="8"/>
+      <c r="I39" s="9"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1">
@@ -2624,7 +2657,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2645,13 +2678,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="9"/>
+      <c r="I54" s="10"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2672,13 +2705,13 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="9"/>
+      <c r="I55" s="10"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2699,13 +2732,13 @@
       <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="9"/>
+      <c r="I56" s="10"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:9">
       <c r="A57" s="3">
         <v>12</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="8" t="s">
         <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -2726,7 +2759,7 @@
       <c r="H57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I57" s="10" t="s">
+      <c r="I57" s="11" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2734,7 +2767,7 @@
       <c r="A58" s="3">
         <v>405</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -2755,7 +2788,7 @@
       <c r="H58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="11" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2763,7 +2796,7 @@
       <c r="A59" s="3">
         <v>235</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="8" t="s">
         <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -2784,7 +2817,7 @@
       <c r="H59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="11" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2792,7 +2825,7 @@
       <c r="A60" s="3">
         <v>617</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -2813,7 +2846,7 @@
       <c r="H60" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="11" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2821,7 +2854,7 @@
       <c r="A68" s="3">
         <v>17</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -2842,19 +2875,43 @@
       <c r="H68" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I68" s="10" t="s">
+      <c r="I68" s="11" t="s">
         <v>157</v>
       </c>
+    </row>
+    <row r="73" s="3" customFormat="1" spans="1:9">
+      <c r="A73" s="3">
+        <v>82</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="11"/>
     </row>
     <row r="74" s="3" customFormat="1" spans="1:9">
       <c r="A74" s="3">
         <v>83</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>171</v>
+      <c r="B74" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>18</v>
@@ -2869,9 +2926,36 @@
         <v>14</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I74" s="10"/>
+        <v>175</v>
+      </c>
+      <c r="I74" s="11"/>
+    </row>
+    <row r="80" s="4" customFormat="1" spans="1:9">
+      <c r="A80" s="4">
+        <v>190</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I80" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -2926,6 +3010,8 @@
     <hyperlink ref="B60" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B68" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
     <hyperlink ref="B74" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
+    <hyperlink ref="B73" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
+    <hyperlink ref="B80" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="182">
   <si>
     <t>编号</t>
   </si>
@@ -557,6 +557,12 @@
   </si>
   <si>
     <t>①②③位运算 ④分治</t>
+  </si>
+  <si>
+    <t>打家劫舍</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/house-robber/</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2956,6 +2962,33 @@
         <v>179</v>
       </c>
       <c r="I80" s="13"/>
+    </row>
+    <row r="81" s="4" customFormat="1" spans="1:9">
+      <c r="A81" s="4">
+        <v>198</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I81" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3012,6 +3045,7 @@
     <hyperlink ref="B74" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="B73" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
     <hyperlink ref="B80" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
+    <hyperlink ref="B81" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="185">
   <si>
     <t>编号</t>
   </si>
@@ -563,6 +563,15 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/house-robber/</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
+    <t>二叉树的右视图</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1617,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2986,9 +2995,33 @@
         <v>178</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="I81" s="13"/>
+    </row>
+    <row r="82" s="4" customFormat="1" spans="1:9">
+      <c r="A82" s="4">
+        <v>199</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I82" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3046,6 +3079,7 @@
     <hyperlink ref="B73" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
     <hyperlink ref="B80" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
     <hyperlink ref="B81" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
+    <hyperlink ref="B82" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="186">
   <si>
     <t>编号</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索</t>
   </si>
 </sst>
 </file>
@@ -3021,6 +3024,9 @@
       <c r="G82" s="4" t="s">
         <v>178</v>
       </c>
+      <c r="H82" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="I82" s="13"/>
     </row>
   </sheetData>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="190">
   <si>
     <t>编号</t>
   </si>
@@ -575,6 +575,18 @@
   </si>
   <si>
     <t>①广度优先搜索 ②深度优先搜索</t>
+  </si>
+  <si>
+    <t>岛屿数量</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>广度优先搜索</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1632,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3028,6 +3040,33 @@
         <v>185</v>
       </c>
       <c r="I82" s="13"/>
+    </row>
+    <row r="83" s="4" customFormat="1" spans="1:9">
+      <c r="A83" s="4">
+        <v>200</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I83" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3086,6 +3125,7 @@
     <hyperlink ref="B80" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
     <hyperlink ref="B81" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
     <hyperlink ref="B82" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
+    <hyperlink ref="B83" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="196">
   <si>
     <t>编号</t>
   </si>
@@ -587,6 +587,24 @@
   </si>
   <si>
     <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
+  </si>
+  <si>
+    <t>搜索插入位置</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>二分查找</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
+  </si>
+  <si>
+    <t>①两轮二分查找 ②一轮二分查找 ③利用矩阵大小关系</t>
   </si>
 </sst>
 </file>
@@ -1632,7 +1650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3067,6 +3085,57 @@
         <v>189</v>
       </c>
       <c r="I83" s="13"/>
+    </row>
+    <row r="88" s="4" customFormat="1" spans="1:9">
+      <c r="A88" s="4">
+        <v>35</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I88" s="13"/>
+    </row>
+    <row r="93" s="4" customFormat="1" spans="1:9">
+      <c r="A93" s="4">
+        <v>74</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I93" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3126,6 +3195,8 @@
     <hyperlink ref="B81" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
     <hyperlink ref="B82" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
     <hyperlink ref="B83" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
+    <hyperlink ref="B88" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
+    <hyperlink ref="B93" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="198">
   <si>
     <t>编号</t>
   </si>
@@ -605,6 +605,12 @@
   </si>
   <si>
     <t>①两轮二分查找 ②一轮二分查找 ③利用矩阵大小关系</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
   </si>
 </sst>
 </file>
@@ -815,6 +821,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -864,12 +876,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1132,93 +1138,93 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1228,38 +1234,38 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1275,6 +1281,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1299,7 +1308,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1650,7 +1665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1700,7 +1715,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1726,7 +1741,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1752,7 +1767,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1778,7 +1793,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1804,7 +1819,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1830,7 +1845,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1856,7 +1871,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1882,7 +1897,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1908,7 +1923,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1934,7 +1949,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1955,13 +1970,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1987,7 +2002,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2013,7 +2028,7 @@
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2039,7 +2054,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2065,7 +2080,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2091,7 +2106,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2117,7 +2132,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2143,7 +2158,7 @@
       <c r="A19" s="1">
         <v>144</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2166,7 +2181,7 @@
       <c r="A20" s="1">
         <v>206</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2189,7 +2204,7 @@
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2215,7 +2230,7 @@
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2241,7 +2256,7 @@
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2267,7 +2282,7 @@
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2293,7 +2308,7 @@
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2314,13 +2329,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="9"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2341,13 +2356,13 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="9"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
       <c r="A27" s="1">
         <v>338</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2368,7 +2383,7 @@
       <c r="H27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="9"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
@@ -2395,13 +2410,13 @@
       <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="9"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2427,7 +2442,7 @@
       <c r="A30" s="1">
         <v>824</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2448,13 +2463,13 @@
       <c r="H30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="9"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1">
         <v>832</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2506,7 +2521,7 @@
       <c r="A33" s="1">
         <v>868</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2527,13 +2542,13 @@
       <c r="H33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="9"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2562,7 +2577,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2591,7 +2606,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2617,7 +2632,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2643,7 +2658,7 @@
       <c r="A38" s="1">
         <v>1052</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -2664,13 +2679,13 @@
       <c r="H38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="9"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2691,7 +2706,7 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="9"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1">
@@ -2705,7 +2720,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2726,13 +2741,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="10"/>
+      <c r="I54" s="11"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2753,13 +2768,13 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="10"/>
+      <c r="I55" s="11"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2780,13 +2795,13 @@
       <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="10"/>
+      <c r="I56" s="11"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:9">
       <c r="A57" s="3">
         <v>12</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="9" t="s">
         <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -2807,7 +2822,7 @@
       <c r="H57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2815,7 +2830,7 @@
       <c r="A58" s="3">
         <v>405</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -2836,7 +2851,7 @@
       <c r="H58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2844,7 +2859,7 @@
       <c r="A59" s="3">
         <v>235</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="9" t="s">
         <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -2865,7 +2880,7 @@
       <c r="H59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2873,7 +2888,7 @@
       <c r="A60" s="3">
         <v>617</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -2894,7 +2909,7 @@
       <c r="H60" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2902,7 +2917,7 @@
       <c r="A68" s="3">
         <v>17</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="9" t="s">
         <v>168</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -2923,7 +2938,7 @@
       <c r="H68" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2931,7 +2946,7 @@
       <c r="A73" s="3">
         <v>82</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="9" t="s">
         <v>171</v>
       </c>
       <c r="C73" s="3" t="s">
@@ -2949,13 +2964,13 @@
       <c r="G73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I73" s="11"/>
+      <c r="I73" s="12"/>
     </row>
     <row r="74" s="3" customFormat="1" spans="1:9">
       <c r="A74" s="3">
         <v>83</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="9" t="s">
         <v>173</v>
       </c>
       <c r="C74" s="3" t="s">
@@ -2976,13 +2991,13 @@
       <c r="H74" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I74" s="11"/>
+      <c r="I74" s="12"/>
     </row>
     <row r="80" s="4" customFormat="1" spans="1:9">
       <c r="A80" s="4">
         <v>190</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>176</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -3003,13 +3018,13 @@
       <c r="H80" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I80" s="13"/>
+      <c r="I80" s="15"/>
     </row>
     <row r="81" s="4" customFormat="1" spans="1:9">
       <c r="A81" s="4">
         <v>198</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="13" t="s">
         <v>180</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -3030,13 +3045,13 @@
       <c r="H81" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="I81" s="13"/>
+      <c r="I81" s="15"/>
     </row>
     <row r="82" s="4" customFormat="1" spans="1:9">
       <c r="A82" s="4">
         <v>199</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>183</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -3057,13 +3072,13 @@
       <c r="H82" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I82" s="13"/>
+      <c r="I82" s="15"/>
     </row>
     <row r="83" s="4" customFormat="1" spans="1:9">
       <c r="A83" s="4">
         <v>200</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>186</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -3084,13 +3099,13 @@
       <c r="H83" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="I83" s="13"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="88" s="4" customFormat="1" spans="1:9">
       <c r="A88" s="4">
         <v>35</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -3108,34 +3123,58 @@
       <c r="G88" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="I88" s="13"/>
-    </row>
-    <row r="93" s="4" customFormat="1" spans="1:9">
-      <c r="A93" s="4">
+      <c r="I88" s="15"/>
+    </row>
+    <row r="93" s="5" customFormat="1" spans="1:9">
+      <c r="A93" s="5">
         <v>74</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E93" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="4" t="s">
+      <c r="F93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H93" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="I93" s="13"/>
+      <c r="I93" s="16"/>
+    </row>
+    <row r="94" s="5" customFormat="1" spans="1:9">
+      <c r="A94" s="5">
+        <v>240</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I94" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3197,6 +3236,7 @@
     <hyperlink ref="B83" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B88" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B93" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
+    <hyperlink ref="B94" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="199">
   <si>
     <t>编号</t>
   </si>
@@ -604,13 +604,16 @@
     <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
   </si>
   <si>
-    <t>①两轮二分查找 ②一轮二分查找 ③利用矩阵大小关系</t>
+    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
   </si>
   <si>
     <t>搜索二维矩阵 II</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①缩减空间</t>
   </si>
 </sst>
 </file>
@@ -3174,6 +3177,9 @@
       <c r="G94" s="5" t="s">
         <v>178</v>
       </c>
+      <c r="H94" s="5" t="s">
+        <v>198</v>
+      </c>
       <c r="I94" s="16"/>
     </row>
   </sheetData>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="203">
   <si>
     <t>编号</t>
   </si>
@@ -614,6 +614,18 @@
   </si>
   <si>
     <t>①缩减空间</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②二分查找</t>
   </si>
 </sst>
 </file>
@@ -667,22 +679,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -699,17 +695,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -729,25 +725,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -760,13 +740,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -782,11 +755,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -796,8 +784,32 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -830,7 +842,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -842,7 +914,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -854,25 +932,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,19 +950,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -908,19 +992,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,67 +1004,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,22 +1039,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1056,6 +1069,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1071,17 +1095,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1109,15 +1136,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1126,149 +1144,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1287,6 +1305,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,10 +1335,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1668,7 +1695,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1718,7 +1745,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1744,7 +1771,7 @@
       <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1770,7 +1797,7 @@
       <c r="A4" s="1">
         <v>27</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1796,7 +1823,7 @@
       <c r="A5" s="1">
         <v>46</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1822,7 +1849,7 @@
       <c r="A6" s="1">
         <v>47</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1848,7 +1875,7 @@
       <c r="A7" s="1">
         <v>53</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1874,7 +1901,7 @@
       <c r="A8" s="1">
         <v>54</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1900,7 +1927,7 @@
       <c r="A9" s="1">
         <v>59</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1926,7 +1953,7 @@
       <c r="A10" s="1">
         <v>61</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1952,7 +1979,7 @@
       <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1973,13 +2000,13 @@
       <c r="H11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
         <v>102</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2005,7 +2032,7 @@
       <c r="A13" s="1">
         <v>103</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2031,7 +2058,7 @@
       <c r="A14" s="1">
         <v>104</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2057,7 +2084,7 @@
       <c r="A15" s="1">
         <v>121</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2083,7 +2110,7 @@
       <c r="A16" s="1">
         <v>125</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2109,7 +2136,7 @@
       <c r="A17" s="1">
         <v>131</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2135,7 +2162,7 @@
       <c r="A18" s="1">
         <v>132</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2161,7 +2188,7 @@
       <c r="A19" s="1">
         <v>144</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2184,7 +2211,7 @@
       <c r="A20" s="1">
         <v>206</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2207,7 +2234,7 @@
       <c r="A21" s="1">
         <v>225</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2233,7 +2260,7 @@
       <c r="A22" s="1">
         <v>226</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2259,7 +2286,7 @@
       <c r="A23" s="1">
         <v>227</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2285,7 +2312,7 @@
       <c r="A24" s="1">
         <v>232</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2311,7 +2338,7 @@
       <c r="A25" s="1">
         <v>303</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2332,13 +2359,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="10"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>304</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2359,13 +2386,13 @@
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
       <c r="A27" s="1">
         <v>338</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2386,7 +2413,7 @@
       <c r="H27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I27" s="10"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
@@ -2413,13 +2440,13 @@
       <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="10"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
         <v>654</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2445,7 +2472,7 @@
       <c r="A30" s="1">
         <v>824</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2466,13 +2493,13 @@
       <c r="H30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="10"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1">
         <v>832</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2524,7 +2551,7 @@
       <c r="A33" s="1">
         <v>868</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2545,13 +2572,13 @@
       <c r="H33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="10"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>997</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2580,7 +2607,7 @@
       <c r="A35" s="1">
         <v>998</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2609,7 +2636,7 @@
       <c r="A36" s="1">
         <v>999</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2635,7 +2662,7 @@
       <c r="A37" s="1">
         <v>1047</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2661,7 +2688,7 @@
       <c r="A38" s="1">
         <v>1052</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -2682,13 +2709,13 @@
       <c r="H38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="10"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>1603</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2709,7 +2736,7 @@
       <c r="H39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="10"/>
+      <c r="I39" s="11"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1">
@@ -2723,7 +2750,7 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="9" t="s">
         <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2744,13 +2771,13 @@
       <c r="H54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="11"/>
+      <c r="I54" s="12"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="9" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2771,13 +2798,13 @@
       <c r="H55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I55" s="11"/>
+      <c r="I55" s="12"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2798,13 +2825,13 @@
       <c r="H56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I56" s="11"/>
+      <c r="I56" s="12"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:9">
       <c r="A57" s="3">
         <v>12</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="10" t="s">
         <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -2825,7 +2852,7 @@
       <c r="H57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="13" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2833,7 +2860,7 @@
       <c r="A58" s="3">
         <v>405</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -2854,7 +2881,7 @@
       <c r="H58" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="13" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2862,7 +2889,7 @@
       <c r="A59" s="3">
         <v>235</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="10" t="s">
         <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -2883,7 +2910,7 @@
       <c r="H59" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="I59" s="13" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2891,7 +2918,7 @@
       <c r="A60" s="3">
         <v>617</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="10" t="s">
         <v>165</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -2912,7 +2939,7 @@
       <c r="H60" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="I60" s="13" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2920,7 +2947,7 @@
       <c r="A68" s="3">
         <v>17</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="10" t="s">
         <v>168</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -2941,7 +2968,7 @@
       <c r="H68" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="13" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2949,7 +2976,7 @@
       <c r="A73" s="3">
         <v>82</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>171</v>
       </c>
       <c r="C73" s="3" t="s">
@@ -2967,13 +2994,13 @@
       <c r="G73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I73" s="12"/>
+      <c r="I73" s="13"/>
     </row>
     <row r="74" s="3" customFormat="1" spans="1:9">
       <c r="A74" s="3">
         <v>83</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>173</v>
       </c>
       <c r="C74" s="3" t="s">
@@ -2994,13 +3021,13 @@
       <c r="H74" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I74" s="12"/>
+      <c r="I74" s="13"/>
     </row>
     <row r="80" s="4" customFormat="1" spans="1:9">
       <c r="A80" s="4">
         <v>190</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="14" t="s">
         <v>176</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -3021,13 +3048,13 @@
       <c r="H80" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I80" s="15"/>
+      <c r="I80" s="17"/>
     </row>
     <row r="81" s="4" customFormat="1" spans="1:9">
       <c r="A81" s="4">
         <v>198</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="14" t="s">
         <v>180</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -3048,13 +3075,13 @@
       <c r="H81" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="I81" s="15"/>
+      <c r="I81" s="17"/>
     </row>
     <row r="82" s="4" customFormat="1" spans="1:9">
       <c r="A82" s="4">
         <v>199</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="14" t="s">
         <v>183</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -3075,13 +3102,13 @@
       <c r="H82" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I82" s="15"/>
+      <c r="I82" s="17"/>
     </row>
     <row r="83" s="4" customFormat="1" spans="1:9">
       <c r="A83" s="4">
         <v>200</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="14" t="s">
         <v>186</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -3102,13 +3129,13 @@
       <c r="H83" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="I83" s="15"/>
+      <c r="I83" s="17"/>
     </row>
     <row r="88" s="4" customFormat="1" spans="1:9">
       <c r="A88" s="4">
         <v>35</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="14" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -3126,13 +3153,13 @@
       <c r="G88" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="I88" s="15"/>
+      <c r="I88" s="17"/>
     </row>
     <row r="93" s="5" customFormat="1" spans="1:9">
       <c r="A93" s="5">
         <v>74</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C93" s="5" t="s">
@@ -3153,13 +3180,13 @@
       <c r="H93" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="I93" s="16"/>
+      <c r="I93" s="18"/>
     </row>
     <row r="94" s="5" customFormat="1" spans="1:9">
       <c r="A94" s="5">
         <v>240</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="15" t="s">
         <v>196</v>
       </c>
       <c r="C94" s="5" t="s">
@@ -3180,7 +3207,34 @@
       <c r="H94" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="I94" s="16"/>
+      <c r="I94" s="18"/>
+    </row>
+    <row r="100" s="6" customFormat="1" spans="1:9">
+      <c r="A100" s="6">
+        <v>153</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I100" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3243,6 +3297,7 @@
     <hyperlink ref="B88" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B93" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
     <hyperlink ref="B94" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B100" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="205">
   <si>
     <t>编号</t>
   </si>
@@ -626,6 +626,12 @@
   </si>
   <si>
     <t>①暴力搜索 ②二分查找</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1701,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3235,6 +3241,33 @@
         <v>202</v>
       </c>
       <c r="I100" s="19"/>
+    </row>
+    <row r="101" s="6" customFormat="1" spans="1:9">
+      <c r="A101" s="6">
+        <v>154</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I101" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3298,6 +3331,7 @@
     <hyperlink ref="B93" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
     <hyperlink ref="B94" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B100" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
+    <hyperlink ref="B101" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="205">
   <si>
     <t>编号</t>
   </si>
@@ -148,490 +148,490 @@
     <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
   </si>
   <si>
+    <t>爬楼梯</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
+  </si>
+  <si>
+    <t>动态规划、斐波那契</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化</t>
+  </si>
+  <si>
+    <t>二叉树的层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>二叉树</t>
+  </si>
+  <si>
+    <t>广度优先搜索/深度优先搜索</t>
+  </si>
+  <si>
+    <t>二叉树的锯齿形层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>列表头插/列表反转/双端队列</t>
+  </si>
+  <si>
+    <t>二叉树的最大深度</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>买卖股票的最佳时机</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②动态规划 ③存储优化</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>字符串</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>两个动态规划</t>
+  </si>
+  <si>
+    <t>二叉树的前序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
+  </si>
+  <si>
+    <t>反转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>递归</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>用栈实现队列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>区域和检索 - 数组不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
+  </si>
+  <si>
+    <t>一维动态规划——数组前缀和</t>
+  </si>
+  <si>
+    <t>二维区域和检索 - 矩阵不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
+  </si>
+  <si>
+    <t>二维动态规划——矩阵前缀和</t>
+  </si>
+  <si>
+    <t>比特位计数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/counting-bits/</t>
+  </si>
+  <si>
+    <t>动态规划、位运算</t>
+  </si>
+  <si>
+    <t>二叉树的直径</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>深度优先搜索</t>
+  </si>
+  <si>
+    <t>子树深度</t>
+  </si>
+  <si>
+    <t>最大二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
+  </si>
+  <si>
+    <t>①递归</t>
+  </si>
+  <si>
+    <t>山羊拉丁文</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/goat-latin/</t>
+  </si>
+  <si>
+    <t>字符串与字符数组效率对比</t>
+  </si>
+  <si>
+    <t>翻转图像</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
+  </si>
+  <si>
+    <t>双指针+异或取反</t>
+  </si>
+  <si>
+    <t>转置矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>二维数组</t>
+  </si>
+  <si>
+    <t>二进制间距</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-gap/</t>
+  </si>
+  <si>
+    <t>进制运算（右移位、与一）</t>
+  </si>
+  <si>
+    <t>找到小镇的法官</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
+  </si>
+  <si>
+    <t>有向图</t>
+  </si>
+  <si>
+    <t>①有向图的入度/出度</t>
+  </si>
+  <si>
+    <t>无官方题解，未计算复杂度</t>
+  </si>
+  <si>
+    <t>最大二叉树 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
+  </si>
+  <si>
+    <t>可以被一步捕获的棋子数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
+  </si>
+  <si>
+    <t>编程练习</t>
+  </si>
+  <si>
+    <t>①编程练习</t>
+  </si>
+  <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>爱生气的书店老板</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
+  </si>
+  <si>
+    <t>滑动窗口</t>
+  </si>
+  <si>
+    <t>长度为X的连续子区间元素之和的最大值</t>
+  </si>
+  <si>
+    <t>设计停车系统</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
+  </si>
+  <si>
+    <t>一和零</t>
+  </si>
+  <si>
+    <t>位1的个数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-1-bits/</t>
+  </si>
+  <si>
+    <t>位运算</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④位运算优化</t>
+  </si>
+  <si>
+    <t>矩阵置零</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/set-matrix-zeroes/</t>
+  </si>
+  <si>
+    <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
+  </si>
+  <si>
+    <t>逆波兰表达式求值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/</t>
+  </si>
+  <si>
+    <t>①逆波兰表达式</t>
+  </si>
+  <si>
+    <t>整数转罗马数字</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/integer-to-roman/</t>
+  </si>
+  <si>
+    <t>①贪心 ②编码表</t>
+  </si>
+  <si>
+    <t>暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>数字转换为十六进制数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
+  </si>
+  <si>
+    <t>①位运算</t>
+  </si>
+  <si>
+    <t>暂缺官方题解 暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>二叉搜索树的最近公共祖先</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
+  </si>
+  <si>
+    <t>①一趟遍历 ②两趟遍历</t>
+  </si>
+  <si>
+    <t>合并二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
+  </si>
+  <si>
+    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
+  </si>
+  <si>
+    <t>电话号码的字母组合</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/</t>
+  </si>
+  <si>
+    <t>①回溯</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
+  </si>
+  <si>
+    <t>①两个变量 ①一个变量</t>
+  </si>
+  <si>
+    <t>颠倒二进制位</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④分治</t>
+  </si>
+  <si>
+    <t>打家劫舍</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/house-robber/</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
+    <t>二叉树的右视图</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索</t>
+  </si>
+  <si>
+    <t>岛屿数量</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>广度优先搜索</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
+  </si>
+  <si>
+    <t>搜索插入位置</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>二分查找</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
+  </si>
+  <si>
+    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①缩减空间</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②二分查找</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
+  </si>
+  <si>
     <t>旋转链表</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/rotate-list/</t>
   </si>
   <si>
-    <t>循环链表</t>
-  </si>
-  <si>
-    <t>爬楼梯</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
-  </si>
-  <si>
-    <t>动态规划、斐波那契</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化</t>
-  </si>
-  <si>
-    <t>二叉树的层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>二叉树</t>
-  </si>
-  <si>
-    <t>广度优先搜索/深度优先搜索</t>
-  </si>
-  <si>
-    <t>二叉树的锯齿形层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>列表头插/列表反转/双端队列</t>
-  </si>
-  <si>
-    <t>二叉树的最大深度</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>买卖股票的最佳时机</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
-  </si>
-  <si>
-    <t>动态规划</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②动态规划 ③存储优化</t>
-  </si>
-  <si>
-    <t>验证回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
-  </si>
-  <si>
-    <t>字符串</t>
-  </si>
-  <si>
-    <t>字符串操作</t>
-  </si>
-  <si>
-    <t>分割回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
-  </si>
-  <si>
-    <t>回溯搜索、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划用于降低判断回文数的复杂度</t>
-  </si>
-  <si>
-    <t>分割回文串 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
-  </si>
-  <si>
-    <t>困难</t>
-  </si>
-  <si>
-    <t>两个动态规划</t>
-  </si>
-  <si>
-    <t>二叉树的前序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
-  </si>
-  <si>
-    <t>反转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
-  </si>
-  <si>
-    <t>用队列实现栈</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
-  </si>
-  <si>
-    <t>队列</t>
-  </si>
-  <si>
-    <t>单/双队列</t>
-  </si>
-  <si>
-    <t>翻转二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
-  </si>
-  <si>
-    <t>递归</t>
-  </si>
-  <si>
-    <t>基本计算器 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式</t>
-  </si>
-  <si>
-    <t>双栈模拟</t>
-  </si>
-  <si>
-    <t>用栈实现队列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
-  </si>
-  <si>
-    <t>栈</t>
-  </si>
-  <si>
-    <t>区域和检索 - 数组不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
-  </si>
-  <si>
-    <t>一维动态规划——数组前缀和</t>
-  </si>
-  <si>
-    <t>二维区域和检索 - 矩阵不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
-  </si>
-  <si>
-    <t>二维动态规划——矩阵前缀和</t>
-  </si>
-  <si>
-    <t>比特位计数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/counting-bits/</t>
-  </si>
-  <si>
-    <t>动态规划、位运算</t>
-  </si>
-  <si>
-    <t>二叉树的直径</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>深度优先搜索</t>
-  </si>
-  <si>
-    <t>子树深度</t>
-  </si>
-  <si>
-    <t>最大二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
-  </si>
-  <si>
-    <t>①递归</t>
-  </si>
-  <si>
-    <t>山羊拉丁文</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/goat-latin/</t>
-  </si>
-  <si>
-    <t>字符串与字符数组效率对比</t>
-  </si>
-  <si>
-    <t>翻转图像</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
-  </si>
-  <si>
-    <t>双指针+异或取反</t>
-  </si>
-  <si>
-    <t>转置矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
-  </si>
-  <si>
-    <t>基础</t>
-  </si>
-  <si>
-    <t>二维数组</t>
-  </si>
-  <si>
-    <t>二进制间距</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-gap/</t>
-  </si>
-  <si>
-    <t>进制运算（右移位、与一）</t>
-  </si>
-  <si>
-    <t>找到小镇的法官</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
-  </si>
-  <si>
-    <t>有向图</t>
-  </si>
-  <si>
-    <t>①有向图的入度/出度</t>
-  </si>
-  <si>
-    <t>无官方题解，未计算复杂度</t>
-  </si>
-  <si>
-    <t>最大二叉树 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
-  </si>
-  <si>
-    <t>可以被一步捕获的棋子数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
-  </si>
-  <si>
-    <t>编程练习</t>
-  </si>
-  <si>
-    <t>①编程练习</t>
-  </si>
-  <si>
-    <t>删除字符串中的所有相邻重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>数据结构</t>
-  </si>
-  <si>
-    <t>爱生气的书店老板</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
-  </si>
-  <si>
-    <t>滑动窗口</t>
-  </si>
-  <si>
-    <t>长度为X的连续子区间元素之和的最大值</t>
-  </si>
-  <si>
-    <t>设计停车系统</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
-  </si>
-  <si>
-    <t>一和零</t>
-  </si>
-  <si>
-    <t>位1的个数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/number-of-1-bits/</t>
-  </si>
-  <si>
-    <t>位运算</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>①②③位运算 ④位运算优化</t>
-  </si>
-  <si>
-    <t>矩阵置零</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/set-matrix-zeroes/</t>
-  </si>
-  <si>
-    <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
-  </si>
-  <si>
-    <t>逆波兰表达式求值</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/</t>
-  </si>
-  <si>
-    <t>①逆波兰表达式</t>
-  </si>
-  <si>
-    <t>整数转罗马数字</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/integer-to-roman/</t>
-  </si>
-  <si>
-    <t>①贪心 ②编码表</t>
-  </si>
-  <si>
-    <t>暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>数字转换为十六进制数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
-  </si>
-  <si>
-    <t>①位运算</t>
-  </si>
-  <si>
-    <t>暂缺官方题解 暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>二叉搜索树的最近公共祖先</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
-  </si>
-  <si>
-    <t>①一趟遍历 ②两趟遍历</t>
-  </si>
-  <si>
-    <t>合并二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
-  </si>
-  <si>
-    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
-  </si>
-  <si>
-    <t>电话号码的字母组合</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/</t>
-  </si>
-  <si>
-    <t>①回溯</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
-  </si>
-  <si>
-    <t>①两个变量 ①一个变量</t>
-  </si>
-  <si>
-    <t>颠倒二进制位</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>①②③位运算 ④分治</t>
-  </si>
-  <si>
-    <t>打家劫舍</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/house-robber/</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
-  </si>
-  <si>
-    <t>二叉树的右视图</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索</t>
-  </si>
-  <si>
-    <t>岛屿数量</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
-  </si>
-  <si>
-    <t>广度优先搜索</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
-  </si>
-  <si>
-    <t>搜索插入位置</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
-  </si>
-  <si>
-    <t>二分查找</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
-  </si>
-  <si>
-    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
-  </si>
-  <si>
-    <t>①缩减空间</t>
-  </si>
-  <si>
-    <t>寻找旋转排序数组中的最小值</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②二分查找</t>
-  </si>
-  <si>
-    <t>寻找旋转排序数组中的最小值 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
+    <t>①闭合成环 ②快慢指针</t>
   </si>
 </sst>
 </file>
@@ -1701,7 +1701,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1955,47 +1955,21 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="1">
-        <v>61</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="11" s="1" customFormat="1" spans="1:9">
       <c r="A11" s="1">
         <v>70</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
@@ -2004,7 +1978,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I11" s="11"/>
     </row>
@@ -2013,16 +1987,16 @@
         <v>102</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
@@ -2031,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2039,16 +2013,16 @@
         <v>103</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
@@ -2057,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
@@ -2065,16 +2039,16 @@
         <v>104</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
@@ -2083,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
@@ -2091,16 +2065,16 @@
         <v>121</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>13</v>
@@ -2109,7 +2083,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
@@ -2117,16 +2091,16 @@
         <v>125</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>13</v>
@@ -2135,7 +2109,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:8">
@@ -2143,16 +2117,16 @@
         <v>131</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -2161,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
@@ -2169,16 +2143,16 @@
         <v>132</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -2187,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:7">
@@ -2195,16 +2169,16 @@
         <v>144</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
@@ -2218,10 +2192,10 @@
         <v>206</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>18</v>
@@ -2241,16 +2215,16 @@
         <v>225</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>13</v>
@@ -2259,7 +2233,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:8">
@@ -2267,16 +2241,16 @@
         <v>226</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>13</v>
@@ -2285,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:8">
@@ -2293,16 +2267,16 @@
         <v>227</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
@@ -2311,7 +2285,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:8">
@@ -2319,16 +2293,16 @@
         <v>232</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>13</v>
@@ -2337,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
@@ -2345,16 +2319,16 @@
         <v>303</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
@@ -2363,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I25" s="11"/>
     </row>
@@ -2372,16 +2346,16 @@
         <v>304</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
@@ -2390,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I26" s="11"/>
     </row>
@@ -2399,16 +2373,16 @@
         <v>338</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2417,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I27" s="11"/>
     </row>
@@ -2426,16 +2400,16 @@
         <v>543</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -2444,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I28" s="11"/>
     </row>
@@ -2453,16 +2427,16 @@
         <v>654</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
@@ -2471,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
@@ -2479,16 +2453,16 @@
         <v>824</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -2497,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I30" s="11"/>
     </row>
@@ -2506,10 +2480,10 @@
         <v>832</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>18</v>
@@ -2524,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
@@ -2532,16 +2506,16 @@
         <v>867</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
@@ -2550,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2558,16 +2532,16 @@
         <v>868</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
@@ -2576,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I33" s="11"/>
     </row>
@@ -2585,16 +2559,16 @@
         <v>997</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
@@ -2603,10 +2577,10 @@
         <v>14</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:9">
@@ -2614,16 +2588,16 @@
         <v>998</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>13</v>
@@ -2632,10 +2606,10 @@
         <v>14</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:8">
@@ -2643,16 +2617,16 @@
         <v>999</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>13</v>
@@ -2661,7 +2635,7 @@
         <v>14</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:8">
@@ -2669,16 +2643,16 @@
         <v>1047</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>13</v>
@@ -2687,7 +2661,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
@@ -2695,16 +2669,16 @@
         <v>1052</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>13</v>
@@ -2713,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I38" s="11"/>
     </row>
@@ -2722,16 +2696,16 @@
         <v>1603</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>13</v>
@@ -2740,7 +2714,7 @@
         <v>14</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I39" s="11"/>
     </row>
@@ -2749,7 +2723,7 @@
         <v>474</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:9">
@@ -2757,25 +2731,25 @@
         <v>191</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I54" s="12"/>
     </row>
@@ -2784,25 +2758,25 @@
         <v>73</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I55" s="12"/>
     </row>
@@ -2811,25 +2785,25 @@
         <v>150</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I56" s="12"/>
     </row>
@@ -2838,16 +2812,16 @@
         <v>12</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>13</v>
@@ -2856,10 +2830,10 @@
         <v>14</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:9">
@@ -2867,16 +2841,16 @@
         <v>405</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>13</v>
@@ -2885,10 +2859,10 @@
         <v>14</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:9">
@@ -2896,16 +2870,16 @@
         <v>235</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>13</v>
@@ -2914,10 +2888,10 @@
         <v>14</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:9">
@@ -2925,16 +2899,16 @@
         <v>617</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>13</v>
@@ -2943,10 +2917,10 @@
         <v>14</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:9">
@@ -2954,10 +2928,10 @@
         <v>17</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>11</v>
@@ -2972,10 +2946,10 @@
         <v>14</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" spans="1:9">
@@ -2983,10 +2957,10 @@
         <v>82</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>11</v>
@@ -3007,10 +2981,10 @@
         <v>83</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>18</v>
@@ -3025,7 +2999,7 @@
         <v>14</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I74" s="13"/>
     </row>
@@ -3034,25 +3008,25 @@
         <v>190</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I80" s="17"/>
     </row>
@@ -3061,25 +3035,25 @@
         <v>198</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I81" s="17"/>
     </row>
@@ -3088,25 +3062,25 @@
         <v>199</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I82" s="17"/>
     </row>
@@ -3115,25 +3089,25 @@
         <v>200</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I83" s="17"/>
     </row>
@@ -3142,22 +3116,22 @@
         <v>35</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I88" s="17"/>
     </row>
@@ -3166,25 +3140,25 @@
         <v>74</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E93" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H93" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="I93" s="18"/>
     </row>
@@ -3193,25 +3167,25 @@
         <v>240</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I94" s="18"/>
     </row>
@@ -3220,25 +3194,25 @@
         <v>153</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I100" s="19"/>
     </row>
@@ -3247,27 +3221,54 @@
         <v>154</v>
       </c>
       <c r="B101" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I101" s="19"/>
+    </row>
+    <row r="102" s="6" customFormat="1" spans="1:9">
+      <c r="A102" s="6">
+        <v>61</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="D102" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="I101" s="19"/>
+      <c r="I102" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3295,7 +3296,7 @@
     <hyperlink ref="B17" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B16" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
     <hyperlink ref="B37" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
-    <hyperlink ref="B10" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B102" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
     <hyperlink ref="B23" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
     <hyperlink ref="B22" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
     <hyperlink ref="B21" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="209">
   <si>
     <t>编号</t>
   </si>
@@ -632,6 +632,18 @@
   </si>
   <si>
     <t>①闭合成环 ②快慢指针</t>
+  </si>
+  <si>
+    <t>n22</t>
+  </si>
+  <si>
+    <t>链表中倒数第k个节点</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/</t>
+  </si>
+  <si>
+    <t>①两趟遍历 ②快慢指针</t>
   </si>
 </sst>
 </file>
@@ -1701,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3269,6 +3281,33 @@
         <v>204</v>
       </c>
       <c r="I102" s="19"/>
+    </row>
+    <row r="103" s="6" customFormat="1" spans="1:9">
+      <c r="A103" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="I103" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3333,6 +3372,7 @@
     <hyperlink ref="B94" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B100" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B101" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
+    <hyperlink ref="B103" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="213">
   <si>
     <t>编号</t>
   </si>
@@ -644,6 +644,18 @@
   </si>
   <si>
     <t>①两趟遍历 ②快慢指针</t>
+  </si>
+  <si>
+    <t>盛最多水的容器</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/container-with-most-water/</t>
+  </si>
+  <si>
+    <t>贪心、双指针</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②双指针</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3308,6 +3320,33 @@
         <v>208</v>
       </c>
       <c r="I103" s="19"/>
+    </row>
+    <row r="104" s="6" customFormat="1" spans="1:9">
+      <c r="A104" s="6">
+        <v>11</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I104" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
@@ -3373,6 +3412,7 @@
     <hyperlink ref="B100" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B101" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B103" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
+    <hyperlink ref="B104" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -46,396 +46,396 @@
     <t>备注</t>
   </si>
   <si>
+    <t>设计停车系统</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>编程练习</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>①编程练习</t>
+  </si>
+  <si>
+    <t>爱生气的书店老板</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>滑动窗口</t>
+  </si>
+  <si>
+    <t>长度为X的连续子区间元素之和的最大值</t>
+  </si>
+  <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>可以被一步捕获的棋子数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
+  </si>
+  <si>
+    <t>最大二叉树 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
+  </si>
+  <si>
+    <t>二叉树</t>
+  </si>
+  <si>
+    <t>①递归</t>
+  </si>
+  <si>
+    <t>无官方题解，未计算复杂度</t>
+  </si>
+  <si>
+    <t>找到小镇的法官</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
+  </si>
+  <si>
+    <t>有向图</t>
+  </si>
+  <si>
+    <t>①有向图的入度/出度</t>
+  </si>
+  <si>
+    <t>二进制间距</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-gap/</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>进制运算（右移位、与一）</t>
+  </si>
+  <si>
+    <t>转置矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
+  </si>
+  <si>
+    <t>二维数组</t>
+  </si>
+  <si>
+    <t>翻转图像</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
+  </si>
+  <si>
+    <t>双指针</t>
+  </si>
+  <si>
+    <t>双指针+异或取反</t>
+  </si>
+  <si>
+    <t>山羊拉丁文</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/goat-latin/</t>
+  </si>
+  <si>
+    <t>字符串</t>
+  </si>
+  <si>
+    <t>字符串与字符数组效率对比</t>
+  </si>
+  <si>
+    <t>最大二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
+  </si>
+  <si>
+    <t>二叉树的直径</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>深度优先搜索</t>
+  </si>
+  <si>
+    <t>子树深度</t>
+  </si>
+  <si>
+    <t>比特位计数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/counting-bits/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>动态规划、位运算</t>
+  </si>
+  <si>
+    <t>二维区域和检索 - 矩阵不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
+  </si>
+  <si>
+    <t>二维动态规划——矩阵前缀和</t>
+  </si>
+  <si>
+    <t>区域和检索 - 数组不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
+  </si>
+  <si>
+    <t>一维动态规划——数组前缀和</t>
+  </si>
+  <si>
+    <t>用栈实现队列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>递归</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
+  </si>
+  <si>
+    <t>反转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
+  </si>
+  <si>
+    <t>链表</t>
+  </si>
+  <si>
+    <t>二叉树的前序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>两个动态规划</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
+  </si>
+  <si>
+    <t>买卖股票的最佳时机</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②动态规划 ③存储优化</t>
+  </si>
+  <si>
+    <t>二叉树的最大深度</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>广度优先搜索/深度优先搜索</t>
+  </si>
+  <si>
+    <t>二叉树的锯齿形层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>列表头插/列表反转/双端队列</t>
+  </si>
+  <si>
+    <t>二叉树的层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>爬楼梯</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
+  </si>
+  <si>
+    <t>动态规划、斐波那契</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化</t>
+  </si>
+  <si>
+    <t>螺旋矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix-ii/</t>
+  </si>
+  <si>
+    <t>数组</t>
+  </si>
+  <si>
+    <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
+  </si>
+  <si>
+    <t>螺旋矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix/</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>1.判断边界 2.避免重复</t>
+  </si>
+  <si>
+    <t>连续子数组最大和</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
+  </si>
+  <si>
+    <t>动态规划、分治、线段树</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
+  </si>
+  <si>
+    <t>全排列 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations-ii/</t>
+  </si>
+  <si>
+    <t>回溯</t>
+  </si>
+  <si>
+    <t>排列去重</t>
+  </si>
+  <si>
+    <t>全排列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations/</t>
+  </si>
+  <si>
+    <t>简单排列</t>
+  </si>
+  <si>
+    <t>移除元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-element/</t>
+  </si>
+  <si>
+    <t>交换or前移</t>
+  </si>
+  <si>
+    <t>删除排序数组中的重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/</t>
+  </si>
+  <si>
+    <t>快慢指针</t>
+  </si>
+  <si>
     <t>两数相加</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/add-two-numbers/</t>
   </si>
   <si>
-    <t>中等</t>
-  </si>
-  <si>
-    <t>链表</t>
-  </si>
-  <si>
-    <t>通过</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>①链表操作</t>
   </si>
   <si>
-    <t>删除排序数组中的重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/</t>
-  </si>
-  <si>
-    <t>简单</t>
-  </si>
-  <si>
-    <t>双指针</t>
-  </si>
-  <si>
-    <t>快慢指针</t>
-  </si>
-  <si>
-    <t>移除元素</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-element/</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>交换or前移</t>
-  </si>
-  <si>
-    <t>全排列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/permutations/</t>
-  </si>
-  <si>
-    <t>回溯</t>
-  </si>
-  <si>
-    <t>简单排列</t>
-  </si>
-  <si>
-    <t>全排列 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/permutations-ii/</t>
-  </si>
-  <si>
-    <t>排列去重</t>
-  </si>
-  <si>
-    <t>连续子数组最大和</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
-  </si>
-  <si>
-    <t>动态规划、分治、线段树</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
-  </si>
-  <si>
-    <t>螺旋矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/spiral-matrix/</t>
-  </si>
-  <si>
-    <t>数组</t>
-  </si>
-  <si>
-    <t>1.判断边界 2.避免重复</t>
-  </si>
-  <si>
-    <t>螺旋矩阵 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/spiral-matrix-ii/</t>
-  </si>
-  <si>
-    <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
-  </si>
-  <si>
-    <t>爬楼梯</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
-  </si>
-  <si>
-    <t>动态规划、斐波那契</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化</t>
-  </si>
-  <si>
-    <t>二叉树的层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>二叉树</t>
-  </si>
-  <si>
-    <t>广度优先搜索/深度优先搜索</t>
-  </si>
-  <si>
-    <t>二叉树的锯齿形层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>列表头插/列表反转/双端队列</t>
-  </si>
-  <si>
-    <t>二叉树的最大深度</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>买卖股票的最佳时机</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
-  </si>
-  <si>
-    <t>动态规划</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②动态规划 ③存储优化</t>
-  </si>
-  <si>
-    <t>验证回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
-  </si>
-  <si>
-    <t>字符串</t>
-  </si>
-  <si>
-    <t>字符串操作</t>
-  </si>
-  <si>
-    <t>分割回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
-  </si>
-  <si>
-    <t>回溯搜索、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划用于降低判断回文数的复杂度</t>
-  </si>
-  <si>
-    <t>分割回文串 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
-  </si>
-  <si>
-    <t>困难</t>
-  </si>
-  <si>
-    <t>两个动态规划</t>
-  </si>
-  <si>
-    <t>二叉树的前序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
-  </si>
-  <si>
-    <t>反转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
-  </si>
-  <si>
-    <t>用队列实现栈</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
-  </si>
-  <si>
-    <t>队列</t>
-  </si>
-  <si>
-    <t>单/双队列</t>
-  </si>
-  <si>
-    <t>翻转二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
-  </si>
-  <si>
-    <t>递归</t>
-  </si>
-  <si>
-    <t>基本计算器 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式</t>
-  </si>
-  <si>
-    <t>双栈模拟</t>
-  </si>
-  <si>
-    <t>用栈实现队列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
-  </si>
-  <si>
-    <t>栈</t>
-  </si>
-  <si>
-    <t>区域和检索 - 数组不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
-  </si>
-  <si>
-    <t>一维动态规划——数组前缀和</t>
-  </si>
-  <si>
-    <t>二维区域和检索 - 矩阵不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
-  </si>
-  <si>
-    <t>二维动态规划——矩阵前缀和</t>
-  </si>
-  <si>
-    <t>比特位计数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/counting-bits/</t>
-  </si>
-  <si>
-    <t>动态规划、位运算</t>
-  </si>
-  <si>
-    <t>二叉树的直径</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>深度优先搜索</t>
-  </si>
-  <si>
-    <t>子树深度</t>
-  </si>
-  <si>
-    <t>最大二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
-  </si>
-  <si>
-    <t>①递归</t>
-  </si>
-  <si>
-    <t>山羊拉丁文</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/goat-latin/</t>
-  </si>
-  <si>
-    <t>字符串与字符数组效率对比</t>
-  </si>
-  <si>
-    <t>翻转图像</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
-  </si>
-  <si>
-    <t>双指针+异或取反</t>
-  </si>
-  <si>
-    <t>转置矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
-  </si>
-  <si>
-    <t>基础</t>
-  </si>
-  <si>
-    <t>二维数组</t>
-  </si>
-  <si>
-    <t>二进制间距</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-gap/</t>
-  </si>
-  <si>
-    <t>进制运算（右移位、与一）</t>
-  </si>
-  <si>
-    <t>找到小镇的法官</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
-  </si>
-  <si>
-    <t>有向图</t>
-  </si>
-  <si>
-    <t>①有向图的入度/出度</t>
-  </si>
-  <si>
-    <t>无官方题解，未计算复杂度</t>
-  </si>
-  <si>
-    <t>最大二叉树 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
-  </si>
-  <si>
-    <t>可以被一步捕获的棋子数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
-  </si>
-  <si>
-    <t>编程练习</t>
-  </si>
-  <si>
-    <t>①编程练习</t>
-  </si>
-  <si>
-    <t>删除字符串中的所有相邻重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>数据结构</t>
-  </si>
-  <si>
-    <t>爱生气的书店老板</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
-  </si>
-  <si>
-    <t>滑动窗口</t>
-  </si>
-  <si>
-    <t>长度为X的连续子区间元素之和的最大值</t>
-  </si>
-  <si>
-    <t>设计停车系统</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
-  </si>
-  <si>
     <t>一和零</t>
   </si>
   <si>
@@ -472,6 +472,183 @@
     <t>①逆波兰表达式</t>
   </si>
   <si>
+    <t>数字转换为十六进制数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
+  </si>
+  <si>
+    <t>①位运算</t>
+  </si>
+  <si>
+    <t>暂缺官方题解 暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>二叉搜索树的最近公共祖先</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
+  </si>
+  <si>
+    <t>①一趟遍历 ②两趟遍历</t>
+  </si>
+  <si>
+    <t>暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>合并二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
+  </si>
+  <si>
+    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
+  </si>
+  <si>
+    <t>电话号码的字母组合</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/</t>
+  </si>
+  <si>
+    <t>①回溯</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
+  </si>
+  <si>
+    <t>①两个变量 ①一个变量</t>
+  </si>
+  <si>
+    <t>颠倒二进制位</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④分治</t>
+  </si>
+  <si>
+    <t>打家劫舍</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/house-robber/</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
+    <t>二叉树的右视图</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索</t>
+  </si>
+  <si>
+    <t>岛屿数量</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>广度优先搜索</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
+  </si>
+  <si>
+    <t>搜索插入位置</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>二分查找</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
+  </si>
+  <si>
+    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①缩减空间</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②二分查找</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
+  </si>
+  <si>
+    <t>旋转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>①闭合成环 ②快慢指针</t>
+  </si>
+  <si>
+    <t>n22</t>
+  </si>
+  <si>
+    <t>链表中倒数第k个节点</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/</t>
+  </si>
+  <si>
+    <t>①两趟遍历 ②快慢指针</t>
+  </si>
+  <si>
+    <t>盛最多水的容器</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/container-with-most-water/</t>
+  </si>
+  <si>
+    <t>贪心、双指针</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②双指针</t>
+  </si>
+  <si>
     <t>整数转罗马数字</t>
   </si>
   <si>
@@ -479,183 +656,6 @@
   </si>
   <si>
     <t>①贪心 ②编码表</t>
-  </si>
-  <si>
-    <t>暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>数字转换为十六进制数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
-  </si>
-  <si>
-    <t>①位运算</t>
-  </si>
-  <si>
-    <t>暂缺官方题解 暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>二叉搜索树的最近公共祖先</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
-  </si>
-  <si>
-    <t>①一趟遍历 ②两趟遍历</t>
-  </si>
-  <si>
-    <t>合并二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
-  </si>
-  <si>
-    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
-  </si>
-  <si>
-    <t>电话号码的字母组合</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/</t>
-  </si>
-  <si>
-    <t>①回溯</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
-  </si>
-  <si>
-    <t>①两个变量 ①一个变量</t>
-  </si>
-  <si>
-    <t>颠倒二进制位</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>①②③位运算 ④分治</t>
-  </si>
-  <si>
-    <t>打家劫舍</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/house-robber/</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
-  </si>
-  <si>
-    <t>二叉树的右视图</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索</t>
-  </si>
-  <si>
-    <t>岛屿数量</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
-  </si>
-  <si>
-    <t>广度优先搜索</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
-  </si>
-  <si>
-    <t>搜索插入位置</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
-  </si>
-  <si>
-    <t>二分查找</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
-  </si>
-  <si>
-    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
-  </si>
-  <si>
-    <t>①缩减空间</t>
-  </si>
-  <si>
-    <t>寻找旋转排序数组中的最小值</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②二分查找</t>
-  </si>
-  <si>
-    <t>寻找旋转排序数组中的最小值 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
-  </si>
-  <si>
-    <t>旋转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/rotate-list/</t>
-  </si>
-  <si>
-    <t>①闭合成环 ②快慢指针</t>
-  </si>
-  <si>
-    <t>n22</t>
-  </si>
-  <si>
-    <t>链表中倒数第k个节点</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/</t>
-  </si>
-  <si>
-    <t>①两趟遍历 ②快慢指针</t>
-  </si>
-  <si>
-    <t>盛最多水的容器</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/container-with-most-water/</t>
-  </si>
-  <si>
-    <t>贪心、双指针</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②双指针</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1341,9 +1341,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1351,6 +1357,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1725,7 +1734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1771,9 +1780,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
-        <v>2</v>
+        <v>1603</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
@@ -1796,10 +1805,11 @@
       <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
-        <v>26</v>
+        <v>1052</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>16</v>
@@ -1817,15 +1827,16 @@
         <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
-        <v>27</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>21</v>
@@ -1834,24 +1845,25 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
+      <c r="G4" s="1">
+        <v>2</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
-        <v>46</v>
+        <v>999</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>25</v>
@@ -1863,47 +1875,51 @@
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>998</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>47</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
-        <v>53</v>
+        <v>997</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>32</v>
@@ -1912,7 +1928,7 @@
         <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>34</v>
@@ -1926,10 +1942,13 @@
       <c r="H7" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="I7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:9">
       <c r="A8" s="1">
-        <v>54</v>
+        <v>868</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>36</v>
@@ -1946,18 +1965,19 @@
       <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
+      <c r="G8" s="1">
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
       <c r="A9" s="1">
-        <v>59</v>
-      </c>
-      <c r="B9" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1972,81 +1992,108 @@
       <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>14</v>
+      <c r="G9" s="1">
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>832</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="10"/>
+    </row>
     <row r="11" s="1" customFormat="1" spans="1:9">
       <c r="A11" s="1">
-        <v>70</v>
+        <v>824</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>14</v>
+      <c r="G11" s="1">
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="11"/>
+        <v>50</v>
+      </c>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="1">
-        <v>102</v>
+        <v>654</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
-        <v>103</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>543</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
@@ -2055,24 +2102,25 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
+        <v>56</v>
+      </c>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:9">
       <c r="A14" s="1">
-        <v>104</v>
+        <v>338</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
@@ -2081,76 +2129,79 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+        <v>60</v>
+      </c>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="1">
-        <v>121</v>
+        <v>304</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>14</v>
+      <c r="G15" s="1">
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:9">
+      <c r="A16" s="1">
+        <v>303</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="A16" s="1">
-        <v>125</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="F16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>63</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="1">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -2159,24 +2210,24 @@
         <v>2</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="1">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -2185,122 +2236,124 @@
         <v>2</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="1">
-        <v>144</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>72</v>
+        <v>226</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:8">
       <c r="A20" s="1">
-        <v>206</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>74</v>
+        <v>225</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>14</v>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:8">
       <c r="A21" s="1">
-        <v>225</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>76</v>
+        <v>206</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="1">
-        <v>2</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="10"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:8">
       <c r="A22" s="1">
-        <v>226</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>80</v>
+        <v>144</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="1">
-        <v>2</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="10"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:8">
       <c r="A23" s="1">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
@@ -2309,24 +2362,24 @@
         <v>2</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:8">
       <c r="A24" s="1">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>13</v>
@@ -2335,78 +2388,78 @@
         <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
-        <v>303</v>
+        <v>125</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
-        <v>304</v>
+        <v>121</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="1">
-        <v>1</v>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I26" s="11"/>
+        <v>98</v>
+      </c>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
       <c r="A27" s="1">
-        <v>338</v>
+        <v>104</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2415,25 +2468,25 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I27" s="11"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:9">
+        <v>101</v>
+      </c>
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:8">
       <c r="A28" s="1">
-        <v>543</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -2442,241 +2495,236 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I28" s="11"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
-        <v>654</v>
+        <v>102</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>14</v>
+      <c r="G29" s="1">
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
       <c r="A30" s="1">
-        <v>824</v>
+        <v>70</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="1">
-        <v>1</v>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I30" s="11"/>
+        <v>110</v>
+      </c>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1">
-        <v>832</v>
+        <v>59</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
       <c r="A32" s="1">
-        <v>867</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>112</v>
+        <v>54</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
+      <c r="G32" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1">
-        <v>868</v>
+        <v>53</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
+      <c r="G33" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I33" s="11"/>
+        <v>122</v>
+      </c>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1">
-        <v>997</v>
+        <v>47</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:9">
+        <v>126</v>
+      </c>
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:8">
       <c r="A35" s="1">
-        <v>998</v>
+        <v>46</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:9">
+      <c r="A36" s="1">
+        <v>27</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:8">
-      <c r="A36" s="1">
-        <v>999</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:8">
+        <v>132</v>
+      </c>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:9">
       <c r="A37" s="1">
-        <v>1047</v>
+        <v>26</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>13</v>
@@ -2685,62 +2733,35 @@
         <v>2</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:9">
+        <v>135</v>
+      </c>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:8">
       <c r="A38" s="1">
-        <v>1052</v>
+        <v>2</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="1">
-        <v>1</v>
+      <c r="G38" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I38" s="11"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:9">
-      <c r="A39" s="1">
-        <v>1603</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I39" s="11"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1">
@@ -2754,14 +2775,14 @@
       <c r="A54" s="2">
         <v>191</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>142</v>
@@ -2775,23 +2796,23 @@
       <c r="H54" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I54" s="12"/>
+      <c r="I54" s="15"/>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:9">
       <c r="A55" s="2">
         <v>73</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>13</v>
@@ -2802,23 +2823,23 @@
       <c r="H55" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I55" s="12"/>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:9">
       <c r="A56" s="2">
         <v>150</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="11" t="s">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>13</v>
@@ -2829,49 +2850,20 @@
       <c r="H56" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I56" s="12"/>
-    </row>
-    <row r="57" s="3" customFormat="1" spans="1:9">
-      <c r="A57" s="3">
-        <v>12</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>154</v>
-      </c>
+      <c r="I56" s="15"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:9">
       <c r="A58" s="3">
         <v>405</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>155</v>
+      <c r="B58" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>142</v>
@@ -2883,27 +2875,27 @@
         <v>14</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>158</v>
+        <v>153</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:9">
       <c r="A59" s="3">
         <v>235</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>159</v>
+      <c r="B59" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>13</v>
@@ -2912,27 +2904,27 @@
         <v>14</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:9">
       <c r="A60" s="3">
         <v>617</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>162</v>
+      <c r="B60" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>13</v>
@@ -2941,27 +2933,27 @@
         <v>14</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>154</v>
+        <v>161</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:9">
       <c r="A68" s="3">
         <v>17</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>165</v>
+      <c r="B68" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>13</v>
@@ -2970,27 +2962,27 @@
         <v>14</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>154</v>
+        <v>164</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" spans="1:9">
       <c r="A73" s="3">
         <v>82</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>168</v>
+      <c r="B73" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>13</v>
@@ -2998,23 +2990,23 @@
       <c r="G73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I73" s="13"/>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" s="3" customFormat="1" spans="1:9">
       <c r="A74" s="3">
         <v>83</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>170</v>
+      <c r="B74" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>13</v>
@@ -3023,22 +3015,22 @@
         <v>14</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I74" s="13"/>
+        <v>169</v>
+      </c>
+      <c r="I74" s="16"/>
     </row>
     <row r="80" s="4" customFormat="1" spans="1:9">
       <c r="A80" s="4">
         <v>190</v>
       </c>
-      <c r="B80" s="14" t="s">
-        <v>173</v>
+      <c r="B80" s="17" t="s">
+        <v>170</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>142</v>
@@ -3047,355 +3039,384 @@
         <v>13</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I80" s="17"/>
+        <v>173</v>
+      </c>
+      <c r="I80" s="20"/>
     </row>
     <row r="81" s="4" customFormat="1" spans="1:9">
       <c r="A81" s="4">
         <v>198</v>
       </c>
-      <c r="B81" s="14" t="s">
-        <v>177</v>
+      <c r="B81" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I81" s="17"/>
+        <v>176</v>
+      </c>
+      <c r="I81" s="20"/>
     </row>
     <row r="82" s="4" customFormat="1" spans="1:9">
       <c r="A82" s="4">
         <v>199</v>
       </c>
-      <c r="B82" s="14" t="s">
-        <v>180</v>
+      <c r="B82" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I82" s="17"/>
+        <v>179</v>
+      </c>
+      <c r="I82" s="20"/>
     </row>
     <row r="83" s="4" customFormat="1" spans="1:9">
       <c r="A83" s="4">
         <v>200</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="I83" s="17"/>
+      <c r="I83" s="20"/>
     </row>
     <row r="88" s="4" customFormat="1" spans="1:9">
       <c r="A88" s="4">
         <v>35</v>
       </c>
-      <c r="B88" s="14" t="s">
-        <v>187</v>
+      <c r="B88" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I88" s="17"/>
+        <v>172</v>
+      </c>
+      <c r="I88" s="20"/>
     </row>
     <row r="93" s="5" customFormat="1" spans="1:9">
       <c r="A93" s="5">
         <v>74</v>
       </c>
-      <c r="B93" s="15" t="s">
-        <v>190</v>
+      <c r="B93" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E93" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H93" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="I93" s="18"/>
+      <c r="I93" s="21"/>
     </row>
     <row r="94" s="5" customFormat="1" spans="1:9">
       <c r="A94" s="5">
         <v>240</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>193</v>
+      <c r="B94" s="18" t="s">
+        <v>190</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I94" s="18"/>
+        <v>192</v>
+      </c>
+      <c r="I94" s="21"/>
     </row>
     <row r="100" s="6" customFormat="1" spans="1:9">
       <c r="A100" s="6">
         <v>153</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B100" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="I100" s="19"/>
+      <c r="I100" s="22"/>
     </row>
     <row r="101" s="6" customFormat="1" spans="1:9">
       <c r="A101" s="6">
         <v>154</v>
       </c>
-      <c r="B101" s="16" t="s">
-        <v>200</v>
+      <c r="B101" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="I101" s="19"/>
+        <v>196</v>
+      </c>
+      <c r="I101" s="22"/>
     </row>
     <row r="102" s="6" customFormat="1" spans="1:9">
       <c r="A102" s="6">
         <v>61</v>
       </c>
-      <c r="B102" s="16" t="s">
-        <v>202</v>
+      <c r="B102" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="I102" s="19"/>
+        <v>201</v>
+      </c>
+      <c r="I102" s="22"/>
     </row>
     <row r="103" s="6" customFormat="1" spans="1:9">
       <c r="A103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H103" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B103" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I103" s="19"/>
+      <c r="I103" s="22"/>
     </row>
     <row r="104" s="6" customFormat="1" spans="1:9">
       <c r="A104" s="6">
         <v>11</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="I104" s="22"/>
+    </row>
+    <row r="105" s="6" customFormat="1" spans="1:9">
+      <c r="A105" s="6">
+        <v>12</v>
+      </c>
+      <c r="B105" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="D104" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="6" t="s">
+      <c r="C105" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H104" s="6" t="s">
+      <c r="D105" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H105" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="I104" s="19"/>
+      <c r="I105" s="22" t="s">
+        <v>158</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I39">
-    <sortState ref="A1:I39">
-      <sortCondition ref="A1"/>
+    <sortState ref="A2:I39">
+      <sortCondition ref="A1" descending="1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B38" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B31" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B30" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C28" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C32" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B33" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B25" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B26" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B12" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="B13" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="C13" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B14" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B27" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
-    <hyperlink ref="B3" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B24" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B17" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B16" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B37" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B3" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B10" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B11" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C13" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C9" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B8" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B16" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B15" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B29" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B28" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="C28" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B14" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B37" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
+    <hyperlink ref="B17" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B24" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B25" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B4" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B102" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B23" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B22" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B21" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
-    <hyperlink ref="B8" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
-    <hyperlink ref="B5" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
-    <hyperlink ref="B6" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
-    <hyperlink ref="B4" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
-    <hyperlink ref="B2" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
-    <hyperlink ref="B9" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
-    <hyperlink ref="B7" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
-    <hyperlink ref="B15" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B20" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
-    <hyperlink ref="B19" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B39" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B36" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B29" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B35" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B18" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B19" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B20" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B32" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
+    <hyperlink ref="B35" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
+    <hyperlink ref="B34" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
+    <hyperlink ref="B36" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
+    <hyperlink ref="B38" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
+    <hyperlink ref="B31" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
+    <hyperlink ref="B33" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
+    <hyperlink ref="B26" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="B21" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B22" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="B2" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B5" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B12" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B6" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B54" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
     <hyperlink ref="B55" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B56" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
-    <hyperlink ref="B57" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
+    <hyperlink ref="B105" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
     <hyperlink ref="B58" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
     <hyperlink ref="B59" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
     <hyperlink ref="B60" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$64</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -46,69 +46,111 @@
     <t>备注</t>
   </si>
   <si>
+    <t>盛最多水的容器</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/container-with-most-water/</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>贪心、双指针</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②双指针</t>
+  </si>
+  <si>
+    <t>整数转罗马数字</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/integer-to-roman/</t>
+  </si>
+  <si>
+    <t>编程练习</t>
+  </si>
+  <si>
+    <t>①贪心 ②编码表</t>
+  </si>
+  <si>
+    <t>暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>罗马数字转整数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/roman-to-integer/</t>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>①编程练习</t>
+  </si>
+  <si>
+    <t>旋转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/rotate-list/</t>
+  </si>
+  <si>
+    <t>链表</t>
+  </si>
+  <si>
+    <t>①闭合成环 ②快慢指针</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t>二分查找</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②二分查找</t>
+  </si>
+  <si>
+    <t>寻找旋转排序数组中的最小值 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>n22</t>
+  </si>
+  <si>
+    <t>链表中倒数第k个节点</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/</t>
+  </si>
+  <si>
+    <t>①两趟遍历 ②快慢指针</t>
+  </si>
+  <si>
     <t>两数相加</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/add-two-numbers/</t>
   </si>
   <si>
-    <t>中等</t>
-  </si>
-  <si>
-    <t>链表</t>
-  </si>
-  <si>
-    <t>通过</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>①链表操作</t>
   </si>
   <si>
-    <t>盛最多水的容器</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/container-with-most-water/</t>
-  </si>
-  <si>
-    <t>贪心、双指针</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②双指针</t>
-  </si>
-  <si>
-    <t>整数转罗马数字</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/integer-to-roman/</t>
-  </si>
-  <si>
-    <t>编程练习</t>
-  </si>
-  <si>
-    <t>①贪心 ②编码表</t>
-  </si>
-  <si>
-    <t>暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>罗马数字转整数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/roman-to-integer/</t>
-  </si>
-  <si>
-    <t>简单</t>
-  </si>
-  <si>
-    <t>①编程练习</t>
-  </si>
-  <si>
     <t>电话号码的字母组合</t>
   </si>
   <si>
@@ -151,9 +193,6 @@
     <t>https://leetcode-cn.com/problems/search-insert-position/</t>
   </si>
   <si>
-    <t>二分查找</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -208,15 +247,6 @@
     <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
   </si>
   <si>
-    <t>旋转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/rotate-list/</t>
-  </si>
-  <si>
-    <t>①闭合成环 ②快慢指针</t>
-  </si>
-  <si>
     <t>爬楼梯</t>
   </si>
   <si>
@@ -334,9 +364,6 @@
     <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
   </si>
   <si>
-    <t>困难</t>
-  </si>
-  <si>
     <t>两个动态规划</t>
   </si>
   <si>
@@ -358,21 +385,6 @@
     <t>①逆波兰表达式</t>
   </si>
   <si>
-    <t>寻找旋转排序数组中的最小值</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②二分查找</t>
-  </si>
-  <si>
-    <t>寻找旋转排序数组中的最小值 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/</t>
-  </si>
-  <si>
     <t>颠倒二进制位</t>
   </si>
   <si>
@@ -650,18 +662,6 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/design-parking-system/</t>
-  </si>
-  <si>
-    <t>n22</t>
-  </si>
-  <si>
-    <t>链表中倒数第k个节点</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/</t>
-  </si>
-  <si>
-    <t>①两趟遍历 ②快慢指针</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1322,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1344,27 +1344,30 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1374,49 +1377,40 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1474,6 +1468,16 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1770,7 +1774,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1816,37 +1820,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1">
-        <v>2</v>
+    <row r="2" spans="1:9">
+      <c r="A2" s="6">
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1862,804 +1867,786 @@
         <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6">
-        <v>12</v>
-      </c>
-      <c r="B4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6">
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6">
-        <v>13</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="6">
+        <v>153</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="6">
+        <v>154</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:9">
+      <c r="A9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="3">
-        <v>17</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1">
-        <v>26</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="H9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:9">
-      <c r="A8" s="1">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
-      <c r="A9" s="4">
-        <v>35</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1">
-        <v>46</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3">
+        <v>17</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:8">
+      <c r="A12" s="1">
+        <v>26</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:9">
-      <c r="A11" s="1">
-        <v>47</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="C12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:8">
+      <c r="A13" s="1">
+        <v>27</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4">
+        <v>35</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:9">
+      <c r="A15" s="1">
+        <v>46</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="15"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:9">
-      <c r="A12" s="1">
-        <v>53</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12" s="15"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1">
-        <v>54</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:9">
-      <c r="A14" s="1">
-        <v>59</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="20"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:9">
-      <c r="A15" s="6">
-        <v>61</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:9">
       <c r="A16" s="1">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:9">
+      <c r="A17" s="1">
+        <v>53</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="A18" s="1">
+        <v>54</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="22"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:9">
-      <c r="A17" s="2">
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:9">
+      <c r="A19" s="1">
+        <v>59</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:9">
+      <c r="A20" s="1">
         <v>70</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="B20" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:9">
+      <c r="A21" s="2">
+        <v>73</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="23"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:9">
+      <c r="A22" s="5">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="24"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:9">
+      <c r="A23" s="3">
+        <v>82</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:9">
+      <c r="A24" s="3">
+        <v>83</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="23"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:9">
-      <c r="A18" s="5">
-        <v>74</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:9">
-      <c r="A19" s="3">
-        <v>82</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:9">
-      <c r="A20" s="3">
-        <v>83</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:8">
-      <c r="A21" s="1">
-        <v>102</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:9">
-      <c r="A22" s="1">
-        <v>103</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="26"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:9">
-      <c r="A23" s="1">
-        <v>104</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:9">
-      <c r="A24" s="1">
-        <v>121</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
-        <v>125</v>
-      </c>
-      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="I25" s="26"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:8">
+      <c r="A26" s="1">
+        <v>103</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:9">
-      <c r="A26" s="1">
-        <v>131</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="15"/>
+        <v>98</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
       <c r="A27" s="1">
-        <v>132</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="15"/>
+        <v>95</v>
+      </c>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
+        <v>121</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="16"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:9">
+      <c r="A29" s="1">
+        <v>125</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:9">
+      <c r="A30" s="1">
+        <v>131</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I30" s="21"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:9">
+      <c r="A31" s="1">
+        <v>132</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="16"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:9">
+      <c r="A32" s="1">
         <v>144</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="B32" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:9">
-      <c r="A29" s="2">
+      <c r="E32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:9">
+      <c r="A33" s="2">
         <v>150</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B33" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I29" s="27"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:9">
-      <c r="A30" s="6">
-        <v>153</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I30" s="16"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:9">
-      <c r="A31" s="6">
-        <v>154</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I31" s="28"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:9">
-      <c r="A32" s="4">
-        <v>190</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32" s="29"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="2">
-        <v>191</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>120</v>
@@ -2668,188 +2655,188 @@
         <v>13</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="I34" s="20"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="2">
+        <v>191</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I34" s="19"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:9">
-      <c r="A35" s="4">
-        <v>199</v>
-      </c>
-      <c r="B35" s="10" t="s">
+      <c r="D35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I35" s="19"/>
+      <c r="I35" s="27"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:9">
       <c r="A36" s="4">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36" s="20"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:9">
+      <c r="A37" s="4">
+        <v>199</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="4" t="s">
+      <c r="D37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="I36" s="30"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:9">
-      <c r="A37" s="1">
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:9">
+      <c r="A38" s="4">
+        <v>200</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:9">
+      <c r="A39" s="1">
         <v>206</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="20"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="1">
+      <c r="B39" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1">
         <v>225</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I38" s="15"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="1">
-        <v>226</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="I39" s="15"/>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:9">
-      <c r="A40" s="1">
-        <v>227</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>13</v>
@@ -2858,25 +2845,25 @@
         <v>2</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I40" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="I40" s="16"/>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:9">
       <c r="A41" s="1">
-        <v>232</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>147</v>
+        <v>226</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>13</v>
@@ -2885,135 +2872,135 @@
         <v>2</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I41" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="I41" s="16"/>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:9">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
+        <v>227</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="1:9">
+      <c r="A43" s="1">
+        <v>232</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="3">
         <v>235</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="5">
+      <c r="B44" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" spans="1:9">
+      <c r="A45" s="5">
         <v>240</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="B45" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I43" s="24"/>
-    </row>
-    <row r="44" s="3" customFormat="1" spans="1:9">
-      <c r="A44" s="1">
-        <v>303</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="1:9">
-      <c r="A45" s="1">
-        <v>304</v>
-      </c>
-      <c r="B45" s="7" t="s">
+      <c r="E45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I45" s="32"/>
+      <c r="I45" s="29"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:9">
       <c r="A46" s="1">
-        <v>338</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>162</v>
+        <v>303</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3022,206 +3009,206 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I46" s="30"/>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:9">
+      <c r="A47" s="1">
+        <v>304</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I46" s="32"/>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:9">
-      <c r="A47" s="3">
-        <v>405</v>
-      </c>
-      <c r="B47" s="9" t="s">
+      <c r="D47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I47" s="31" t="s">
-        <v>168</v>
-      </c>
+      <c r="I47" s="30"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:9">
       <c r="A48" s="1">
+        <v>338</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I48" s="30"/>
+    </row>
+    <row r="49" s="3" customFormat="1" spans="1:9">
+      <c r="A49" s="3">
+        <v>405</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" s="3" customFormat="1" spans="1:9">
+      <c r="A50" s="1">
         <v>474</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="1:9">
-      <c r="A49" s="1">
-        <v>543</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I49" s="32"/>
-    </row>
-    <row r="50" s="4" customFormat="1" spans="1:9">
-      <c r="A50" s="3">
-        <v>617</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I50" s="31" t="s">
-        <v>25</v>
-      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
     </row>
     <row r="51" s="4" customFormat="1" spans="1:9">
       <c r="A51" s="1">
-        <v>654</v>
-      </c>
-      <c r="B51" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="I51" s="30"/>
+    </row>
+    <row r="52" s="4" customFormat="1" spans="1:9">
+      <c r="A52" s="3">
+        <v>617</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" s="4" customFormat="1" spans="1:9">
-      <c r="A52" s="1">
-        <v>824</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="D52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="1">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I52" s="32"/>
+      <c r="I52" s="19" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="53" s="4" customFormat="1" spans="1:9">
       <c r="A53" s="1">
-        <v>832</v>
-      </c>
-      <c r="B53" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="1">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I53" s="15"/>
+      <c r="I53" s="1"/>
     </row>
     <row r="54" s="4" customFormat="1" spans="1:9">
       <c r="A54" s="1">
-        <v>867</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>186</v>
+        <v>824</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>13</v>
@@ -3230,25 +3217,25 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" s="5" customFormat="1" spans="1:9">
+        <v>186</v>
+      </c>
+      <c r="I54" s="30"/>
+    </row>
+    <row r="55" s="4" customFormat="1" spans="1:9">
       <c r="A55" s="1">
-        <v>868</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>190</v>
+        <v>832</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>13</v>
@@ -3257,280 +3244,307 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I55" s="32"/>
+        <v>189</v>
+      </c>
+      <c r="I55" s="16"/>
     </row>
     <row r="56" s="5" customFormat="1" spans="1:9">
       <c r="A56" s="1">
-        <v>997</v>
-      </c>
-      <c r="B56" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" s="5" customFormat="1" spans="1:9">
+      <c r="A57" s="1">
+        <v>868</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="D57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="1:9">
-      <c r="A57" s="1">
-        <v>998</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="I57" s="30"/>
     </row>
     <row r="58" s="6" customFormat="1" spans="1:9">
       <c r="A58" s="1">
-        <v>999</v>
-      </c>
-      <c r="B58" s="7" t="s">
+        <v>997</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I58" s="15"/>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:9">
       <c r="A59" s="1">
-        <v>1047</v>
-      </c>
-      <c r="B59" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>203</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="1">
-        <v>2</v>
+      <c r="G59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I59" s="15"/>
+        <v>183</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="60" s="6" customFormat="1" spans="1:9">
       <c r="A60" s="1">
-        <v>1052</v>
-      </c>
-      <c r="B60" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="D60" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="1">
-        <v>1</v>
+      <c r="G60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I60" s="32"/>
+        <v>24</v>
+      </c>
+      <c r="I60" s="16"/>
     </row>
     <row r="61" s="6" customFormat="1" spans="1:9">
       <c r="A61" s="1">
+        <v>1047</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I61" s="16"/>
+    </row>
+    <row r="62" s="6" customFormat="1" spans="1:9">
+      <c r="A62" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I62" s="30"/>
+    </row>
+    <row r="63" s="6" customFormat="1" spans="1:9">
+      <c r="A63" s="1">
         <v>1603</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="B63" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I61" s="32"/>
-    </row>
-    <row r="62" s="6" customFormat="1" spans="1:9">
-      <c r="A62" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I62" s="16"/>
-    </row>
-    <row r="63" s="6" customFormat="1" spans="1:9">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="E63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="30"/>
+    </row>
+    <row r="64" s="6" customFormat="1" spans="1:9">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I63">
-    <sortState ref="A2:I63">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:I64">
+    <sortState ref="A2:I64">
+      <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B60" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B53" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B52" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C49" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C54" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B55" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B44" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B45" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B21" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="B22" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="C22" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B23" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B46" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
-    <hyperlink ref="B7" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B41" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B26" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B25" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B59" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
-    <hyperlink ref="B15" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B40" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B39" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B38" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
-    <hyperlink ref="B13" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
-    <hyperlink ref="B10" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
-    <hyperlink ref="B11" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
-    <hyperlink ref="B8" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
-    <hyperlink ref="B2" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
-    <hyperlink ref="B14" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
-    <hyperlink ref="B12" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
-    <hyperlink ref="B24" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B37" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
-    <hyperlink ref="B28" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B61" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B58" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B51" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B57" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
-    <hyperlink ref="B33" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B17" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
-    <hyperlink ref="B29" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
-    <hyperlink ref="B4" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B47" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B42" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B50" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
-    <hyperlink ref="B6" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
-    <hyperlink ref="B20" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
-    <hyperlink ref="B19" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
-    <hyperlink ref="B32" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
-    <hyperlink ref="B34" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
-    <hyperlink ref="B35" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
-    <hyperlink ref="B36" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
-    <hyperlink ref="B9" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
-    <hyperlink ref="B18" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B43" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
-    <hyperlink ref="B30" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
-    <hyperlink ref="B31" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
-    <hyperlink ref="B62" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
-    <hyperlink ref="B3" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
-    <hyperlink ref="B5" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
+    <hyperlink ref="B62" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B55" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B54" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C51" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C56" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B57" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B46" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B47" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B48" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
+    <hyperlink ref="B43" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B61" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
+    <hyperlink ref="B42" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B41" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B40" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
+    <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
+    <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
+    <hyperlink ref="B13" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
+    <hyperlink ref="B10" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
+    <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
+    <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
+    <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="B39" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="B63" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B60" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B53" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B59" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
+    <hyperlink ref="B21" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
+    <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
+    <hyperlink ref="B49" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B44" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B52" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
+    <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
+    <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
+    <hyperlink ref="B34" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
+    <hyperlink ref="B36" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
+    <hyperlink ref="B37" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
+    <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
+    <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
+    <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
+    <hyperlink ref="B45" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
+    <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
+    <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
+    <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
+    <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="216">
   <si>
     <t>编号</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/house-robber/</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>①动态规划 ②存储优化 ③记忆化递归</t>
@@ -669,8 +672,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
@@ -702,13 +705,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -716,7 +712,61 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -731,53 +781,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -791,41 +795,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -844,13 +818,48 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -884,7 +893,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -896,109 +1043,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1010,43 +1061,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1090,6 +1105,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1112,6 +1145,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1139,39 +1187,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1180,10 +1195,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1192,137 +1207,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1344,73 +1359,82 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1821,212 +1845,212 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>11</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="F2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="17"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6">
-        <v>13</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="7">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="17"/>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="17"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="20"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>61</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="18"/>
+      <c r="I6" s="21"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>153</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="18"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>154</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="18"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="18"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2049,31 +2073,31 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>17</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2081,7 +2105,7 @@
       <c r="A12" s="1">
         <v>26</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2107,7 +2131,7 @@
       <c r="A13" s="1">
         <v>27</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2130,35 +2154,35 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <v>35</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="20"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="1">
         <v>46</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2179,13 +2203,13 @@
       <c r="H15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="11"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:9">
       <c r="A16" s="1">
         <v>47</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2206,13 +2230,13 @@
       <c r="H16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:9">
       <c r="A17" s="1">
         <v>53</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2233,13 +2257,13 @@
       <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:9">
       <c r="A18" s="1">
         <v>54</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2260,13 +2284,13 @@
       <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="16"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
       <c r="A19" s="1">
         <v>59</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2287,13 +2311,13 @@
       <c r="H19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="16"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
       <c r="A20" s="1">
         <v>70</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2311,122 +2335,122 @@
       <c r="G20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="22"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:9">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>73</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="23"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>74</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I22" s="24"/>
+      <c r="I22" s="27"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>82</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="25"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="28"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>83</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="F24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="25"/>
+      <c r="I24" s="28"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>102</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2447,13 +2471,13 @@
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="26"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
       <c r="A26" s="1">
         <v>103</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2479,7 +2503,7 @@
       <c r="A27" s="1">
         <v>104</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2500,13 +2524,13 @@
       <c r="H27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I27" s="16"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
         <v>121</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -2527,13 +2551,13 @@
       <c r="H28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I28" s="16"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:9">
       <c r="A29" s="1">
         <v>125</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2554,13 +2578,13 @@
       <c r="H29" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I29" s="16"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
       <c r="A30" s="1">
         <v>131</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2581,13 +2605,13 @@
       <c r="H30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I30" s="21"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:9">
       <c r="A31" s="1">
         <v>132</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2608,13 +2632,13 @@
       <c r="H31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I31" s="16"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:9">
       <c r="A32" s="1">
         <v>144</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="16" t="s">
         <v>116</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2632,180 +2656,180 @@
       <c r="G32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="21"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:9">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>150</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="23"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="4">
+      <c r="A34" s="5">
         <v>190</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="I34" s="20"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>191</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="F35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:9">
-      <c r="A36" s="4">
+      <c r="I35" s="29"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:9">
+      <c r="A36" s="18">
         <v>198</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F36" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" s="30"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:9">
+      <c r="A37" s="5">
+        <v>199</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I36" s="20"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:9">
-      <c r="A37" s="4">
-        <v>199</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="H37" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I37" s="31"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:9">
+      <c r="A38" s="5">
+        <v>200</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="4" t="s">
+      <c r="E38" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I37" s="28"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="4">
-        <v>200</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="I38" s="28"/>
+      <c r="H38" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" s="31"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>206</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>139</v>
+      <c r="B39" s="16" t="s">
+        <v>140</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>23</v>
@@ -2819,24 +2843,24 @@
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>225</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>141</v>
+      <c r="B40" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>13</v>
@@ -2845,19 +2869,19 @@
         <v>2</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I40" s="16"/>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:9">
+        <v>145</v>
+      </c>
+      <c r="I40" s="17"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:9">
       <c r="A41" s="1">
         <v>226</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>145</v>
+      <c r="B41" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>23</v>
@@ -2872,19 +2896,19 @@
         <v>2</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I41" s="16"/>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:9">
+        <v>148</v>
+      </c>
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:9">
       <c r="A42" s="1">
         <v>227</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>148</v>
+      <c r="B42" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>11</v>
@@ -2899,25 +2923,25 @@
         <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" s="2" customFormat="1" spans="1:9">
+    <row r="43" s="3" customFormat="1" spans="1:9">
       <c r="A43" s="1">
         <v>232</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>151</v>
+      <c r="B43" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -2926,75 +2950,75 @@
         <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>235</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B44" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="C44" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="F44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I44" s="19" t="s">
+      <c r="H44" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I44" s="22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" s="3" customFormat="1" spans="1:9">
-      <c r="A45" s="5">
+    <row r="45" s="4" customFormat="1" spans="1:9">
+      <c r="A45" s="6">
         <v>240</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="B45" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="C45" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="F45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H45" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I45" s="29"/>
-    </row>
-    <row r="46" s="3" customFormat="1" spans="1:9">
+      <c r="H45" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I45" s="32"/>
+    </row>
+    <row r="46" s="4" customFormat="1" spans="1:9">
       <c r="A46" s="1">
         <v>303</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>160</v>
+      <c r="B46" s="9" t="s">
+        <v>161</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>23</v>
@@ -3009,19 +3033,19 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I46" s="30"/>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:9">
+        <v>163</v>
+      </c>
+      <c r="I46" s="33"/>
+    </row>
+    <row r="47" s="4" customFormat="1" spans="1:9">
       <c r="A47" s="1">
         <v>304</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>163</v>
+      <c r="B47" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>11</v>
@@ -3036,19 +3060,19 @@
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I47" s="30"/>
-    </row>
-    <row r="48" s="3" customFormat="1" spans="1:9">
+        <v>166</v>
+      </c>
+      <c r="I47" s="33"/>
+    </row>
+    <row r="48" s="4" customFormat="1" spans="1:9">
       <c r="A48" s="1">
         <v>338</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>166</v>
+      <c r="B48" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>11</v>
@@ -3063,45 +3087,45 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I48" s="30"/>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="1:9">
-      <c r="A49" s="3">
+        <v>169</v>
+      </c>
+      <c r="I48" s="33"/>
+    </row>
+    <row r="49" s="4" customFormat="1" spans="1:9">
+      <c r="A49" s="4">
         <v>405</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B49" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="C49" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="F49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I49" s="19" t="s">
+      <c r="H49" s="4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="50" s="3" customFormat="1" spans="1:9">
+      <c r="I49" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" s="4" customFormat="1" spans="1:9">
       <c r="A50" s="1">
         <v>474</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3111,21 +3135,21 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" s="4" customFormat="1" spans="1:9">
+    <row r="51" s="5" customFormat="1" spans="1:9">
       <c r="A51" s="1">
         <v>543</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
@@ -3134,48 +3158,48 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I51" s="30"/>
-    </row>
-    <row r="52" s="4" customFormat="1" spans="1:9">
-      <c r="A52" s="3">
+        <v>178</v>
+      </c>
+      <c r="I51" s="33"/>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:9">
+      <c r="A52" s="4">
         <v>617</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="B52" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="C52" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="3" t="s">
+      <c r="F52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="I52" s="19" t="s">
+      <c r="H52" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I52" s="22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" s="4" customFormat="1" spans="1:9">
+    <row r="53" s="5" customFormat="1" spans="1:9">
       <c r="A53" s="1">
         <v>654</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>181</v>
+      <c r="B53" s="9" t="s">
+        <v>182</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>11</v>
@@ -3190,19 +3214,19 @@
         <v>42</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="1"/>
     </row>
-    <row r="54" s="4" customFormat="1" spans="1:9">
+    <row r="54" s="5" customFormat="1" spans="1:9">
       <c r="A54" s="1">
         <v>824</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>184</v>
+      <c r="B54" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>23</v>
@@ -3217,19 +3241,19 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I54" s="30"/>
-    </row>
-    <row r="55" s="4" customFormat="1" spans="1:9">
+        <v>187</v>
+      </c>
+      <c r="I54" s="33"/>
+    </row>
+    <row r="55" s="5" customFormat="1" spans="1:9">
       <c r="A55" s="1">
         <v>832</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>187</v>
+      <c r="B55" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
@@ -3244,25 +3268,25 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I55" s="16"/>
-    </row>
-    <row r="56" s="5" customFormat="1" spans="1:9">
+        <v>190</v>
+      </c>
+      <c r="I55" s="17"/>
+    </row>
+    <row r="56" s="6" customFormat="1" spans="1:9">
       <c r="A56" s="1">
         <v>867</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3271,25 +3295,25 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" s="5" customFormat="1" spans="1:9">
+    <row r="57" s="6" customFormat="1" spans="1:9">
       <c r="A57" s="1">
         <v>868</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>194</v>
+      <c r="B57" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3298,25 +3322,25 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I57" s="30"/>
-    </row>
-    <row r="58" s="6" customFormat="1" spans="1:9">
+        <v>197</v>
+      </c>
+      <c r="I57" s="33"/>
+    </row>
+    <row r="58" s="7" customFormat="1" spans="1:9">
       <c r="A58" s="1">
         <v>997</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>197</v>
+      <c r="B58" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3325,21 +3349,21 @@
         <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="59" s="6" customFormat="1" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" s="7" customFormat="1" spans="1:9">
       <c r="A59" s="1">
         <v>998</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>202</v>
+      <c r="B59" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>11</v>
@@ -3354,21 +3378,21 @@
         <v>42</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="60" s="6" customFormat="1" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" s="7" customFormat="1" spans="1:9">
       <c r="A60" s="1">
         <v>999</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>204</v>
+      <c r="B60" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
@@ -3385,23 +3409,23 @@
       <c r="H60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I60" s="16"/>
-    </row>
-    <row r="61" s="6" customFormat="1" spans="1:9">
+      <c r="I60" s="17"/>
+    </row>
+    <row r="61" s="7" customFormat="1" spans="1:9">
       <c r="A61" s="1">
         <v>1047</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>206</v>
+      <c r="B61" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3410,25 +3434,25 @@
         <v>2</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I61" s="16"/>
-    </row>
-    <row r="62" s="6" customFormat="1" spans="1:9">
+        <v>209</v>
+      </c>
+      <c r="I61" s="17"/>
+    </row>
+    <row r="62" s="7" customFormat="1" spans="1:9">
       <c r="A62" s="1">
         <v>1052</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>209</v>
+      <c r="B62" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3437,19 +3461,19 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I62" s="30"/>
-    </row>
-    <row r="63" s="6" customFormat="1" spans="1:9">
+        <v>213</v>
+      </c>
+      <c r="I62" s="33"/>
+    </row>
+    <row r="63" s="7" customFormat="1" spans="1:9">
       <c r="A63" s="1">
         <v>1603</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>213</v>
+      <c r="B63" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
@@ -3466,9 +3490,9 @@
       <c r="H63" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="30"/>
-    </row>
-    <row r="64" s="6" customFormat="1" spans="1:9">
+      <c r="I63" s="33"/>
+    </row>
+    <row r="64" s="7" customFormat="1" spans="1:9">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3481,7 +3505,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
-    <sortState ref="A2:I64">
+    <sortState ref="A1:I64">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="220">
   <si>
     <t>编号</t>
   </si>
@@ -665,6 +665,18 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/design-parking-system/</t>
+  </si>
+  <si>
+    <t>生命游戏</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/game-of-life/</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>①复制数组 ②复合状态</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3502,6 +3514,33 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
+    </row>
+    <row r="70" s="7" customFormat="1" spans="1:9">
+      <c r="A70" s="1">
+        <v>289</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I70" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3569,6 +3608,7 @@
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
+    <hyperlink ref="B70" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -676,7 +676,7 @@
     <t>Q</t>
   </si>
   <si>
-    <t>①复制数组 ②复合状态</t>
+    <t>①复制数组 ②复合状态 ③位运算</t>
   </si>
 </sst>
 </file>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -259,424 +259,424 @@
     <t>①动态规划 ②存储优化</t>
   </si>
   <si>
+    <t>搜索二维矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
+  </si>
+  <si>
+    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
+  </si>
+  <si>
+    <t>删除排序链表中的重复元素</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
+  </si>
+  <si>
+    <t>①两个变量 ①一个变量</t>
+  </si>
+  <si>
+    <t>二叉树的层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>二叉树</t>
+  </si>
+  <si>
+    <t>广度优先搜索/深度优先搜索</t>
+  </si>
+  <si>
+    <t>二叉树的锯齿形层序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
+  </si>
+  <si>
+    <t>列表头插/列表反转/双端队列</t>
+  </si>
+  <si>
+    <t>二叉树的最大深度</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>买卖股票的最佳时机</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>①暴力搜索 ②动态规划 ③存储优化</t>
+  </si>
+  <si>
+    <t>验证回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>字符串</t>
+  </si>
+  <si>
+    <t>字符串操作</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯搜索、动态规划</t>
+  </si>
+  <si>
+    <t>动态规划用于降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>两个动态规划</t>
+  </si>
+  <si>
+    <t>二叉树的前序遍历</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式求值</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/</t>
+  </si>
+  <si>
+    <t>逆波兰表达式</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>①逆波兰表达式</t>
+  </si>
+  <si>
+    <t>颠倒二进制位</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
+  </si>
+  <si>
+    <t>位运算</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④分治</t>
+  </si>
+  <si>
+    <t>位1的个数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-1-bits/</t>
+  </si>
+  <si>
+    <t>①②③位运算 ④位运算优化</t>
+  </si>
+  <si>
+    <t>打家劫舍</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/house-robber/</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
+    <t>二叉树的右视图</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索</t>
+  </si>
+  <si>
+    <t>岛屿数量</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>广度优先搜索</t>
+  </si>
+  <si>
+    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
+  </si>
+  <si>
+    <t>反转链表</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
+  </si>
+  <si>
+    <t>用队列实现栈</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
+  </si>
+  <si>
+    <t>队列</t>
+  </si>
+  <si>
+    <t>单/双队列</t>
+  </si>
+  <si>
+    <t>翻转二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
+  </si>
+  <si>
+    <t>递归</t>
+  </si>
+  <si>
+    <t>基本计算器 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
+  </si>
+  <si>
+    <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>用栈实现队列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>栈</t>
+  </si>
+  <si>
+    <t>二叉搜索树的最近公共祖先</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
+  </si>
+  <si>
+    <t>①一趟遍历 ②两趟遍历</t>
+  </si>
+  <si>
+    <t>搜索二维矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①缩减空间</t>
+  </si>
+  <si>
+    <t>区域和检索 - 数组不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
+  </si>
+  <si>
+    <t>一维动态规划——数组前缀和</t>
+  </si>
+  <si>
+    <t>二维区域和检索 - 矩阵不可变</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
+  </si>
+  <si>
+    <t>二维动态规划——矩阵前缀和</t>
+  </si>
+  <si>
+    <t>比特位计数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/counting-bits/</t>
+  </si>
+  <si>
+    <t>动态规划、位运算</t>
+  </si>
+  <si>
+    <t>数字转换为十六进制数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
+  </si>
+  <si>
+    <t>①位运算</t>
+  </si>
+  <si>
+    <t>暂缺官方题解 暂缺负雪明烛</t>
+  </si>
+  <si>
+    <t>一和零</t>
+  </si>
+  <si>
+    <t>二叉树的直径</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>深度优先搜索</t>
+  </si>
+  <si>
+    <t>子树深度</t>
+  </si>
+  <si>
+    <t>合并二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
+  </si>
+  <si>
+    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
+  </si>
+  <si>
+    <t>最大二叉树</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
+  </si>
+  <si>
+    <t>①递归</t>
+  </si>
+  <si>
+    <t>山羊拉丁文</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/goat-latin/</t>
+  </si>
+  <si>
+    <t>字符串与字符数组效率对比</t>
+  </si>
+  <si>
+    <t>翻转图像</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
+  </si>
+  <si>
+    <t>双指针+异或取反</t>
+  </si>
+  <si>
+    <t>转置矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>二维数组</t>
+  </si>
+  <si>
+    <t>二进制间距</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/binary-gap/</t>
+  </si>
+  <si>
+    <t>进制运算（右移位、与一）</t>
+  </si>
+  <si>
+    <t>找到小镇的法官</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
+  </si>
+  <si>
+    <t>有向图</t>
+  </si>
+  <si>
+    <t>①有向图的入度/出度</t>
+  </si>
+  <si>
+    <t>无官方题解，未计算复杂度</t>
+  </si>
+  <si>
+    <t>最大二叉树 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
+  </si>
+  <si>
+    <t>可以被一步捕获的棋子数</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
+  </si>
+  <si>
+    <t>删除字符串中的所有相邻重复项</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>爱生气的书店老板</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
+  </si>
+  <si>
+    <t>滑动窗口</t>
+  </si>
+  <si>
+    <t>长度为X的连续子区间元素之和的最大值</t>
+  </si>
+  <si>
+    <t>设计停车系统</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
+  </si>
+  <si>
+    <t>生命游戏</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/game-of-life/</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>①复制数组 ②复合状态 ③位运算</t>
+  </si>
+  <si>
     <t>矩阵置零</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/set-matrix-zeroes/</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix/</t>
-  </si>
-  <si>
-    <t>①两轮二分查找 ②一轮二分查找 ③缩减空间</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/</t>
-  </si>
-  <si>
-    <t>删除排序链表中的重复元素</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/</t>
-  </si>
-  <si>
-    <t>①两个变量 ①一个变量</t>
-  </si>
-  <si>
-    <t>二叉树的层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>二叉树</t>
-  </si>
-  <si>
-    <t>广度优先搜索/深度优先搜索</t>
-  </si>
-  <si>
-    <t>二叉树的锯齿形层序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/</t>
-  </si>
-  <si>
-    <t>列表头插/列表反转/双端队列</t>
-  </si>
-  <si>
-    <t>二叉树的最大深度</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>买卖股票的最佳时机</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
-  </si>
-  <si>
-    <t>动态规划</t>
-  </si>
-  <si>
-    <t>①暴力搜索 ②动态规划 ③存储优化</t>
-  </si>
-  <si>
-    <t>验证回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/valid-palindrome/</t>
-  </si>
-  <si>
-    <t>字符串</t>
-  </si>
-  <si>
-    <t>字符串操作</t>
-  </si>
-  <si>
-    <t>分割回文串</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
-  </si>
-  <si>
-    <t>回溯搜索、动态规划</t>
-  </si>
-  <si>
-    <t>动态规划用于降低判断回文数的复杂度</t>
-  </si>
-  <si>
-    <t>分割回文串 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
-  </si>
-  <si>
-    <t>两个动态规划</t>
-  </si>
-  <si>
-    <t>二叉树的前序遍历</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-preorder-traversal/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式求值</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/</t>
-  </si>
-  <si>
-    <t>逆波兰表达式</t>
-  </si>
-  <si>
-    <t>①逆波兰表达式</t>
-  </si>
-  <si>
-    <t>颠倒二进制位</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-bits/</t>
-  </si>
-  <si>
-    <t>位运算</t>
-  </si>
-  <si>
-    <t>①②③位运算 ④分治</t>
-  </si>
-  <si>
-    <t>位1的个数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/number-of-1-bits/</t>
-  </si>
-  <si>
-    <t>①②③位运算 ④位运算优化</t>
-  </si>
-  <si>
-    <t>打家劫舍</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/house-robber/</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
-  </si>
-  <si>
-    <t>二叉树的右视图</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-tree-right-side-view/</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索</t>
-  </si>
-  <si>
-    <t>岛屿数量</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/number-of-islands/</t>
-  </si>
-  <si>
-    <t>广度优先搜索</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
-  </si>
-  <si>
-    <t>反转链表</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/reverse-linked-list/</t>
-  </si>
-  <si>
-    <t>用队列实现栈</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-stack-using-queues/</t>
-  </si>
-  <si>
-    <t>队列</t>
-  </si>
-  <si>
-    <t>单/双队列</t>
-  </si>
-  <si>
-    <t>翻转二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/invert-binary-tree/</t>
-  </si>
-  <si>
-    <t>递归</t>
-  </si>
-  <si>
-    <t>基本计算器 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/basic-calculator-ii/</t>
-  </si>
-  <si>
-    <t>双栈模拟</t>
-  </si>
-  <si>
-    <t>用栈实现队列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/implement-queue-using-stacks/</t>
-  </si>
-  <si>
-    <t>栈</t>
-  </si>
-  <si>
-    <t>二叉搜索树的最近公共祖先</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/</t>
-  </si>
-  <si>
-    <t>①一趟遍历 ②两趟遍历</t>
-  </si>
-  <si>
-    <t>搜索二维矩阵 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-a-2d-matrix-ii/</t>
-  </si>
-  <si>
-    <t>①缩减空间</t>
-  </si>
-  <si>
-    <t>区域和检索 - 数组不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-immutable/</t>
-  </si>
-  <si>
-    <t>一维动态规划——数组前缀和</t>
-  </si>
-  <si>
-    <t>二维区域和检索 - 矩阵不可变</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/range-sum-query-2d-immutable/</t>
-  </si>
-  <si>
-    <t>二维动态规划——矩阵前缀和</t>
-  </si>
-  <si>
-    <t>比特位计数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/counting-bits/</t>
-  </si>
-  <si>
-    <t>动态规划、位运算</t>
-  </si>
-  <si>
-    <t>数字转换为十六进制数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/</t>
-  </si>
-  <si>
-    <t>①位运算</t>
-  </si>
-  <si>
-    <t>暂缺官方题解 暂缺负雪明烛</t>
-  </si>
-  <si>
-    <t>一和零</t>
-  </si>
-  <si>
-    <t>二叉树的直径</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/diameter-of-binary-tree/</t>
-  </si>
-  <si>
-    <t>深度优先搜索</t>
-  </si>
-  <si>
-    <t>子树深度</t>
-  </si>
-  <si>
-    <t>合并二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/merge-two-binary-trees/</t>
-  </si>
-  <si>
-    <t>①深度优先搜索（原地/新建） ②广度优先搜索（原地/新建）</t>
-  </si>
-  <si>
-    <t>最大二叉树</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree/</t>
-  </si>
-  <si>
-    <t>①递归</t>
-  </si>
-  <si>
-    <t>山羊拉丁文</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/goat-latin/</t>
-  </si>
-  <si>
-    <t>字符串与字符数组效率对比</t>
-  </si>
-  <si>
-    <t>翻转图像</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/flipping-an-image/</t>
-  </si>
-  <si>
-    <t>双指针+异或取反</t>
-  </si>
-  <si>
-    <t>转置矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/transpose-matrix/</t>
-  </si>
-  <si>
-    <t>基础</t>
-  </si>
-  <si>
-    <t>二维数组</t>
-  </si>
-  <si>
-    <t>二进制间距</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/binary-gap/</t>
-  </si>
-  <si>
-    <t>进制运算（右移位、与一）</t>
-  </si>
-  <si>
-    <t>找到小镇的法官</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/find-the-town-judge/</t>
-  </si>
-  <si>
-    <t>有向图</t>
-  </si>
-  <si>
-    <t>①有向图的入度/出度</t>
-  </si>
-  <si>
-    <t>无官方题解，未计算复杂度</t>
-  </si>
-  <si>
-    <t>最大二叉树 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-binary-tree-ii/</t>
-  </si>
-  <si>
-    <t>可以被一步捕获的棋子数</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/available-captures-for-rook/</t>
-  </si>
-  <si>
-    <t>删除字符串中的所有相邻重复项</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/</t>
-  </si>
-  <si>
-    <t>数据结构</t>
-  </si>
-  <si>
-    <t>爱生气的书店老板</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/grumpy-bookstore-owner/</t>
-  </si>
-  <si>
-    <t>滑动窗口</t>
-  </si>
-  <si>
-    <t>长度为X的连续子区间元素之和的最大值</t>
-  </si>
-  <si>
-    <t>设计停车系统</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/design-parking-system/</t>
-  </si>
-  <si>
-    <t>生命游戏</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/game-of-life/</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>①复制数组 ②复合状态 ③位运算</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1349,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1389,21 +1389,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1428,13 +1425,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1810,7 +1807,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1881,7 +1878,7 @@
       <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="20"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="7">
@@ -1908,7 +1905,7 @@
       <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1937,7 +1934,7 @@
       <c r="H4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="20"/>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7"/>
@@ -1948,7 +1945,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="20"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7">
@@ -1975,7 +1972,7 @@
       <c r="H6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="21"/>
+      <c r="I6" s="20"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="7">
@@ -2002,7 +1999,7 @@
       <c r="H7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="21"/>
+      <c r="I7" s="20"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7">
@@ -2029,7 +2026,7 @@
       <c r="H8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:9">
       <c r="A9" s="7" t="s">
@@ -2056,7 +2053,7 @@
       <c r="H9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
       <c r="A10" s="1">
@@ -2109,7 +2106,7 @@
       <c r="H11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2188,7 +2185,7 @@
         <v>58</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="23"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="1">
@@ -2242,7 +2239,7 @@
       <c r="H16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="24"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:9">
       <c r="A17" s="1">
@@ -2269,7 +2266,7 @@
       <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="24"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:9">
       <c r="A18" s="1">
@@ -2296,7 +2293,7 @@
       <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="17"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:9">
       <c r="A19" s="1">
@@ -2323,7 +2320,7 @@
       <c r="H19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="17"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:9">
       <c r="A20" s="1">
@@ -2350,44 +2347,17 @@
       <c r="H20" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:9">
-      <c r="A21" s="3">
-        <v>73</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="26"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:9">
       <c r="A22" s="6">
         <v>74</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>84</v>
+      <c r="B22" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>11</v>
@@ -2402,19 +2372,19 @@
         <v>58</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="27"/>
+        <v>82</v>
+      </c>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:9">
       <c r="A23" s="4">
         <v>82</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
@@ -2429,17 +2399,17 @@
         <v>42</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="28"/>
+      <c r="I23" s="26"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:9">
       <c r="A24" s="4">
         <v>83</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>23</v>
@@ -2454,25 +2424,25 @@
         <v>42</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" s="28"/>
+        <v>87</v>
+      </c>
+      <c r="I24" s="26"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:9">
       <c r="A25" s="1">
         <v>102</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
@@ -2481,25 +2451,25 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I25" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
       <c r="A26" s="1">
         <v>103</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
@@ -2508,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:9">
@@ -2516,16 +2486,16 @@
         <v>104</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2534,25 +2504,25 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
         <v>121</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -2561,25 +2531,25 @@
         <v>42</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I28" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:9">
       <c r="A29" s="1">
         <v>125</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
@@ -2588,25 +2558,25 @@
         <v>2</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="17"/>
+        <v>104</v>
+      </c>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:9">
       <c r="A30" s="1">
         <v>131</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -2615,25 +2585,25 @@
         <v>2</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I30" s="24"/>
+        <v>108</v>
+      </c>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:9">
       <c r="A31" s="1">
         <v>132</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -2642,25 +2612,25 @@
         <v>2</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I31" s="17"/>
+        <v>111</v>
+      </c>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:9">
       <c r="A32" s="1">
         <v>144</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>116</v>
+      <c r="B32" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
@@ -2668,51 +2638,51 @@
       <c r="G32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="24"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:9">
       <c r="A33" s="3">
         <v>150</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>118</v>
+      <c r="B33" s="16" t="s">
+        <v>114</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I33" s="26"/>
+        <v>118</v>
+      </c>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="5">
         <v>190</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>13</v>
@@ -2721,79 +2691,79 @@
         <v>58</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="23"/>
+        <v>122</v>
+      </c>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3">
         <v>191</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>126</v>
+      <c r="B35" s="16" t="s">
+        <v>123</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:9">
+      <c r="A36" s="17">
+        <v>198</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="I35" s="29"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
-      <c r="A36" s="18">
-        <v>198</v>
-      </c>
-      <c r="B36" s="19" t="s">
+      <c r="H36" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" s="30"/>
+      <c r="I36" s="29"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:9">
       <c r="A37" s="5">
         <v>199</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>13</v>
@@ -2802,25 +2772,25 @@
         <v>58</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I37" s="31"/>
+        <v>132</v>
+      </c>
+      <c r="I37" s="30"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:9">
       <c r="A38" s="5">
         <v>200</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>13</v>
@@ -2829,19 +2799,19 @@
         <v>58</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I38" s="31"/>
+        <v>136</v>
+      </c>
+      <c r="I38" s="30"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:9">
       <c r="A39" s="1">
         <v>206</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>140</v>
+      <c r="B39" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>23</v>
@@ -2855,24 +2825,24 @@
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>225</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>13</v>
@@ -2881,25 +2851,25 @@
         <v>2</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" s="17"/>
+        <v>142</v>
+      </c>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:9">
       <c r="A41" s="1">
         <v>226</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>13</v>
@@ -2908,25 +2878,25 @@
         <v>2</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I41" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:9">
       <c r="A42" s="1">
         <v>227</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>13</v>
@@ -2935,7 +2905,7 @@
         <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I42" s="1"/>
     </row>
@@ -2944,16 +2914,16 @@
         <v>232</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -2962,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I43" s="1"/>
     </row>
@@ -2971,16 +2941,16 @@
         <v>235</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>13</v>
@@ -2989,9 +2959,9 @@
         <v>42</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I44" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2999,11 +2969,11 @@
       <c r="A45" s="6">
         <v>240</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>158</v>
+      <c r="B45" s="13" t="s">
+        <v>155</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>11</v>
@@ -3018,25 +2988,25 @@
         <v>58</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I45" s="32"/>
+        <v>157</v>
+      </c>
+      <c r="I45" s="31"/>
     </row>
     <row r="46" s="4" customFormat="1" spans="1:9">
       <c r="A46" s="1">
         <v>303</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3045,25 +3015,25 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I46" s="33"/>
+        <v>160</v>
+      </c>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:9">
       <c r="A47" s="1">
         <v>304</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3072,25 +3042,25 @@
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I47" s="33"/>
+        <v>163</v>
+      </c>
+      <c r="I47" s="32"/>
     </row>
     <row r="48" s="4" customFormat="1" spans="1:9">
       <c r="A48" s="1">
         <v>338</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>13</v>
@@ -3099,25 +3069,25 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I48" s="33"/>
+        <v>166</v>
+      </c>
+      <c r="I48" s="32"/>
     </row>
     <row r="49" s="4" customFormat="1" spans="1:9">
       <c r="A49" s="4">
         <v>405</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>13</v>
@@ -3126,10 +3096,10 @@
         <v>42</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>173</v>
+        <v>169</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="50" s="4" customFormat="1" spans="1:9">
@@ -3137,7 +3107,7 @@
         <v>474</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3152,16 +3122,16 @@
         <v>543</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
@@ -3170,25 +3140,25 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I51" s="33"/>
+        <v>175</v>
+      </c>
+      <c r="I51" s="32"/>
     </row>
     <row r="52" s="5" customFormat="1" spans="1:9">
       <c r="A52" s="4">
         <v>617</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>13</v>
@@ -3197,9 +3167,9 @@
         <v>42</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I52" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="I52" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3208,16 +3178,16 @@
         <v>654</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>13</v>
@@ -3226,7 +3196,7 @@
         <v>42</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I53" s="1"/>
     </row>
@@ -3235,16 +3205,16 @@
         <v>824</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>13</v>
@@ -3253,19 +3223,19 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I54" s="33"/>
+        <v>184</v>
+      </c>
+      <c r="I54" s="32"/>
     </row>
     <row r="55" s="5" customFormat="1" spans="1:9">
       <c r="A55" s="1">
         <v>832</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
@@ -3280,25 +3250,25 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I55" s="17"/>
+        <v>187</v>
+      </c>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" s="6" customFormat="1" spans="1:9">
       <c r="A56" s="1">
         <v>867</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3307,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I56" s="1"/>
     </row>
@@ -3316,16 +3286,16 @@
         <v>868</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3334,25 +3304,25 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I57" s="33"/>
+        <v>194</v>
+      </c>
+      <c r="I57" s="32"/>
     </row>
     <row r="58" s="7" customFormat="1" spans="1:9">
       <c r="A58" s="1">
         <v>997</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3361,10 +3331,10 @@
         <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" s="7" customFormat="1" spans="1:9">
@@ -3372,16 +3342,16 @@
         <v>998</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3390,10 +3360,10 @@
         <v>42</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" s="7" customFormat="1" spans="1:9">
@@ -3401,10 +3371,10 @@
         <v>999</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
@@ -3421,23 +3391,23 @@
       <c r="H60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I60" s="17"/>
+      <c r="I60" s="15"/>
     </row>
     <row r="61" s="7" customFormat="1" spans="1:9">
       <c r="A61" s="1">
         <v>1047</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3446,25 +3416,25 @@
         <v>2</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I61" s="17"/>
+        <v>206</v>
+      </c>
+      <c r="I61" s="15"/>
     </row>
     <row r="62" s="7" customFormat="1" spans="1:9">
       <c r="A62" s="1">
         <v>1052</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3473,19 +3443,19 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I62" s="33"/>
+        <v>210</v>
+      </c>
+      <c r="I62" s="32"/>
     </row>
     <row r="63" s="7" customFormat="1" spans="1:9">
       <c r="A63" s="1">
         <v>1603</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
@@ -3502,7 +3472,7 @@
       <c r="H63" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="33"/>
+      <c r="I63" s="32"/>
     </row>
     <row r="64" s="7" customFormat="1" spans="1:9">
       <c r="A64" s="1"/>
@@ -3520,10 +3490,10 @@
         <v>289</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>11</v>
@@ -3535,12 +3505,39 @@
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I70" s="32"/>
+    </row>
+    <row r="71" s="7" customFormat="1" spans="1:9">
+      <c r="A71" s="1">
+        <v>73</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="D71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I70" s="33"/>
+      <c r="I71" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3587,7 +3584,7 @@
     <hyperlink ref="B53" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
     <hyperlink ref="B59" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B21" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B71" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
     <hyperlink ref="B49" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="224">
   <si>
     <t>编号</t>
   </si>
@@ -677,6 +677,18 @@
   </si>
   <si>
     <t>①标记数组 ②两个状态变量 ③一个状态变量 ④位运算空间压缩</t>
+  </si>
+  <si>
+    <t>实现 Trie (前缀树)</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/implement-trie-prefix-tree/</t>
+  </si>
+  <si>
+    <t>前缀树</t>
+  </si>
+  <si>
+    <t>①固定长度数组 ②哈希表</t>
   </si>
 </sst>
 </file>
@@ -1807,7 +1819,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3538,6 +3550,33 @@
         <v>219</v>
       </c>
       <c r="I71" s="32"/>
+    </row>
+    <row r="72" s="7" customFormat="1" spans="1:9">
+      <c r="A72" s="1">
+        <v>208</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I72" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3606,6 +3645,7 @@
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
     <hyperlink ref="B70" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B72" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="227">
   <si>
     <t>编号</t>
   </si>
@@ -689,6 +689,15 @@
   </si>
   <si>
     <t>①固定长度数组 ②哈希表</t>
+  </si>
+  <si>
+    <t>单词替换</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/replace-words/</t>
+  </si>
+  <si>
+    <t>①前缀树 ②暴力搜索</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3577,6 +3586,33 @@
         <v>223</v>
       </c>
       <c r="I72" s="32"/>
+    </row>
+    <row r="73" s="7" customFormat="1" spans="1:9">
+      <c r="A73" s="1">
+        <v>648</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I73" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3646,6 +3682,7 @@
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
     <hyperlink ref="B70" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
     <hyperlink ref="B72" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B73" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="230">
   <si>
     <t>编号</t>
   </si>
@@ -698,6 +698,15 @@
   </si>
   <si>
     <t>①前缀树 ②暴力搜索</t>
+  </si>
+  <si>
+    <t>词典中最长的单词</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/longest-word-in-dictionary/</t>
+  </si>
+  <si>
+    <t>①前缀树+深度优先搜索 ②前缀树+广度优先搜索 ③暴力搜索</t>
   </si>
 </sst>
 </file>
@@ -735,6 +744,22 @@
       <color rgb="FF262626"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -790,14 +815,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -823,14 +840,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1228,10 +1237,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1240,61 +1249,61 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -1303,16 +1312,16 @@
     <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1321,56 +1330,56 @@
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1469,6 +1478,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1828,7 +1846,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3567,7 +3585,7 @@
       <c r="B72" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="33" t="s">
         <v>221</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3594,7 +3612,7 @@
       <c r="B73" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="34" t="s">
         <v>225</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3613,6 +3631,32 @@
         <v>226</v>
       </c>
       <c r="I73" s="32"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
+        <v>720</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3683,6 +3727,9 @@
     <hyperlink ref="B70" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
     <hyperlink ref="B72" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
     <hyperlink ref="B73" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C73" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C72" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B74" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="232">
   <si>
     <t>编号</t>
   </si>
@@ -707,6 +707,12 @@
   </si>
   <si>
     <t>①前缀树+深度优先搜索 ②前缀树+广度优先搜索 ③暴力搜索</t>
+  </si>
+  <si>
+    <t>单词搜索</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/word-search/</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1484,9 +1490,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1846,7 +1849,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3632,11 +3635,11 @@
       </c>
       <c r="I73" s="32"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" s="7" customFormat="1" spans="1:9">
       <c r="A74" s="1">
         <v>720</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="B74" s="9" t="s">
         <v>227</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -3657,6 +3660,34 @@
       <c r="H74" s="1" t="s">
         <v>229</v>
       </c>
+      <c r="I74" s="32"/>
+    </row>
+    <row r="75" s="7" customFormat="1" spans="1:9">
+      <c r="A75" s="1">
+        <v>79</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
@@ -3730,6 +3761,7 @@
     <hyperlink ref="C73" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
     <hyperlink ref="C72" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
     <hyperlink ref="B74" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B75" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$64</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="233">
   <si>
     <t>编号</t>
   </si>
@@ -424,10 +424,13 @@
     <t>https://leetcode-cn.com/problems/number-of-islands/</t>
   </si>
   <si>
-    <t>广度优先搜索</t>
-  </si>
-  <si>
-    <t>①广度优先搜索 ②深度优先搜索 ③并查集</t>
+    <t>搜索、并查集</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>①深度优先搜索 ②广度优先搜索 ③并查集</t>
   </si>
   <si>
     <t>反转链表</t>
@@ -896,7 +899,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -906,6 +909,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,6 +951,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1243,10 +1258,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1255,16 +1270,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1276,116 +1291,116 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1410,76 +1425,94 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1849,7 +1882,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -1858,15 +1891,15 @@
     <col min="4" max="4" width="6.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.5" style="1" customWidth="1"/>
     <col min="6" max="7" width="5.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.75" style="1" customWidth="1"/>
-    <col min="10" max="32" width="18.625" style="1" customWidth="1"/>
-    <col min="33" max="16352" width="28.125" style="1" customWidth="1"/>
-    <col min="16353" max="16383" width="18.625" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="18.625" style="1"/>
+    <col min="8" max="8" width="11.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="41.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.75" style="1" customWidth="1"/>
+    <col min="11" max="33" width="18.625" style="1" customWidth="1"/>
+    <col min="34" max="16353" width="28.125" style="1" customWidth="1"/>
+    <col min="16354" max="16384" width="18.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1888,220 +1921,228 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="7">
+    <row r="2" spans="1:10">
+      <c r="A2" s="8">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="7">
+      <c r="J2" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="8">
         <v>12</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8"/>
+      <c r="I3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="J3" s="22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="7">
-        <v>13</v>
-      </c>
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="8">
+        <v>13</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="7">
+      <c r="J4" s="22"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="8">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="7">
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="8">
         <v>153</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="7">
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="8">
         <v>154</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
-      <c r="A9" s="7" t="s">
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:10">
+      <c r="A9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="20"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:9">
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2119,44 +2160,45 @@
       <c r="G10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="4">
+    <row r="11" spans="1:10">
+      <c r="A11" s="5">
         <v>17</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="J11" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
+    <row r="12" s="1" customFormat="1" spans="1:9">
       <c r="A12" s="1">
         <v>26</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2174,15 +2216,15 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:8">
+    <row r="13" s="1" customFormat="1" spans="1:9">
       <c r="A13" s="1">
         <v>27</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2200,40 +2242,41 @@
       <c r="G13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="5">
+    <row r="14" spans="1:10">
+      <c r="A14" s="6">
         <v>35</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="F14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="22"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:9">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="25"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:10">
       <c r="A15" s="1">
         <v>46</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2251,16 +2294,16 @@
       <c r="G15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:9">
+      <c r="J15" s="26"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:10">
       <c r="A16" s="1">
         <v>47</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2278,16 +2321,16 @@
       <c r="G16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:9">
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:10">
       <c r="A17" s="1">
         <v>53</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2305,16 +2348,16 @@
       <c r="G17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="23"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="J17" s="27"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:10">
       <c r="A18" s="1">
         <v>54</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2332,16 +2375,16 @@
       <c r="G18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:9">
+      <c r="J18" s="28"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:10">
       <c r="A19" s="1">
         <v>59</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2359,16 +2402,16 @@
       <c r="G19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:9">
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:10">
       <c r="A20" s="1">
         <v>70</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2386,95 +2429,99 @@
       <c r="G20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="13"/>
+      <c r="I20" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:9">
-      <c r="A22" s="6">
+      <c r="J20" s="29"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:10">
+      <c r="A22" s="7">
         <v>74</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="25"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:9">
-      <c r="A23" s="4">
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:10">
+      <c r="A23" s="5">
         <v>82</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="26"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:9">
-      <c r="A24" s="4">
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="31"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:10">
+      <c r="A24" s="5">
         <v>83</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="I24" s="26"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:9">
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:10">
       <c r="A25" s="1">
         <v>102</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2492,16 +2539,16 @@
       <c r="G25" s="1">
         <v>1</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I25" s="23"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:8">
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>103</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2519,15 +2566,15 @@
       <c r="G26" s="1">
         <v>1</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:9">
+    <row r="27" s="1" customFormat="1" spans="1:10">
       <c r="A27" s="1">
         <v>104</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>95</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2545,16 +2592,16 @@
       <c r="G27" s="1">
         <v>1</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:9">
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:10">
       <c r="A28" s="1">
         <v>121</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -2572,16 +2619,16 @@
       <c r="G28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:9">
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:10">
       <c r="A29" s="1">
         <v>125</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>101</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2599,16 +2646,16 @@
       <c r="G29" s="1">
         <v>2</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:9">
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:10">
       <c r="A30" s="1">
         <v>131</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2626,16 +2673,16 @@
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I30" s="23"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:9">
+      <c r="J30" s="27"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:10">
       <c r="A31" s="1">
         <v>132</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="10" t="s">
         <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2653,16 +2700,16 @@
       <c r="G31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:9">
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:10">
       <c r="A32" s="1">
         <v>144</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="15" t="s">
         <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2680,91 +2727,94 @@
       <c r="G32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="23"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:9">
-      <c r="A33" s="3">
+      <c r="I32" s="28"/>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:10">
+      <c r="A33" s="4">
         <v>150</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I33" s="27"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="5">
+      <c r="J33" s="32"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="6">
         <v>190</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="F34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I34" s="22"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="3">
+      <c r="J34" s="25"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4">
         <v>191</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="F35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I35" s="28"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
+      <c r="J35" s="33"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:10">
       <c r="A36" s="17">
         <v>198</v>
       </c>
@@ -2786,74 +2836,79 @@
       <c r="G36" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="17"/>
+      <c r="I36" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="I36" s="29"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:9">
-      <c r="A37" s="5">
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:10">
+      <c r="A37" s="6">
         <v>199</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="F37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I37" s="30"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:9">
-      <c r="A38" s="5">
+      <c r="J37" s="35"/>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:10">
+      <c r="A38" s="19">
         <v>200</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H38" s="5" t="s">
+      <c r="F38" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I38" s="30"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:9">
+      <c r="H38" s="21">
+        <v>44301</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J38" s="36"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:10">
       <c r="A39" s="1">
         <v>206</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>137</v>
+      <c r="B39" s="15" t="s">
+        <v>138</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>23</v>
@@ -2867,24 +2922,24 @@
       <c r="G39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>225</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>139</v>
+      <c r="B40" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>13</v>
@@ -2892,20 +2947,20 @@
       <c r="G40" s="1">
         <v>2</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I40" s="15"/>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="1:9">
+      <c r="I40" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J40" s="28"/>
+    </row>
+    <row r="41" s="4" customFormat="1" spans="1:10">
       <c r="A41" s="1">
         <v>226</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>143</v>
+      <c r="B41" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>23</v>
@@ -2919,20 +2974,21 @@
       <c r="G41" s="1">
         <v>2</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I41" s="15"/>
-    </row>
-    <row r="42" s="3" customFormat="1" spans="1:9">
+      <c r="H41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J41" s="28"/>
+    </row>
+    <row r="42" s="4" customFormat="1" spans="1:10">
       <c r="A42" s="1">
         <v>227</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>146</v>
+      <c r="B42" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>11</v>
@@ -2946,26 +3002,27 @@
       <c r="G42" s="1">
         <v>2</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="1:9">
+      <c r="H42" s="1"/>
+      <c r="I42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" s="4" customFormat="1" spans="1:10">
       <c r="A43" s="1">
         <v>232</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>149</v>
+      <c r="B43" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -2973,76 +3030,79 @@
       <c r="G43" s="1">
         <v>2</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="4">
+      <c r="H43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="5">
         <v>235</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="B44" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="C44" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="4" t="s">
+      <c r="F44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I44" s="21" t="s">
+      <c r="H44" s="5"/>
+      <c r="I44" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J44" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" s="4" customFormat="1" spans="1:9">
-      <c r="A45" s="6">
+    <row r="45" s="5" customFormat="1" spans="1:10">
+      <c r="A45" s="7">
         <v>240</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="C45" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="6" t="s">
+      <c r="F45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="I45" s="31"/>
-    </row>
-    <row r="46" s="4" customFormat="1" spans="1:9">
+      <c r="H45" s="7"/>
+      <c r="I45" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J45" s="37"/>
+    </row>
+    <row r="46" s="5" customFormat="1" spans="1:10">
       <c r="A46" s="1">
         <v>303</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>158</v>
+      <c r="B46" s="10" t="s">
+        <v>159</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>23</v>
@@ -3056,20 +3116,21 @@
       <c r="G46" s="1">
         <v>1</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I46" s="32"/>
-    </row>
-    <row r="47" s="4" customFormat="1" spans="1:9">
+      <c r="H46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46" s="38"/>
+    </row>
+    <row r="47" s="5" customFormat="1" spans="1:10">
       <c r="A47" s="1">
         <v>304</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>161</v>
+      <c r="B47" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>11</v>
@@ -3083,20 +3144,21 @@
       <c r="G47" s="1">
         <v>1</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I47" s="32"/>
-    </row>
-    <row r="48" s="4" customFormat="1" spans="1:9">
+      <c r="H47" s="1"/>
+      <c r="I47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J47" s="38"/>
+    </row>
+    <row r="48" s="5" customFormat="1" spans="1:10">
       <c r="A48" s="1">
         <v>338</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>164</v>
+      <c r="B48" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>11</v>
@@ -3110,46 +3172,47 @@
       <c r="G48" s="1">
         <v>1</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I48" s="32"/>
-    </row>
-    <row r="49" s="4" customFormat="1" spans="1:9">
-      <c r="A49" s="4">
+      <c r="H48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J48" s="38"/>
+    </row>
+    <row r="49" s="5" customFormat="1" spans="1:10">
+      <c r="A49" s="5">
         <v>405</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C49" s="4" t="s">
+      <c r="B49" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="C49" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="4" t="s">
+      <c r="F49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I49" s="21" t="s">
+      <c r="I49" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="50" s="4" customFormat="1" spans="1:9">
+      <c r="J49" s="24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" s="5" customFormat="1" spans="1:10">
       <c r="A50" s="1">
         <v>474</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3158,22 +3221,23 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" s="5" customFormat="1" spans="1:9">
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" s="6" customFormat="1" spans="1:10">
       <c r="A51" s="1">
         <v>543</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
@@ -3181,49 +3245,51 @@
       <c r="G51" s="1">
         <v>1</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I51" s="32"/>
-    </row>
-    <row r="52" s="5" customFormat="1" spans="1:9">
-      <c r="A52" s="4">
+      <c r="H51" s="1"/>
+      <c r="I51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J51" s="38"/>
+    </row>
+    <row r="52" s="6" customFormat="1" spans="1:10">
+      <c r="A52" s="5">
         <v>617</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" s="4" t="s">
+      <c r="B52" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="C52" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="4" t="s">
+      <c r="F52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I52" s="21" t="s">
+      <c r="H52" s="5"/>
+      <c r="I52" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J52" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" s="5" customFormat="1" spans="1:9">
+    <row r="53" s="6" customFormat="1" spans="1:10">
       <c r="A53" s="1">
         <v>654</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>179</v>
+      <c r="B53" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>11</v>
@@ -3237,20 +3303,21 @@
       <c r="G53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" s="5" customFormat="1" spans="1:9">
+      <c r="H53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" s="6" customFormat="1" spans="1:10">
       <c r="A54" s="1">
         <v>824</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>182</v>
+      <c r="B54" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>23</v>
@@ -3264,20 +3331,21 @@
       <c r="G54" s="1">
         <v>1</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I54" s="32"/>
-    </row>
-    <row r="55" s="5" customFormat="1" spans="1:9">
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J54" s="38"/>
+    </row>
+    <row r="55" s="6" customFormat="1" spans="1:10">
       <c r="A55" s="1">
         <v>832</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>185</v>
+      <c r="B55" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
@@ -3291,26 +3359,27 @@
       <c r="G55" s="1">
         <v>1</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I55" s="15"/>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="1:9">
+      <c r="H55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J55" s="28"/>
+    </row>
+    <row r="56" s="7" customFormat="1" spans="1:10">
       <c r="A56" s="1">
         <v>867</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3318,26 +3387,27 @@
       <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="1:9">
+      <c r="H56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" s="7" customFormat="1" spans="1:10">
       <c r="A57" s="1">
         <v>868</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>192</v>
+      <c r="B57" s="10" t="s">
+        <v>193</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3345,26 +3415,27 @@
       <c r="G57" s="1">
         <v>1</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I57" s="32"/>
-    </row>
-    <row r="58" s="7" customFormat="1" spans="1:9">
+      <c r="H57" s="1"/>
+      <c r="I57" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J57" s="38"/>
+    </row>
+    <row r="58" s="8" customFormat="1" spans="1:10">
       <c r="A58" s="1">
         <v>997</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>195</v>
+      <c r="B58" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3372,22 +3443,23 @@
       <c r="G58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="59" s="7" customFormat="1" spans="1:9">
+      <c r="J58" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" s="8" customFormat="1" spans="1:10">
       <c r="A59" s="1">
         <v>998</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>200</v>
+      <c r="B59" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>11</v>
@@ -3401,22 +3473,23 @@
       <c r="G59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>181</v>
-      </c>
+      <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="60" s="7" customFormat="1" spans="1:9">
+        <v>182</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" s="8" customFormat="1" spans="1:10">
       <c r="A60" s="1">
         <v>999</v>
       </c>
-      <c r="B60" s="9" t="s">
-        <v>202</v>
+      <c r="B60" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
@@ -3430,26 +3503,27 @@
       <c r="G60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I60" s="15"/>
-    </row>
-    <row r="61" s="7" customFormat="1" spans="1:9">
+      <c r="J60" s="28"/>
+    </row>
+    <row r="61" s="8" customFormat="1" spans="1:10">
       <c r="A61" s="1">
         <v>1047</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>204</v>
+      <c r="B61" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3457,26 +3531,27 @@
       <c r="G61" s="1">
         <v>2</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I61" s="15"/>
-    </row>
-    <row r="62" s="7" customFormat="1" spans="1:9">
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J61" s="28"/>
+    </row>
+    <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
         <v>1052</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>207</v>
+      <c r="B62" s="10" t="s">
+        <v>208</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3484,20 +3559,21 @@
       <c r="G62" s="1">
         <v>1</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I62" s="32"/>
-    </row>
-    <row r="63" s="7" customFormat="1" spans="1:9">
+      <c r="H62" s="1"/>
+      <c r="I62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J62" s="38"/>
+    </row>
+    <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
         <v>1603</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>211</v>
+      <c r="B63" s="10" t="s">
+        <v>212</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
@@ -3511,12 +3587,13 @@
       <c r="G63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="1"/>
+      <c r="I63" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="32"/>
-    </row>
-    <row r="64" s="7" customFormat="1" spans="1:9">
+      <c r="J63" s="38"/>
+    </row>
+    <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3526,16 +3603,17 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-    </row>
-    <row r="70" s="7" customFormat="1" spans="1:9">
+      <c r="J64" s="1"/>
+    </row>
+    <row r="70" s="8" customFormat="1" spans="1:10">
       <c r="A70" s="1">
         <v>289</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>213</v>
+      <c r="B70" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>11</v>
@@ -3547,22 +3625,23 @@
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H70" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I70" s="32"/>
-    </row>
-    <row r="71" s="7" customFormat="1" spans="1:9">
+      <c r="H70" s="1"/>
+      <c r="I70" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J70" s="38"/>
+    </row>
+    <row r="71" s="8" customFormat="1" spans="1:10">
       <c r="A71" s="1">
         <v>73</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>217</v>
+      <c r="B71" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>11</v>
@@ -3574,103 +3653,107 @@
         <v>13</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I71" s="32"/>
-    </row>
-    <row r="72" s="7" customFormat="1" spans="1:9">
+        <v>216</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J71" s="38"/>
+    </row>
+    <row r="72" s="8" customFormat="1" spans="1:10">
       <c r="A72" s="1">
         <v>208</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="33" t="s">
+      <c r="B72" s="10" t="s">
         <v>221</v>
+      </c>
+      <c r="C72" s="39" t="s">
+        <v>222</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="I72" s="32"/>
-    </row>
-    <row r="73" s="7" customFormat="1" spans="1:9">
+        <v>216</v>
+      </c>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J72" s="38"/>
+    </row>
+    <row r="73" s="8" customFormat="1" spans="1:10">
       <c r="A73" s="1">
         <v>648</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C73" s="34" t="s">
+      <c r="B73" s="10" t="s">
         <v>225</v>
+      </c>
+      <c r="C73" s="40" t="s">
+        <v>226</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I73" s="32"/>
-    </row>
-    <row r="74" s="7" customFormat="1" spans="1:9">
+        <v>216</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J73" s="38"/>
+    </row>
+    <row r="74" s="8" customFormat="1" spans="1:10">
       <c r="A74" s="1">
         <v>720</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>227</v>
+      <c r="B74" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I74" s="32"/>
-    </row>
-    <row r="75" s="7" customFormat="1" spans="1:9">
+        <v>216</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J74" s="38"/>
+    </row>
+    <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
         <v>79</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>230</v>
+      <c r="B75" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
@@ -3682,16 +3765,17 @@
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H75" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I75" s="32"/>
+      <c r="J75" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64">
-    <sortState ref="A1:I64">
+  <autoFilter ref="A1:J64">
+    <sortState ref="A1:J64">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="237">
   <si>
     <t>编号</t>
   </si>
@@ -431,6 +431,18 @@
   </si>
   <si>
     <t>①深度优先搜索 ②广度优先搜索 ③并查集</t>
+  </si>
+  <si>
+    <t>岛屿的周长</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/island-perimeter/</t>
+  </si>
+  <si>
+    <t>搜索</t>
+  </si>
+  <si>
+    <t>①遍历 ②深度优先搜索 ③广度优先搜索</t>
   </si>
   <si>
     <t>反转链表</t>
@@ -1882,7 +1894,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2900,61 +2912,64 @@
       </c>
       <c r="J38" s="36"/>
     </row>
-    <row r="39" s="1" customFormat="1" spans="1:10">
-      <c r="A39" s="1">
+    <row r="39" s="3" customFormat="1" spans="1:10">
+      <c r="A39" s="19">
+        <v>463</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="21">
+        <v>44301</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J39" s="36"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:10">
+      <c r="A40" s="1">
         <v>206</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="1">
-        <v>225</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>140</v>
+      <c r="B40" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="1">
-        <v>2</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="G40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="28"/>
       <c r="J40" s="28"/>
     </row>
-    <row r="41" s="4" customFormat="1" spans="1:10">
+    <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>144</v>
@@ -2966,7 +2981,7 @@
         <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>13</v>
@@ -2974,27 +2989,26 @@
       <c r="G41" s="1">
         <v>2</v>
       </c>
-      <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J41" s="28"/>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:10">
       <c r="A42" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>13</v>
@@ -3004,25 +3018,25 @@
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J42" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="J42" s="28"/>
     </row>
     <row r="43" s="4" customFormat="1" spans="1:10">
       <c r="A43" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -3032,108 +3046,108 @@
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="5">
+    <row r="44" s="4" customFormat="1" spans="1:10">
+      <c r="A44" s="1">
+        <v>232</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="5">
         <v>235</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="B45" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="F45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J44" s="24" t="s">
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J45" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="1" spans="1:10">
-      <c r="A45" s="7">
+    <row r="46" s="5" customFormat="1" spans="1:10">
+      <c r="A46" s="7">
         <v>240</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D45" s="7" t="s">
+      <c r="B46" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E46" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="7" t="s">
+      <c r="F46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" s="37"/>
-    </row>
-    <row r="46" s="5" customFormat="1" spans="1:10">
-      <c r="A46" s="1">
-        <v>303</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J46" s="38"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J46" s="37"/>
     </row>
     <row r="47" s="5" customFormat="1" spans="1:10">
       <c r="A47" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>99</v>
@@ -3146,19 +3160,19 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J47" s="38"/>
     </row>
     <row r="48" s="5" customFormat="1" spans="1:10">
       <c r="A48" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>11</v>
@@ -3174,184 +3188,184 @@
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J48" s="38"/>
     </row>
     <row r="49" s="5" customFormat="1" spans="1:10">
-      <c r="A49" s="5">
+      <c r="A49" s="1">
+        <v>338</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J49" s="38"/>
+    </row>
+    <row r="50" s="5" customFormat="1" spans="1:10">
+      <c r="A50" s="5">
         <v>405</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="B50" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="5" t="s">
+      <c r="F50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J49" s="24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" s="5" customFormat="1" spans="1:10">
-      <c r="A50" s="1">
+      <c r="I50" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J50" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" s="5" customFormat="1" spans="1:10">
+      <c r="A51" s="1">
         <v>474</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" s="6" customFormat="1" spans="1:10">
-      <c r="A51" s="1">
+      <c r="B51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" s="6" customFormat="1" spans="1:10">
+      <c r="A52" s="1">
         <v>543</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="B52" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1">
+      <c r="E52" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1">
         <v>1</v>
       </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J51" s="38"/>
-    </row>
-    <row r="52" s="6" customFormat="1" spans="1:10">
-      <c r="A52" s="5">
+      <c r="H52" s="1"/>
+      <c r="I52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="38"/>
+    </row>
+    <row r="53" s="6" customFormat="1" spans="1:10">
+      <c r="A53" s="5">
         <v>617</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="B53" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="5" t="s">
+      <c r="F53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J52" s="24" t="s">
+      <c r="H53" s="5"/>
+      <c r="I53" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J53" s="24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="1:10">
-      <c r="A53" s="1">
-        <v>654</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J53" s="1"/>
     </row>
     <row r="54" s="6" customFormat="1" spans="1:10">
       <c r="A54" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="1">
-        <v>1</v>
+      <c r="G54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J54" s="38"/>
+        <v>186</v>
+      </c>
+      <c r="J54" s="1"/>
     </row>
     <row r="55" s="6" customFormat="1" spans="1:10">
       <c r="A55" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>13</v>
@@ -3361,25 +3375,25 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J55" s="28"/>
-    </row>
-    <row r="56" s="7" customFormat="1" spans="1:10">
+        <v>189</v>
+      </c>
+      <c r="J55" s="38"/>
+    </row>
+    <row r="56" s="6" customFormat="1" spans="1:10">
       <c r="A56" s="1">
-        <v>867</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>189</v>
+        <v>832</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3391,13 +3405,13 @@
       <c r="I56" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J56" s="1"/>
+      <c r="J56" s="28"/>
     </row>
     <row r="57" s="7" customFormat="1" spans="1:10">
       <c r="A57" s="1">
-        <v>868</v>
-      </c>
-      <c r="B57" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -3407,7 +3421,7 @@
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3417,55 +3431,53 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J57" s="38"/>
-    </row>
-    <row r="58" s="8" customFormat="1" spans="1:10">
+        <v>196</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" s="7" customFormat="1" spans="1:10">
       <c r="A58" s="1">
-        <v>997</v>
+        <v>868</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>42</v>
+      <c r="G58" s="1">
+        <v>1</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="J58" s="38"/>
     </row>
     <row r="59" s="8" customFormat="1" spans="1:10">
       <c r="A59" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3475,27 +3487,27 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" s="8" customFormat="1" spans="1:10">
       <c r="A60" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3505,69 +3517,71 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="28"/>
+        <v>186</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="61" s="8" customFormat="1" spans="1:10">
       <c r="A61" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="1">
-        <v>2</v>
+      <c r="G61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="J61" s="28"/>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J62" s="38"/>
+      <c r="J62" s="28"/>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>212</v>
@@ -3576,66 +3590,66 @@
         <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>42</v>
+      <c r="G63" s="1">
+        <v>1</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J63" s="38"/>
+    </row>
+    <row r="64" s="8" customFormat="1" spans="1:10">
+      <c r="A64" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J63" s="38"/>
-    </row>
-    <row r="64" s="8" customFormat="1" spans="1:10">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-    </row>
-    <row r="70" s="8" customFormat="1" spans="1:10">
-      <c r="A70" s="1">
-        <v>289</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J70" s="38"/>
+      <c r="J64" s="38"/>
+    </row>
+    <row r="65" s="8" customFormat="1" spans="1:10">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
     </row>
     <row r="71" s="8" customFormat="1" spans="1:10">
       <c r="A71" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>218</v>
@@ -3653,35 +3667,35 @@
         <v>13</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J71" s="38"/>
     </row>
     <row r="72" s="8" customFormat="1" spans="1:10">
       <c r="A72" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C72" s="39" t="s">
         <v>222</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
@@ -3691,118 +3705,146 @@
     </row>
     <row r="73" s="8" customFormat="1" spans="1:10">
       <c r="A73" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="39" t="s">
         <v>226</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J73" s="38"/>
     </row>
     <row r="74" s="8" customFormat="1" spans="1:10">
       <c r="A74" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C74" s="1" t="s">
         <v>229</v>
       </c>
+      <c r="C74" s="40" t="s">
+        <v>230</v>
+      </c>
       <c r="D74" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J74" s="38"/>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J75" s="38"/>
+    </row>
+    <row r="76" s="8" customFormat="1" spans="1:10">
+      <c r="A76" s="1">
+        <v>79</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J75" s="38"/>
+      <c r="J76" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J64">
-    <sortState ref="A1:J64">
+  <autoFilter ref="A1:J65">
+    <sortState ref="A1:J65">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B62" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B55" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B54" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C51" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C56" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B57" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B46" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B47" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B63" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B56" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B55" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C52" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C57" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B58" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B47" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B48" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
     <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
     <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B48" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B49" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B43" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B44" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B61" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B62" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B42" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B41" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B40" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B43" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B42" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B41" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
@@ -3811,19 +3853,19 @@
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
     <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B39" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B40" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
     <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B63" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B60" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B53" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B59" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B64" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B61" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B54" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B60" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B71" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B72" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B49" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B44" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B52" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B50" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B45" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B53" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
     <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
@@ -3833,19 +3875,20 @@
     <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B45" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B46" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B70" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B72" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B73" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C73" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C72" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B74" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B75" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B71" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B73" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B74" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C74" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C73" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B75" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B76" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B39" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$66</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="240">
   <si>
     <t>编号</t>
   </si>
@@ -442,7 +442,16 @@
     <t>搜索</t>
   </si>
   <si>
-    <t>①遍历 ②深度优先搜索 ③广度优先搜索</t>
+    <t>①基本遍历 ②深度优先搜索 ③广度优先搜索</t>
+  </si>
+  <si>
+    <t>岛屿的最大面积</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/max-area-of-island/</t>
+  </si>
+  <si>
+    <t>①深度优先搜索 ②广度优先搜索</t>
   </si>
   <si>
     <t>反转链表</t>
@@ -1894,7 +1903,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2942,73 +2951,76 @@
       </c>
       <c r="J39" s="36"/>
     </row>
-    <row r="40" s="1" customFormat="1" spans="1:10">
-      <c r="A40" s="1">
+    <row r="40" s="3" customFormat="1" spans="1:10">
+      <c r="A40" s="19">
+        <v>695</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" s="21">
+        <v>44301</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J40" s="36"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:10">
+      <c r="A41" s="1">
         <v>206</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="1">
-        <v>225</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>144</v>
+      <c r="B41" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="1">
-        <v>2</v>
-      </c>
-      <c r="I41" s="1" t="s">
+      <c r="G41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1">
+        <v>225</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J41" s="28"/>
-    </row>
-    <row r="42" s="4" customFormat="1" spans="1:10">
-      <c r="A42" s="1">
-        <v>226</v>
-      </c>
-      <c r="B42" s="10" t="s">
+      <c r="C42" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>13</v>
@@ -3016,7 +3028,6 @@
       <c r="G42" s="1">
         <v>2</v>
       </c>
-      <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
         <v>150</v>
       </c>
@@ -3024,7 +3035,7 @@
     </row>
     <row r="43" s="4" customFormat="1" spans="1:10">
       <c r="A43" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>151</v>
@@ -3033,10 +3044,10 @@
         <v>152</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -3048,11 +3059,11 @@
       <c r="I43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J43" s="1"/>
+      <c r="J43" s="28"/>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:10">
       <c r="A44" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>154</v>
@@ -3061,10 +3072,10 @@
         <v>155</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>13</v>
@@ -3074,99 +3085,99 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="5">
+    <row r="45" s="4" customFormat="1" spans="1:10">
+      <c r="A45" s="1">
+        <v>232</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="5">
         <v>235</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="B46" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="F46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J45" s="24" t="s">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J46" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" s="5" customFormat="1" spans="1:10">
-      <c r="A46" s="7">
+    <row r="47" s="5" customFormat="1" spans="1:10">
+      <c r="A47" s="7">
         <v>240</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="B47" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E47" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="F47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="J46" s="37"/>
-    </row>
-    <row r="47" s="5" customFormat="1" spans="1:10">
-      <c r="A47" s="1">
-        <v>303</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1" t="s">
+      <c r="H47" s="7"/>
+      <c r="I47" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J47" s="38"/>
+      <c r="J47" s="37"/>
     </row>
     <row r="48" s="5" customFormat="1" spans="1:10">
       <c r="A48" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>166</v>
@@ -3175,7 +3186,7 @@
         <v>167</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>99</v>
@@ -3194,7 +3205,7 @@
     </row>
     <row r="49" s="5" customFormat="1" spans="1:10">
       <c r="A49" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>169</v>
@@ -3221,139 +3232,139 @@
       <c r="J49" s="38"/>
     </row>
     <row r="50" s="5" customFormat="1" spans="1:10">
-      <c r="A50" s="5">
+      <c r="A50" s="1">
+        <v>338</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J50" s="38"/>
+    </row>
+    <row r="51" s="5" customFormat="1" spans="1:10">
+      <c r="A51" s="5">
         <v>405</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="B51" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="F51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="51" s="5" customFormat="1" spans="1:10">
-      <c r="A51" s="1">
+      <c r="I51" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:10">
+      <c r="A52" s="1">
         <v>474</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" s="6" customFormat="1" spans="1:10">
-      <c r="A52" s="1">
+      <c r="B52" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" s="6" customFormat="1" spans="1:10">
+      <c r="A53" s="1">
         <v>543</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="B53" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="1">
+      <c r="E53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="1">
         <v>1</v>
       </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J52" s="38"/>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="1:10">
-      <c r="A53" s="5">
+      <c r="H53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J53" s="38"/>
+    </row>
+    <row r="54" s="6" customFormat="1" spans="1:10">
+      <c r="A54" s="5">
         <v>617</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="B54" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="5" t="s">
+      <c r="F54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="J53" s="24" t="s">
+      <c r="H54" s="5"/>
+      <c r="I54" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J54" s="24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="54" s="6" customFormat="1" spans="1:10">
-      <c r="A54" s="1">
-        <v>654</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J54" s="1"/>
     </row>
     <row r="55" s="6" customFormat="1" spans="1:10">
       <c r="A55" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>187</v>
@@ -3362,26 +3373,26 @@
         <v>188</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="1">
-        <v>1</v>
+      <c r="G55" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J55" s="38"/>
+      <c r="J55" s="1"/>
     </row>
     <row r="56" s="6" customFormat="1" spans="1:10">
       <c r="A56" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>190</v>
@@ -3393,7 +3404,7 @@
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3405,13 +3416,13 @@
       <c r="I56" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J56" s="28"/>
-    </row>
-    <row r="57" s="7" customFormat="1" spans="1:10">
+      <c r="J56" s="38"/>
+    </row>
+    <row r="57" s="6" customFormat="1" spans="1:10">
       <c r="A57" s="1">
-        <v>867</v>
-      </c>
-      <c r="B57" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>193</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -3421,7 +3432,7 @@
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3431,25 +3442,25 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J57" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="J57" s="28"/>
     </row>
     <row r="58" s="7" customFormat="1" spans="1:10">
       <c r="A58" s="1">
-        <v>868</v>
-      </c>
-      <c r="B58" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3461,11 +3472,11 @@
       <c r="I58" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J58" s="38"/>
-    </row>
-    <row r="59" s="8" customFormat="1" spans="1:10">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" s="7" customFormat="1" spans="1:10">
       <c r="A59" s="1">
-        <v>997</v>
+        <v>868</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>200</v>
@@ -3477,37 +3488,35 @@
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>42</v>
+      <c r="G59" s="1">
+        <v>1</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>204</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="J59" s="38"/>
     </row>
     <row r="60" s="8" customFormat="1" spans="1:10">
       <c r="A60" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3517,27 +3526,27 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" s="8" customFormat="1" spans="1:10">
       <c r="A61" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3547,41 +3556,43 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="28"/>
+        <v>189</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="1">
-        <v>2</v>
+      <c r="G62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="J62" s="28"/>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>212</v>
@@ -3590,100 +3601,100 @@
         <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J63" s="38"/>
+        <v>214</v>
+      </c>
+      <c r="J63" s="28"/>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>42</v>
+      <c r="G64" s="1">
+        <v>1</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J64" s="38"/>
+    </row>
+    <row r="65" s="8" customFormat="1" spans="1:10">
+      <c r="A65" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J64" s="38"/>
-    </row>
-    <row r="65" s="8" customFormat="1" spans="1:10">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-    </row>
-    <row r="71" s="8" customFormat="1" spans="1:10">
-      <c r="A71" s="1">
-        <v>289</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J71" s="38"/>
+      <c r="J65" s="38"/>
+    </row>
+    <row r="66" s="8" customFormat="1" spans="1:10">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
     </row>
     <row r="72" s="8" customFormat="1" spans="1:10">
       <c r="A72" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B72" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>11</v>
@@ -3695,7 +3706,7 @@
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
@@ -3705,53 +3716,53 @@
     </row>
     <row r="73" s="8" customFormat="1" spans="1:10">
       <c r="A73" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C73" s="39" t="s">
+      <c r="C73" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>227</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J73" s="38"/>
     </row>
     <row r="74" s="8" customFormat="1" spans="1:10">
       <c r="A74" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C74" s="39" t="s">
         <v>229</v>
-      </c>
-      <c r="C74" s="40" t="s">
-        <v>230</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
@@ -3761,25 +3772,25 @@
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="40" t="s">
         <v>233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
@@ -3789,7 +3800,7 @@
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>235</v>
@@ -3798,53 +3809,81 @@
         <v>236</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J76" s="38"/>
+    </row>
+    <row r="77" s="8" customFormat="1" spans="1:10">
+      <c r="A77" s="1">
+        <v>79</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J76" s="38"/>
+      <c r="J77" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J65">
-    <sortState ref="A1:J65">
+  <autoFilter ref="A1:J66">
+    <sortState ref="A1:J66">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B63" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B56" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B55" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C52" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C57" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B58" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B47" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B48" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B64" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B57" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B56" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C53" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C58" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B59" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B48" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B49" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
     <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
     <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B49" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B50" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B44" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B45" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B62" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B63" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B43" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B42" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B41" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B44" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B43" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B42" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
@@ -3853,19 +3892,19 @@
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
     <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B40" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B41" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
     <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B64" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B61" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B54" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B60" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B65" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B62" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B55" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B61" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B72" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B73" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B50" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B45" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B53" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B51" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B46" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B54" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
     <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
@@ -3875,20 +3914,21 @@
     <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B46" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B47" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B71" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B73" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B74" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C74" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C73" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B75" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B76" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B72" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B74" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B75" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C75" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C74" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B76" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B77" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
     <hyperlink ref="B39" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
+    <hyperlink ref="B40" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="242">
   <si>
     <t>编号</t>
   </si>
@@ -452,6 +452,12 @@
   </si>
   <si>
     <t>①深度优先搜索 ②广度优先搜索</t>
+  </si>
+  <si>
+    <t>最大人工岛</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/making-a-large-island/</t>
   </si>
   <si>
     <t>反转链表</t>
@@ -1903,7 +1909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2981,36 +2987,41 @@
       </c>
       <c r="J40" s="36"/>
     </row>
-    <row r="41" s="1" customFormat="1" spans="1:10">
-      <c r="A41" s="1">
+    <row r="41" s="3" customFormat="1" spans="1:10">
+      <c r="A41" s="19">
+        <v>827</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="21">
+        <v>44302</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="36"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:10">
+      <c r="A42" s="1">
         <v>206</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="1">
-        <v>225</v>
-      </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -3020,34 +3031,32 @@
         <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1">
+        <v>225</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="I42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="J42" s="28"/>
-    </row>
-    <row r="43" s="4" customFormat="1" spans="1:10">
-      <c r="A43" s="1">
-        <v>226</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>13</v>
@@ -3055,27 +3064,26 @@
       <c r="G43" s="1">
         <v>2</v>
       </c>
-      <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J43" s="28"/>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:10">
       <c r="A44" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B44" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="D44" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>13</v>
@@ -3085,25 +3093,25 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J44" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="J44" s="28"/>
     </row>
     <row r="45" s="4" customFormat="1" spans="1:10">
       <c r="A45" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
@@ -3113,108 +3121,108 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="5">
+    <row r="46" s="4" customFormat="1" spans="1:10">
+      <c r="A46" s="1">
+        <v>232</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="5">
         <v>235</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="B47" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="F47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J46" s="24" t="s">
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J47" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" s="5" customFormat="1" spans="1:10">
-      <c r="A47" s="7">
+    <row r="48" s="5" customFormat="1" spans="1:10">
+      <c r="A48" s="7">
         <v>240</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="7" t="s">
+      <c r="B48" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E48" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="F48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="J47" s="37"/>
-    </row>
-    <row r="48" s="5" customFormat="1" spans="1:10">
-      <c r="A48" s="1">
-        <v>303</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="H48" s="7"/>
+      <c r="I48" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J48" s="38"/>
+      <c r="J48" s="37"/>
     </row>
     <row r="49" s="5" customFormat="1" spans="1:10">
       <c r="A49" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="D49" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>99</v>
@@ -3227,19 +3235,19 @@
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J49" s="38"/>
     </row>
     <row r="50" s="5" customFormat="1" spans="1:10">
       <c r="A50" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>11</v>
@@ -3255,184 +3263,184 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J50" s="38"/>
+    </row>
+    <row r="51" s="5" customFormat="1" spans="1:10">
+      <c r="A51" s="1">
+        <v>338</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="J50" s="38"/>
-    </row>
-    <row r="51" s="5" customFormat="1" spans="1:10">
-      <c r="A51" s="5">
+      <c r="C51" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J51" s="38"/>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:10">
+      <c r="A52" s="5">
         <v>405</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="B52" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="5" t="s">
+      <c r="F52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" s="5" customFormat="1" spans="1:10">
-      <c r="A52" s="1">
+      <c r="I52" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J52" s="24" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" s="5" customFormat="1" spans="1:10">
+      <c r="A53" s="1">
         <v>474</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="1:10">
-      <c r="A53" s="1">
+      <c r="B53" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" s="6" customFormat="1" spans="1:10">
+      <c r="A54" s="1">
         <v>543</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="B54" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="1">
+      <c r="E54" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="1">
         <v>1</v>
       </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="J53" s="38"/>
-    </row>
-    <row r="54" s="6" customFormat="1" spans="1:10">
-      <c r="A54" s="5">
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J54" s="38"/>
+    </row>
+    <row r="55" s="6" customFormat="1" spans="1:10">
+      <c r="A55" s="5">
         <v>617</v>
       </c>
-      <c r="B54" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="B55" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="F55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J54" s="24" t="s">
+      <c r="H55" s="5"/>
+      <c r="I55" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J55" s="24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="1:10">
-      <c r="A55" s="1">
-        <v>654</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J55" s="1"/>
     </row>
     <row r="56" s="6" customFormat="1" spans="1:10">
       <c r="A56" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B56" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="D56" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="1">
-        <v>1</v>
+      <c r="G56" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J56" s="38"/>
+        <v>191</v>
+      </c>
+      <c r="J56" s="1"/>
     </row>
     <row r="57" s="6" customFormat="1" spans="1:10">
       <c r="A57" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3442,25 +3450,25 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J57" s="38"/>
+    </row>
+    <row r="58" s="6" customFormat="1" spans="1:10">
+      <c r="A58" s="1">
+        <v>832</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="J57" s="28"/>
-    </row>
-    <row r="58" s="7" customFormat="1" spans="1:10">
-      <c r="A58" s="1">
-        <v>867</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3470,25 +3478,25 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J58" s="1"/>
+        <v>197</v>
+      </c>
+      <c r="J58" s="28"/>
     </row>
     <row r="59" s="7" customFormat="1" spans="1:10">
       <c r="A59" s="1">
-        <v>868</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>200</v>
+        <v>867</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3498,55 +3506,53 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" s="7" customFormat="1" spans="1:10">
+      <c r="A60" s="1">
+        <v>868</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="J59" s="38"/>
-    </row>
-    <row r="60" s="8" customFormat="1" spans="1:10">
-      <c r="A60" s="1">
-        <v>997</v>
-      </c>
-      <c r="B60" s="10" t="s">
+      <c r="C60" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>42</v>
+      <c r="G60" s="1">
+        <v>1</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>207</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="J60" s="38"/>
     </row>
     <row r="61" s="8" customFormat="1" spans="1:10">
       <c r="A61" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3556,15 +3562,15 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>210</v>
@@ -3573,10 +3579,10 @@
         <v>211</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3586,13 +3592,15 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="28"/>
+        <v>191</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>212</v>
@@ -3604,125 +3612,125 @@
         <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="1">
-        <v>2</v>
+      <c r="G63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>214</v>
+        <v>24</v>
       </c>
       <c r="J63" s="28"/>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J64" s="38"/>
+        <v>216</v>
+      </c>
+      <c r="J64" s="28"/>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
       <c r="A65" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>42</v>
+      <c r="G65" s="1">
+        <v>1</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J65" s="38"/>
+    </row>
+    <row r="66" s="8" customFormat="1" spans="1:10">
+      <c r="A66" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J65" s="38"/>
-    </row>
-    <row r="66" s="8" customFormat="1" spans="1:10">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-    </row>
-    <row r="72" s="8" customFormat="1" spans="1:10">
-      <c r="A72" s="1">
-        <v>289</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J72" s="38"/>
+      <c r="J66" s="38"/>
+    </row>
+    <row r="67" s="8" customFormat="1" spans="1:10">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
     </row>
     <row r="73" s="8" customFormat="1" spans="1:10">
       <c r="A73" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>11</v>
@@ -3734,156 +3742,184 @@
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J73" s="38"/>
     </row>
     <row r="74" s="8" customFormat="1" spans="1:10">
       <c r="A74" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C74" s="39" t="s">
-        <v>229</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J74" s="38"/>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C75" s="40" t="s">
-        <v>233</v>
+        <v>230</v>
+      </c>
+      <c r="C75" s="39" t="s">
+        <v>231</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J75" s="38"/>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C76" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J76" s="38"/>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:10">
       <c r="A77" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B77" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J77" s="38"/>
+    </row>
+    <row r="78" s="8" customFormat="1" spans="1:10">
+      <c r="A78" s="1">
+        <v>79</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J77" s="38"/>
+      <c r="J78" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J66">
-    <sortState ref="A1:J66">
+  <autoFilter ref="A1:J67">
+    <sortState ref="A1:J67">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B64" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B57" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B56" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C53" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C58" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B59" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B48" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B49" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B65" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B58" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B57" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C54" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C59" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B60" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B49" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B50" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
     <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
     <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B50" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B51" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B45" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B46" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B63" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B64" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B44" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B43" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B42" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B45" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B44" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B43" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
@@ -3892,19 +3928,19 @@
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
     <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B41" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B42" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
     <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B65" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B62" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B55" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B61" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B66" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B63" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B56" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B62" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B73" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B74" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B51" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B46" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B54" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B52" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B47" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B55" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
     <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
@@ -3914,21 +3950,22 @@
     <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B47" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B48" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B72" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B74" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B75" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C75" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C74" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B76" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B77" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B73" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B75" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B76" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C76" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C75" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B77" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B78" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
     <hyperlink ref="B39" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
     <hyperlink ref="B40" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
+    <hyperlink ref="B41" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$68</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="244">
   <si>
     <t>编号</t>
   </si>
@@ -458,6 +458,12 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/making-a-large-island/</t>
+  </si>
+  <si>
+    <t>被围绕的区域</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/surrounded-regions/</t>
   </si>
   <si>
     <t>反转链表</t>
@@ -1909,7 +1915,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -3017,36 +3023,41 @@
       </c>
       <c r="J41" s="36"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:10">
-      <c r="A42" s="1">
+    <row r="42" s="3" customFormat="1" spans="1:10">
+      <c r="A42" s="19">
+        <v>130</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="21">
+        <v>44302</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="36"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:10">
+      <c r="A43" s="1">
         <v>206</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="1">
-        <v>225</v>
-      </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="15" t="s">
         <v>149</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -3056,34 +3067,32 @@
         <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1">
+        <v>225</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2</v>
-      </c>
-      <c r="I43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="J43" s="28"/>
-    </row>
-    <row r="44" s="4" customFormat="1" spans="1:10">
-      <c r="A44" s="1">
-        <v>226</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>13</v>
@@ -3091,27 +3100,26 @@
       <c r="G44" s="1">
         <v>2</v>
       </c>
-      <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J44" s="28"/>
     </row>
     <row r="45" s="4" customFormat="1" spans="1:10">
       <c r="A45" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
@@ -3121,25 +3129,25 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="J45" s="28"/>
     </row>
     <row r="46" s="4" customFormat="1" spans="1:10">
       <c r="A46" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3149,108 +3157,108 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="5">
+    <row r="47" s="4" customFormat="1" spans="1:10">
+      <c r="A47" s="1">
+        <v>232</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="5">
         <v>235</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="B48" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="5" t="s">
+      <c r="F48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J47" s="24" t="s">
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J48" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" s="5" customFormat="1" spans="1:10">
-      <c r="A48" s="7">
+    <row r="49" s="5" customFormat="1" spans="1:10">
+      <c r="A49" s="7">
         <v>240</v>
       </c>
-      <c r="B48" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="B49" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E49" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="F49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J48" s="37"/>
-    </row>
-    <row r="49" s="5" customFormat="1" spans="1:10">
-      <c r="A49" s="1">
-        <v>303</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="H49" s="7"/>
+      <c r="I49" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J49" s="38"/>
+      <c r="J49" s="37"/>
     </row>
     <row r="50" s="5" customFormat="1" spans="1:10">
       <c r="A50" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="D50" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>99</v>
@@ -3263,19 +3271,19 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J50" s="38"/>
     </row>
     <row r="51" s="5" customFormat="1" spans="1:10">
       <c r="A51" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>11</v>
@@ -3291,184 +3299,184 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J51" s="38"/>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="1:10">
+      <c r="A52" s="1">
+        <v>338</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="J51" s="38"/>
-    </row>
-    <row r="52" s="5" customFormat="1" spans="1:10">
-      <c r="A52" s="5">
+      <c r="C52" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J52" s="38"/>
+    </row>
+    <row r="53" s="5" customFormat="1" spans="1:10">
+      <c r="A53" s="5">
         <v>405</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="B53" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="5" t="s">
+      <c r="F53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J52" s="24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53" s="5" customFormat="1" spans="1:10">
-      <c r="A53" s="1">
+      <c r="I53" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J53" s="24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:10">
+      <c r="A54" s="1">
         <v>474</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" s="6" customFormat="1" spans="1:10">
-      <c r="A54" s="1">
+      <c r="B54" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" s="6" customFormat="1" spans="1:10">
+      <c r="A55" s="1">
         <v>543</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="B55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="E55" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1">
         <v>1</v>
       </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J54" s="38"/>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="1:10">
-      <c r="A55" s="5">
+      <c r="H55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J55" s="38"/>
+    </row>
+    <row r="56" s="6" customFormat="1" spans="1:10">
+      <c r="A56" s="5">
         <v>617</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="B56" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="F56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="J55" s="24" t="s">
+      <c r="H56" s="5"/>
+      <c r="I56" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J56" s="24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="1:10">
-      <c r="A56" s="1">
-        <v>654</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J56" s="1"/>
     </row>
     <row r="57" s="6" customFormat="1" spans="1:10">
       <c r="A57" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="1">
-        <v>1</v>
+      <c r="G57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J57" s="38"/>
+        <v>193</v>
+      </c>
+      <c r="J57" s="1"/>
     </row>
     <row r="58" s="6" customFormat="1" spans="1:10">
       <c r="A58" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3478,25 +3486,25 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J58" s="38"/>
+    </row>
+    <row r="59" s="6" customFormat="1" spans="1:10">
+      <c r="A59" s="1">
+        <v>832</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="J58" s="28"/>
-    </row>
-    <row r="59" s="7" customFormat="1" spans="1:10">
-      <c r="A59" s="1">
-        <v>867</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3506,25 +3514,25 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J59" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="J59" s="28"/>
     </row>
     <row r="60" s="7" customFormat="1" spans="1:10">
       <c r="A60" s="1">
-        <v>868</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>202</v>
+        <v>867</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3534,55 +3542,53 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" s="7" customFormat="1" spans="1:10">
+      <c r="A61" s="1">
+        <v>868</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="J60" s="38"/>
-    </row>
-    <row r="61" s="8" customFormat="1" spans="1:10">
-      <c r="A61" s="1">
-        <v>997</v>
-      </c>
-      <c r="B61" s="10" t="s">
+      <c r="C61" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>42</v>
+      <c r="G61" s="1">
+        <v>1</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>209</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="J61" s="38"/>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3592,15 +3598,15 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>212</v>
@@ -3609,10 +3615,10 @@
         <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
@@ -3622,13 +3628,15 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J63" s="28"/>
+        <v>193</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>214</v>
@@ -3640,125 +3648,125 @@
         <v>23</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="1">
-        <v>2</v>
+      <c r="G64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="J64" s="28"/>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
       <c r="A65" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="D65" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J65" s="38"/>
+        <v>218</v>
+      </c>
+      <c r="J65" s="28"/>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:10">
       <c r="A66" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B66" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>42</v>
+      <c r="G66" s="1">
+        <v>1</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J66" s="38"/>
+    </row>
+    <row r="67" s="8" customFormat="1" spans="1:10">
+      <c r="A67" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J66" s="38"/>
-    </row>
-    <row r="67" s="8" customFormat="1" spans="1:10">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-    </row>
-    <row r="73" s="8" customFormat="1" spans="1:10">
-      <c r="A73" s="1">
-        <v>289</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J73" s="38"/>
+      <c r="J67" s="38"/>
+    </row>
+    <row r="68" s="8" customFormat="1" spans="1:10">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
     </row>
     <row r="74" s="8" customFormat="1" spans="1:10">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>11</v>
@@ -3770,156 +3778,184 @@
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J74" s="38"/>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="C75" s="39" t="s">
-        <v>231</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J75" s="38"/>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C76" s="40" t="s">
-        <v>235</v>
+        <v>232</v>
+      </c>
+      <c r="C76" s="39" t="s">
+        <v>233</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J76" s="38"/>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:10">
       <c r="A77" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B77" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J77" s="38"/>
     </row>
     <row r="78" s="8" customFormat="1" spans="1:10">
       <c r="A78" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B78" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J78" s="38"/>
+    </row>
+    <row r="79" s="8" customFormat="1" spans="1:10">
+      <c r="A79" s="1">
+        <v>79</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J78" s="38"/>
+      <c r="J79" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J67">
-    <sortState ref="A1:J67">
+  <autoFilter ref="A1:J68">
+    <sortState ref="A1:J68">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B65" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B58" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B57" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C54" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C59" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B60" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B49" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B50" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B66" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B59" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B58" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C55" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C60" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B61" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B50" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B51" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
     <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
     <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
     <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B51" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B52" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B46" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B47" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
     <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
     <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B64" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B65" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B45" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B44" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B43" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B46" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B45" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B44" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
@@ -3928,19 +3964,19 @@
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
     <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B42" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B43" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
     <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B66" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B63" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B56" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B62" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B67" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B64" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B57" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B63" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
     <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B74" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B75" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
     <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B52" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B47" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B55" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B53" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B48" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B56" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
     <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
@@ -3950,22 +3986,23 @@
     <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
     <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B48" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B49" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B73" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B75" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B76" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C76" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C75" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B77" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B78" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B74" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B76" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B77" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C77" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C76" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B78" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B79" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
     <hyperlink ref="B39" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
     <hyperlink ref="B40" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
     <hyperlink ref="B41" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
+    <hyperlink ref="B42" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="243">
   <si>
     <t>编号</t>
   </si>
@@ -449,9 +449,6 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/max-area-of-island/</t>
-  </si>
-  <si>
-    <t>①深度优先搜索 ②广度优先搜索</t>
   </si>
   <si>
     <t>最大人工岛</t>
@@ -2989,7 +2986,7 @@
         <v>44301</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="J40" s="36"/>
     </row>
@@ -2998,10 +2995,10 @@
         <v>827</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>145</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>146</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>35</v>
@@ -3028,10 +3025,10 @@
         <v>130</v>
       </c>
       <c r="B42" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>148</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>11</v>
@@ -3058,10 +3055,10 @@
         <v>206</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
@@ -3083,16 +3080,16 @@
         <v>225</v>
       </c>
       <c r="B44" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>13</v>
@@ -3101,7 +3098,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J44" s="28"/>
     </row>
@@ -3110,10 +3107,10 @@
         <v>226</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
@@ -3129,7 +3126,7 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J45" s="28"/>
     </row>
@@ -3138,10 +3135,10 @@
         <v>227</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>11</v>
@@ -3157,7 +3154,7 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -3166,16 +3163,16 @@
         <v>232</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3185,7 +3182,7 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -3194,10 +3191,10 @@
         <v>235</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>23</v>
@@ -3213,7 +3210,7 @@
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J48" s="24" t="s">
         <v>20</v>
@@ -3224,10 +3221,10 @@
         <v>240</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>11</v>
@@ -3243,7 +3240,7 @@
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J49" s="37"/>
     </row>
@@ -3252,10 +3249,10 @@
         <v>303</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>23</v>
@@ -3271,7 +3268,7 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J50" s="38"/>
     </row>
@@ -3280,10 +3277,10 @@
         <v>304</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>11</v>
@@ -3299,7 +3296,7 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J51" s="38"/>
     </row>
@@ -3308,10 +3305,10 @@
         <v>338</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>11</v>
@@ -3327,7 +3324,7 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J52" s="38"/>
     </row>
@@ -3336,10 +3333,10 @@
         <v>405</v>
       </c>
       <c r="B53" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>23</v>
@@ -3354,10 +3351,10 @@
         <v>42</v>
       </c>
       <c r="I53" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J53" s="24" t="s">
         <v>181</v>
-      </c>
-      <c r="J53" s="24" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="54" s="5" customFormat="1" spans="1:10">
@@ -3365,7 +3362,7 @@
         <v>474</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3381,16 +3378,16 @@
         <v>543</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>13</v>
@@ -3400,7 +3397,7 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J55" s="38"/>
     </row>
@@ -3409,10 +3406,10 @@
         <v>617</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>23</v>
@@ -3428,7 +3425,7 @@
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J56" s="24" t="s">
         <v>20</v>
@@ -3439,10 +3436,10 @@
         <v>654</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>11</v>
@@ -3458,7 +3455,7 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J57" s="1"/>
     </row>
@@ -3467,10 +3464,10 @@
         <v>824</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
@@ -3486,7 +3483,7 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J58" s="38"/>
     </row>
@@ -3495,10 +3492,10 @@
         <v>832</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
@@ -3514,7 +3511,7 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J59" s="28"/>
     </row>
@@ -3523,16 +3520,16 @@
         <v>867</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3542,7 +3539,7 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J60" s="1"/>
     </row>
@@ -3551,16 +3548,16 @@
         <v>868</v>
       </c>
       <c r="B61" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3570,7 +3567,7 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J61" s="38"/>
     </row>
@@ -3579,16 +3576,16 @@
         <v>997</v>
       </c>
       <c r="B62" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3598,10 +3595,10 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
@@ -3609,10 +3606,10 @@
         <v>998</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>11</v>
@@ -3628,10 +3625,10 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
@@ -3639,10 +3636,10 @@
         <v>999</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>23</v>
@@ -3667,16 +3664,16 @@
         <v>1047</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
@@ -3686,7 +3683,7 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J65" s="28"/>
     </row>
@@ -3695,16 +3692,16 @@
         <v>1052</v>
       </c>
       <c r="B66" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
@@ -3714,7 +3711,7 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J66" s="38"/>
     </row>
@@ -3723,10 +3720,10 @@
         <v>1603</v>
       </c>
       <c r="B67" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>23</v>
@@ -3763,10 +3760,10 @@
         <v>289</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>11</v>
@@ -3778,11 +3775,11 @@
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J74" s="38"/>
     </row>
@@ -3791,10 +3788,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
@@ -3806,11 +3803,11 @@
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J75" s="38"/>
     </row>
@@ -3819,26 +3816,26 @@
         <v>208</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" s="39" t="s">
         <v>232</v>
-      </c>
-      <c r="C76" s="39" t="s">
-        <v>233</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J76" s="38"/>
     </row>
@@ -3847,26 +3844,26 @@
         <v>648</v>
       </c>
       <c r="B77" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C77" s="40" t="s">
         <v>236</v>
-      </c>
-      <c r="C77" s="40" t="s">
-        <v>237</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J77" s="38"/>
     </row>
@@ -3875,26 +3872,26 @@
         <v>720</v>
       </c>
       <c r="B78" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J78" s="38"/>
     </row>
@@ -3903,10 +3900,10 @@
         <v>79</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>11</v>
@@ -3918,7 +3915,7 @@
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
   <si>
     <t>编号</t>
   </si>
@@ -253,10 +253,13 @@
     <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
   </si>
   <si>
-    <t>动态规划、斐波那契</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化</t>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
   </si>
   <si>
     <t>搜索二维矩阵</t>
@@ -316,9 +319,6 @@
     <t>https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/</t>
   </si>
   <si>
-    <t>动态规划</t>
-  </si>
-  <si>
     <t>①暴力搜索 ②动态规划 ③存储优化</t>
   </si>
   <si>
@@ -406,9 +406,6 @@
     <t>W</t>
   </si>
   <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
-  </si>
-  <si>
     <t>二叉树的右视图</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
   </si>
   <si>
     <t>搜索、并查集</t>
-  </si>
-  <si>
-    <t>Z</t>
   </si>
   <si>
     <t>①深度优先搜索 ②广度优先搜索 ③并查集</t>
@@ -938,13 +932,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -980,13 +974,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1430,7 +1424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1470,55 +1464,52 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1533,13 +1524,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1984,7 +1972,7 @@
       <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="22"/>
+      <c r="J2" s="21"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="8">
@@ -2012,7 +2000,7 @@
       <c r="I3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2042,7 +2030,7 @@
       <c r="I4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="22"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="8"/>
@@ -2054,7 +2042,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="22"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="8">
@@ -2082,7 +2070,7 @@
       <c r="I6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="8">
@@ -2110,7 +2098,7 @@
       <c r="I7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="23"/>
+      <c r="J7" s="22"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="8">
@@ -2138,7 +2126,7 @@
       <c r="I8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="23"/>
+      <c r="J8" s="22"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:10">
       <c r="A9" s="8" t="s">
@@ -2166,7 +2154,7 @@
       <c r="I9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="23"/>
+      <c r="J9" s="22"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:9">
       <c r="A10" s="1">
@@ -2220,7 +2208,7 @@
       <c r="I11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2300,7 +2288,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="25"/>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:10">
       <c r="A15" s="1">
@@ -2327,7 +2315,7 @@
       <c r="I15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:10">
       <c r="A16" s="1">
@@ -2354,7 +2342,7 @@
       <c r="I16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="27"/>
+      <c r="J16" s="26"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:10">
       <c r="A17" s="1">
@@ -2381,7 +2369,7 @@
       <c r="I17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="27"/>
+      <c r="J17" s="26"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:10">
       <c r="A18" s="1">
@@ -2408,7 +2396,7 @@
       <c r="I18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J18" s="28"/>
+      <c r="J18" s="27"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:10">
       <c r="A19" s="1">
@@ -2435,45 +2423,47 @@
       <c r="I19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J19" s="28"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:10">
-      <c r="A20" s="1">
+      <c r="J19" s="27"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:10">
+      <c r="A20" s="13">
         <v>70</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="26" t="s">
+      <c r="F20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="29"/>
+      <c r="H20" s="15">
+        <v>44305</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="28"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:10">
       <c r="A22" s="7">
         <v>74</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>80</v>
+      <c r="B22" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>11</v>
@@ -2489,19 +2479,19 @@
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="30"/>
+        <v>83</v>
+      </c>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:10">
       <c r="A23" s="5">
         <v>82</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>11</v>
@@ -2517,17 +2507,17 @@
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="31"/>
+      <c r="J23" s="30"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:10">
       <c r="A24" s="5">
         <v>83</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>23</v>
@@ -2543,25 +2533,25 @@
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J24" s="31"/>
+        <v>88</v>
+      </c>
+      <c r="J24" s="30"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:10">
       <c r="A25" s="1">
         <v>102</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
@@ -2570,25 +2560,25 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J25" s="27"/>
+        <v>92</v>
+      </c>
+      <c r="J25" s="26"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:9">
       <c r="A26" s="1">
         <v>103</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
@@ -2597,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:10">
@@ -2605,16 +2595,16 @@
         <v>104</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2623,25 +2613,25 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J27" s="28"/>
+        <v>92</v>
+      </c>
+      <c r="J27" s="27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:10">
       <c r="A28" s="1">
         <v>121</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -2652,7 +2642,7 @@
       <c r="I28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J28" s="28"/>
+      <c r="J28" s="27"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:10">
       <c r="A29" s="1">
@@ -2679,7 +2669,7 @@
       <c r="I29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J29" s="28"/>
+      <c r="J29" s="27"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:10">
       <c r="A30" s="1">
@@ -2706,7 +2696,7 @@
       <c r="I30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J30" s="27"/>
+      <c r="J30" s="26"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:10">
       <c r="A31" s="1">
@@ -2722,7 +2712,7 @@
         <v>35</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -2733,13 +2723,13 @@
       <c r="I31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J31" s="28"/>
+      <c r="J31" s="27"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:10">
       <c r="A32" s="1">
         <v>144</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="17" t="s">
         <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2749,7 +2739,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
@@ -2757,14 +2747,14 @@
       <c r="G32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="28"/>
-      <c r="J32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="26"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:10">
       <c r="A33" s="4">
         <v>150</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="18" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -2786,7 +2776,7 @@
       <c r="I33" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J33" s="32"/>
+      <c r="J33" s="31"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="6">
@@ -2814,13 +2804,13 @@
       <c r="I34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>191</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="18" t="s">
         <v>123</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -2842,51 +2832,51 @@
       <c r="I35" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J35" s="33"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:10">
-      <c r="A36" s="17">
+      <c r="J35" s="32"/>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:10">
+      <c r="A36" s="19">
         <v>198</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="17" t="s">
+      <c r="E36" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="J36" s="34"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="33"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:10">
       <c r="A37" s="6">
         <v>199</v>
       </c>
       <c r="B37" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>13</v>
@@ -2896,169 +2886,169 @@
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J37" s="34"/>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:10">
+      <c r="A38" s="13">
+        <v>200</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="J37" s="35"/>
-    </row>
-    <row r="38" s="3" customFormat="1" spans="1:10">
-      <c r="A38" s="19">
-        <v>200</v>
-      </c>
-      <c r="B38" s="20" t="s">
+      <c r="C38" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="D38" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="F38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="15">
+        <v>44301</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J38" s="28"/>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="1:10">
+      <c r="A39" s="13">
+        <v>463</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="15">
+        <v>44301</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J39" s="28"/>
+    </row>
+    <row r="40" s="2" customFormat="1" spans="1:10">
+      <c r="A40" s="13">
+        <v>695</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E40" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" s="15">
+        <v>44301</v>
+      </c>
+      <c r="I40" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="H38" s="21">
-        <v>44301</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J38" s="36"/>
-    </row>
-    <row r="39" s="3" customFormat="1" spans="1:10">
-      <c r="A39" s="19">
-        <v>463</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="H39" s="21">
-        <v>44301</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J39" s="36"/>
-    </row>
-    <row r="40" s="3" customFormat="1" spans="1:10">
-      <c r="A40" s="19">
-        <v>695</v>
-      </c>
-      <c r="B40" s="20" t="s">
+      <c r="J40" s="28"/>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="1:10">
+      <c r="A41" s="13">
+        <v>827</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C41" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D41" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" s="15">
+        <v>44302</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J41" s="28"/>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="1:10">
+      <c r="A42" s="13">
+        <v>130</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="H40" s="21">
-        <v>44301</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J40" s="36"/>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="1:10">
-      <c r="A41" s="19">
-        <v>827</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="19" t="s">
+      <c r="E42" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H42" s="15">
+        <v>44302</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="H41" s="21">
-        <v>44302</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J41" s="36"/>
-    </row>
-    <row r="42" s="3" customFormat="1" spans="1:10">
-      <c r="A42" s="19">
-        <v>130</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="H42" s="21">
-        <v>44302</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" s="36"/>
+      <c r="J42" s="28"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:10">
       <c r="A43" s="1">
         <v>206</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>148</v>
+      <c r="B43" s="17" t="s">
+        <v>146</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
@@ -3072,24 +3062,24 @@
       <c r="G43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
         <v>225</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>13</v>
@@ -3098,25 +3088,25 @@
         <v>2</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J44" s="28"/>
+        <v>151</v>
+      </c>
+      <c r="J44" s="27"/>
     </row>
     <row r="45" s="4" customFormat="1" spans="1:10">
       <c r="A45" s="1">
         <v>226</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
@@ -3126,19 +3116,19 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J45" s="28"/>
+        <v>154</v>
+      </c>
+      <c r="J45" s="27"/>
     </row>
     <row r="46" s="4" customFormat="1" spans="1:10">
       <c r="A46" s="1">
         <v>227</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>11</v>
@@ -3154,7 +3144,7 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -3163,16 +3153,16 @@
         <v>232</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3182,7 +3172,7 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -3191,16 +3181,16 @@
         <v>235</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>13</v>
@@ -3210,9 +3200,9 @@
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="J48" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="J48" s="23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3220,11 +3210,11 @@
       <c r="A49" s="7">
         <v>240</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>166</v>
+      <c r="B49" s="16" t="s">
+        <v>164</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>11</v>
@@ -3240,25 +3230,25 @@
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="J49" s="37"/>
+        <v>166</v>
+      </c>
+      <c r="J49" s="35"/>
     </row>
     <row r="50" s="5" customFormat="1" spans="1:10">
       <c r="A50" s="1">
         <v>303</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>13</v>
@@ -3268,25 +3258,25 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J50" s="38"/>
+        <v>169</v>
+      </c>
+      <c r="J50" s="36"/>
     </row>
     <row r="51" s="5" customFormat="1" spans="1:10">
       <c r="A51" s="1">
         <v>304</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
@@ -3296,25 +3286,25 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J51" s="38"/>
+        <v>172</v>
+      </c>
+      <c r="J51" s="36"/>
     </row>
     <row r="52" s="5" customFormat="1" spans="1:10">
       <c r="A52" s="1">
         <v>338</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>13</v>
@@ -3324,19 +3314,19 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J52" s="38"/>
+        <v>175</v>
+      </c>
+      <c r="J52" s="36"/>
     </row>
     <row r="53" s="5" customFormat="1" spans="1:10">
       <c r="A53" s="5">
         <v>405</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>23</v>
@@ -3351,10 +3341,10 @@
         <v>42</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="J53" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="J53" s="23" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="54" s="5" customFormat="1" spans="1:10">
@@ -3362,7 +3352,7 @@
         <v>474</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3378,16 +3368,16 @@
         <v>543</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>13</v>
@@ -3397,25 +3387,25 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J55" s="38"/>
+        <v>184</v>
+      </c>
+      <c r="J55" s="36"/>
     </row>
     <row r="56" s="6" customFormat="1" spans="1:10">
       <c r="A56" s="5">
         <v>617</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>13</v>
@@ -3425,9 +3415,9 @@
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J56" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="J56" s="23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3436,16 +3426,16 @@
         <v>654</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>13</v>
@@ -3455,7 +3445,7 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J57" s="1"/>
     </row>
@@ -3464,10 +3454,10 @@
         <v>824</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
@@ -3483,19 +3473,19 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J58" s="38"/>
+        <v>193</v>
+      </c>
+      <c r="J58" s="36"/>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:10">
       <c r="A59" s="1">
         <v>832</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
@@ -3511,25 +3501,25 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J59" s="28"/>
+        <v>196</v>
+      </c>
+      <c r="J59" s="27"/>
     </row>
     <row r="60" s="7" customFormat="1" spans="1:10">
       <c r="A60" s="1">
         <v>867</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3539,7 +3529,7 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J60" s="1"/>
     </row>
@@ -3548,16 +3538,16 @@
         <v>868</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3567,25 +3557,25 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J61" s="38"/>
+        <v>203</v>
+      </c>
+      <c r="J61" s="36"/>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:10">
       <c r="A62" s="1">
         <v>997</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3595,10 +3585,10 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
@@ -3606,16 +3596,16 @@
         <v>998</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
@@ -3625,10 +3615,10 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
@@ -3636,10 +3626,10 @@
         <v>999</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>23</v>
@@ -3657,23 +3647,23 @@
       <c r="I64" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J64" s="28"/>
+      <c r="J64" s="27"/>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
       <c r="A65" s="1">
         <v>1047</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
@@ -3683,25 +3673,25 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J65" s="28"/>
+        <v>215</v>
+      </c>
+      <c r="J65" s="27"/>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:10">
       <c r="A66" s="1">
         <v>1052</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
@@ -3711,19 +3701,19 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J66" s="38"/>
+        <v>219</v>
+      </c>
+      <c r="J66" s="36"/>
     </row>
     <row r="67" s="8" customFormat="1" spans="1:10">
       <c r="A67" s="1">
         <v>1603</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>23</v>
@@ -3741,7 +3731,7 @@
       <c r="I67" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J67" s="38"/>
+      <c r="J67" s="36"/>
     </row>
     <row r="68" s="8" customFormat="1" spans="1:10">
       <c r="A68" s="1"/>
@@ -3760,10 +3750,10 @@
         <v>289</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>11</v>
@@ -3775,23 +3765,23 @@
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J74" s="38"/>
+        <v>225</v>
+      </c>
+      <c r="J74" s="36"/>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
@@ -3803,107 +3793,107 @@
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="J75" s="38"/>
+        <v>228</v>
+      </c>
+      <c r="J75" s="36"/>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
         <v>208</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C76" s="39" t="s">
-        <v>232</v>
+        <v>229</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>230</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J76" s="38"/>
+        <v>232</v>
+      </c>
+      <c r="J76" s="36"/>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:10">
       <c r="A77" s="1">
         <v>648</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C77" s="40" t="s">
-        <v>236</v>
+        <v>233</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>234</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J77" s="38"/>
+        <v>235</v>
+      </c>
+      <c r="J77" s="36"/>
     </row>
     <row r="78" s="8" customFormat="1" spans="1:10">
       <c r="A78" s="1">
         <v>720</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J78" s="38"/>
+        <v>238</v>
+      </c>
+      <c r="J78" s="36"/>
     </row>
     <row r="79" s="8" customFormat="1" spans="1:10">
       <c r="A79" s="1">
         <v>79</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>11</v>
@@ -3915,13 +3905,13 @@
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J79" s="38"/>
+      <c r="J79" s="36"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J68">

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$69</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="243">
   <si>
     <t>编号</t>
   </si>
@@ -247,19 +247,25 @@
     <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
   </si>
   <si>
+    <t>不同路径</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/unique-paths/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
     <t>爬楼梯</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
-  </si>
-  <si>
-    <t>动态规划</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
   </si>
   <si>
     <t>搜索二维矩阵</t>
@@ -1900,7 +1906,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2427,7 +2433,7 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="1:10">
       <c r="A20" s="13">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>76</v>
@@ -2436,7 +2442,7 @@
         <v>77</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>78</v>
@@ -2455,63 +2461,67 @@
       </c>
       <c r="J20" s="28"/>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:10">
-      <c r="A22" s="7">
+    <row r="21" s="2" customFormat="1" spans="1:10">
+      <c r="A21" s="13">
+        <v>70</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="15">
+        <v>44305</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:10">
+      <c r="A23" s="7">
         <v>74</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="B23" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="29"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:10">
-      <c r="A23" s="5">
-        <v>82</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="H23" s="7"/>
+      <c r="I23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="30"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:10">
       <c r="A24" s="5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>86</v>
@@ -2520,7 +2530,7 @@
         <v>87</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>27</v>
@@ -2532,53 +2542,52 @@
         <v>42</v>
       </c>
       <c r="H24" s="5"/>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="5"/>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:10">
+      <c r="A25" s="5">
+        <v>83</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="J24" s="30"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:10">
-      <c r="A25" s="1">
+      <c r="C25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:10">
+      <c r="A26" s="1">
         <v>102</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="B26" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:9">
-      <c r="A26" s="1">
-        <v>103</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
@@ -2587,24 +2596,25 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:9">
+      <c r="A27" s="1">
+        <v>103</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:10">
-      <c r="A27" s="1">
-        <v>104</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2613,13 +2623,12 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J27" s="27"/>
+        <v>97</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:10">
       <c r="A28" s="1">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>98</v>
@@ -2631,61 +2640,61 @@
         <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>42</v>
+      <c r="G28" s="1">
+        <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J28" s="27"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:10">
       <c r="A29" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="1">
-        <v>2</v>
+      <c r="G29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J29" s="27"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:10">
       <c r="A30" s="1">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -2694,25 +2703,25 @@
         <v>2</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J30" s="26"/>
+        <v>106</v>
+      </c>
+      <c r="J30" s="27"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:10">
       <c r="A31" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -2721,220 +2730,217 @@
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J31" s="27"/>
+        <v>110</v>
+      </c>
+      <c r="J31" s="26"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:10">
       <c r="A32" s="1">
+        <v>132</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:10">
+      <c r="A33" s="1">
         <v>144</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="B33" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="27"/>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:10">
-      <c r="A33" s="4">
+      <c r="I33" s="27"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:10">
+      <c r="A34" s="4">
         <v>150</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B34" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J33" s="31"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="6">
+      <c r="F34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J34" s="31"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="6">
         <v>190</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B35" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J35" s="24"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4">
+        <v>191</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" s="32"/>
+    </row>
+    <row r="37" s="3" customFormat="1" spans="1:10">
+      <c r="A37" s="19">
+        <v>198</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="33"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:10">
+      <c r="A38" s="6">
+        <v>199</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J34" s="24"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4">
-        <v>191</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J35" s="32"/>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:10">
-      <c r="A36" s="19">
-        <v>198</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" s="33"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:10">
-      <c r="A37" s="6">
-        <v>199</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="J37" s="34"/>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:10">
-      <c r="A38" s="13">
-        <v>200</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H38" s="15">
-        <v>44301</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="J38" s="28"/>
+      <c r="J38" s="34"/>
     </row>
     <row r="39" s="2" customFormat="1" spans="1:10">
       <c r="A39" s="13">
-        <v>463</v>
+        <v>200</v>
       </c>
       <c r="B39" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="F39" s="13" t="s">
         <v>13</v>
@@ -2946,25 +2952,25 @@
         <v>44301</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J39" s="28"/>
     </row>
     <row r="40" s="2" customFormat="1" spans="1:10">
       <c r="A40" s="13">
-        <v>695</v>
+        <v>463</v>
       </c>
       <c r="B40" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>13</v>
@@ -2976,13 +2982,13 @@
         <v>44301</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J40" s="28"/>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:10">
       <c r="A41" s="13">
-        <v>827</v>
+        <v>695</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>142</v>
@@ -2991,10 +2997,10 @@
         <v>143</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>13</v>
@@ -3003,16 +3009,16 @@
         <v>79</v>
       </c>
       <c r="H41" s="15">
-        <v>44302</v>
+        <v>44301</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J41" s="28"/>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:10">
       <c r="A42" s="13">
-        <v>130</v>
+        <v>827</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>144</v>
@@ -3021,10 +3027,10 @@
         <v>145</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>13</v>
@@ -3036,40 +3042,45 @@
         <v>44302</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J42" s="28"/>
     </row>
-    <row r="43" s="1" customFormat="1" spans="1:10">
-      <c r="A43" s="1">
+    <row r="43" s="2" customFormat="1" spans="1:10">
+      <c r="A43" s="13">
+        <v>130</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="15">
+        <v>44302</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="J43" s="28"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:10">
+      <c r="A44" s="1">
         <v>206</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="1">
-        <v>225</v>
-      </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="17" t="s">
         <v>148</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -3079,34 +3090,32 @@
         <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1">
+        <v>225</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2</v>
-      </c>
-      <c r="I44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="J44" s="27"/>
-    </row>
-    <row r="45" s="4" customFormat="1" spans="1:10">
-      <c r="A45" s="1">
-        <v>226</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
@@ -3114,27 +3123,26 @@
       <c r="G45" s="1">
         <v>2</v>
       </c>
-      <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J45" s="27"/>
     </row>
     <row r="46" s="4" customFormat="1" spans="1:10">
       <c r="A46" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3144,25 +3152,25 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J46" s="1"/>
+        <v>156</v>
+      </c>
+      <c r="J46" s="27"/>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:10">
       <c r="A47" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3172,108 +3180,108 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="5">
+    <row r="48" s="4" customFormat="1" spans="1:10">
+      <c r="A48" s="1">
+        <v>232</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="5">
         <v>235</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="B49" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="5" t="s">
+      <c r="E49" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="J48" s="23" t="s">
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J49" s="23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" s="5" customFormat="1" spans="1:10">
-      <c r="A49" s="7">
+    <row r="50" s="5" customFormat="1" spans="1:10">
+      <c r="A50" s="7">
         <v>240</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="B50" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E50" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="F50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J49" s="35"/>
-    </row>
-    <row r="50" s="5" customFormat="1" spans="1:10">
-      <c r="A50" s="1">
-        <v>303</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="H50" s="7"/>
+      <c r="I50" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="36"/>
+      <c r="J50" s="35"/>
     </row>
     <row r="51" s="5" customFormat="1" spans="1:10">
       <c r="A51" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="D51" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>78</v>
@@ -3286,19 +3294,19 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J51" s="36"/>
     </row>
     <row r="52" s="5" customFormat="1" spans="1:10">
       <c r="A52" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>11</v>
@@ -3314,184 +3322,184 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J52" s="36"/>
+    </row>
+    <row r="53" s="5" customFormat="1" spans="1:10">
+      <c r="A53" s="1">
+        <v>338</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="J52" s="36"/>
-    </row>
-    <row r="53" s="5" customFormat="1" spans="1:10">
-      <c r="A53" s="5">
+      <c r="C53" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J53" s="36"/>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:10">
+      <c r="A54" s="5">
         <v>405</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="B54" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="5" t="s">
+      <c r="E54" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J53" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="54" s="5" customFormat="1" spans="1:10">
-      <c r="A54" s="1">
+      <c r="I54" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" s="5" customFormat="1" spans="1:10">
+      <c r="A55" s="1">
         <v>474</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="1:10">
-      <c r="A55" s="1">
+      <c r="B55" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" s="6" customFormat="1" spans="1:10">
+      <c r="A56" s="1">
         <v>543</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="B56" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="E56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J55" s="36"/>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="1:10">
-      <c r="A56" s="5">
+      <c r="H56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J56" s="36"/>
+    </row>
+    <row r="57" s="6" customFormat="1" spans="1:10">
+      <c r="A57" s="5">
         <v>617</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="B57" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="5" t="s">
+      <c r="E57" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="J56" s="23" t="s">
+      <c r="H57" s="5"/>
+      <c r="I57" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J57" s="23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="1:10">
-      <c r="A57" s="1">
-        <v>654</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J57" s="1"/>
     </row>
     <row r="58" s="6" customFormat="1" spans="1:10">
       <c r="A58" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="D58" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="1">
-        <v>1</v>
+      <c r="G58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J58" s="36"/>
+        <v>192</v>
+      </c>
+      <c r="J58" s="1"/>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:10">
       <c r="A59" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3501,25 +3509,25 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J59" s="36"/>
+    </row>
+    <row r="60" s="6" customFormat="1" spans="1:10">
+      <c r="A60" s="1">
+        <v>832</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="J59" s="27"/>
-    </row>
-    <row r="60" s="7" customFormat="1" spans="1:10">
-      <c r="A60" s="1">
-        <v>867</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3529,25 +3537,25 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J60" s="1"/>
+        <v>198</v>
+      </c>
+      <c r="J60" s="27"/>
     </row>
     <row r="61" s="7" customFormat="1" spans="1:10">
       <c r="A61" s="1">
-        <v>868</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>201</v>
+        <v>867</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3557,55 +3565,53 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" s="7" customFormat="1" spans="1:10">
+      <c r="A62" s="1">
+        <v>868</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="J61" s="36"/>
-    </row>
-    <row r="62" s="8" customFormat="1" spans="1:10">
-      <c r="A62" s="1">
-        <v>997</v>
-      </c>
-      <c r="B62" s="10" t="s">
+      <c r="C62" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>42</v>
+      <c r="G62" s="1">
+        <v>1</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="J62" s="36"/>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
@@ -3615,15 +3621,15 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>211</v>
@@ -3632,10 +3638,10 @@
         <v>212</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
@@ -3645,13 +3651,15 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J64" s="27"/>
+        <v>192</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
       <c r="A65" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>213</v>
@@ -3663,125 +3671,125 @@
         <v>23</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="1">
-        <v>2</v>
+      <c r="G65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="J65" s="27"/>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:10">
       <c r="A66" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B66" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="D66" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J66" s="36"/>
+        <v>217</v>
+      </c>
+      <c r="J66" s="27"/>
     </row>
     <row r="67" s="8" customFormat="1" spans="1:10">
       <c r="A67" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B67" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>42</v>
+      <c r="G67" s="1">
+        <v>1</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J67" s="36"/>
+    </row>
+    <row r="68" s="8" customFormat="1" spans="1:10">
+      <c r="A68" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J67" s="36"/>
-    </row>
-    <row r="68" s="8" customFormat="1" spans="1:10">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="74" s="8" customFormat="1" spans="1:10">
-      <c r="A74" s="1">
-        <v>289</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J74" s="36"/>
+      <c r="J68" s="36"/>
+    </row>
+    <row r="69" s="8" customFormat="1" spans="1:10">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:10">
       <c r="A75" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
@@ -3793,156 +3801,184 @@
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J75" s="36"/>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C76" s="37" t="s">
-        <v>230</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J76" s="36"/>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:10">
       <c r="A77" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>234</v>
+        <v>231</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>232</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J77" s="36"/>
     </row>
     <row r="78" s="8" customFormat="1" spans="1:10">
       <c r="A78" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B78" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J78" s="36"/>
     </row>
     <row r="79" s="8" customFormat="1" spans="1:10">
       <c r="A79" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="D79" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J79" s="36"/>
+    </row>
+    <row r="80" s="8" customFormat="1" spans="1:10">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J79" s="36"/>
+      <c r="J80" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J68">
-    <sortState ref="A1:J68">
+  <autoFilter ref="A1:J69">
+    <sortState ref="A1:J69">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B66" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B59" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B58" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C55" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C60" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B61" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B50" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B51" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B25" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="B26" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="C26" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B27" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B52" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B67" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B60" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B59" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C56" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C61" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B62" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B51" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B52" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B26" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B27" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="C27" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="B28" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B53" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B47" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B30" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B29" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B65" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B48" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B31" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B30" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B66" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B46" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B45" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B44" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B47" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B46" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B45" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
@@ -3950,46 +3986,47 @@
     <hyperlink ref="B10" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
-    <hyperlink ref="B28" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B43" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
-    <hyperlink ref="B32" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B67" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B64" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B57" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B63" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
-    <hyperlink ref="B35" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B75" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
-    <hyperlink ref="B33" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
+    <hyperlink ref="B29" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="B44" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B33" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="B68" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B65" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B58" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B64" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B36" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
+    <hyperlink ref="B76" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B34" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B53" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B48" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B56" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B54" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B49" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B57" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
-    <hyperlink ref="B24" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
-    <hyperlink ref="B23" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
-    <hyperlink ref="B34" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
-    <hyperlink ref="B36" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
-    <hyperlink ref="B37" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
-    <hyperlink ref="B38" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
+    <hyperlink ref="B25" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
+    <hyperlink ref="B24" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
+    <hyperlink ref="B35" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
+    <hyperlink ref="B37" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
+    <hyperlink ref="B38" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
+    <hyperlink ref="B39" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
-    <hyperlink ref="B22" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B49" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B23" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
+    <hyperlink ref="B50" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B74" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B76" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B77" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C77" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C76" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B78" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B79" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
-    <hyperlink ref="B39" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
-    <hyperlink ref="B40" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
-    <hyperlink ref="B41" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
-    <hyperlink ref="B42" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
+    <hyperlink ref="B75" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B77" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B78" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C78" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C77" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B79" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B80" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B40" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
+    <hyperlink ref="B41" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
+    <hyperlink ref="B42" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
+    <hyperlink ref="B43" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
+    <hyperlink ref="B20" r:id="rId67" display="不同路径" tooltip="https://leetcode-cn.com/problems/unique-paths/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="246">
   <si>
     <t>编号</t>
   </si>
@@ -266,6 +266,15 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
+  </si>
+  <si>
+    <t>将字符串翻转到单调递增</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/</t>
+  </si>
+  <si>
+    <t>①遍历分割点 ②动态规划 ③存储优化 ④记忆化递归</t>
   </si>
   <si>
     <t>搜索二维矩阵</t>
@@ -2491,15 +2500,45 @@
       </c>
       <c r="J21" s="28"/>
     </row>
+    <row r="22" s="2" customFormat="1" spans="1:10">
+      <c r="A22" s="13">
+        <v>926</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="15">
+        <v>44305</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="28"/>
+    </row>
     <row r="23" s="1" customFormat="1" spans="1:10">
       <c r="A23" s="7">
         <v>74</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>11</v>
@@ -2515,7 +2554,7 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J23" s="29"/>
     </row>
@@ -2524,10 +2563,10 @@
         <v>82</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>11</v>
@@ -2550,10 +2589,10 @@
         <v>83</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>23</v>
@@ -2569,7 +2608,7 @@
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J25" s="30"/>
     </row>
@@ -2578,16 +2617,16 @@
         <v>102</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
@@ -2596,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J26" s="26"/>
     </row>
@@ -2605,16 +2644,16 @@
         <v>103</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
@@ -2623,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:10">
@@ -2631,16 +2670,16 @@
         <v>104</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
@@ -2649,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J28" s="27"/>
     </row>
@@ -2658,10 +2697,10 @@
         <v>121</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
@@ -2676,7 +2715,7 @@
         <v>42</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J29" s="27"/>
     </row>
@@ -2685,16 +2724,16 @@
         <v>125</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -2703,7 +2742,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J30" s="27"/>
     </row>
@@ -2712,16 +2751,16 @@
         <v>131</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -2730,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J31" s="26"/>
     </row>
@@ -2739,10 +2778,10 @@
         <v>132</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>35</v>
@@ -2757,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J32" s="27"/>
     </row>
@@ -2766,16 +2805,16 @@
         <v>144</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
@@ -2791,26 +2830,26 @@
         <v>150</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J34" s="31"/>
     </row>
@@ -2819,16 +2858,16 @@
         <v>190</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>13</v>
@@ -2838,7 +2877,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J35" s="24"/>
     </row>
@@ -2847,26 +2886,26 @@
         <v>191</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J36" s="32"/>
     </row>
@@ -2875,10 +2914,10 @@
         <v>198</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>11</v>
@@ -2890,7 +2929,7 @@
         <v>13</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H37" s="19"/>
       <c r="I37" s="19" t="s">
@@ -2903,16 +2942,16 @@
         <v>199</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>13</v>
@@ -2922,7 +2961,7 @@
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J38" s="34"/>
     </row>
@@ -2931,16 +2970,16 @@
         <v>200</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F39" s="13" t="s">
         <v>13</v>
@@ -2952,7 +2991,7 @@
         <v>44301</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J39" s="28"/>
     </row>
@@ -2961,16 +3000,16 @@
         <v>463</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>13</v>
@@ -2982,7 +3021,7 @@
         <v>44301</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J40" s="28"/>
     </row>
@@ -2991,16 +3030,16 @@
         <v>695</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>13</v>
@@ -3012,7 +3051,7 @@
         <v>44301</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J41" s="28"/>
     </row>
@@ -3021,16 +3060,16 @@
         <v>827</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>13</v>
@@ -3042,7 +3081,7 @@
         <v>44302</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J42" s="28"/>
     </row>
@@ -3051,16 +3090,16 @@
         <v>130</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>13</v>
@@ -3072,7 +3111,7 @@
         <v>44302</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J43" s="28"/>
     </row>
@@ -3081,10 +3120,10 @@
         <v>206</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>23</v>
@@ -3106,16 +3145,16 @@
         <v>225</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
@@ -3124,7 +3163,7 @@
         <v>2</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J45" s="27"/>
     </row>
@@ -3133,16 +3172,16 @@
         <v>226</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3152,7 +3191,7 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J46" s="27"/>
     </row>
@@ -3161,16 +3200,16 @@
         <v>227</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3180,7 +3219,7 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -3189,16 +3228,16 @@
         <v>232</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>13</v>
@@ -3208,7 +3247,7 @@
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -3217,16 +3256,16 @@
         <v>235</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>13</v>
@@ -3236,7 +3275,7 @@
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J49" s="23" t="s">
         <v>20</v>
@@ -3247,10 +3286,10 @@
         <v>240</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>11</v>
@@ -3266,7 +3305,7 @@
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J50" s="35"/>
     </row>
@@ -3275,10 +3314,10 @@
         <v>303</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>23</v>
@@ -3294,7 +3333,7 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J51" s="36"/>
     </row>
@@ -3303,10 +3342,10 @@
         <v>304</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>11</v>
@@ -3322,7 +3361,7 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J52" s="36"/>
     </row>
@@ -3331,10 +3370,10 @@
         <v>338</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>11</v>
@@ -3350,7 +3389,7 @@
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J53" s="36"/>
     </row>
@@ -3359,16 +3398,16 @@
         <v>405</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>13</v>
@@ -3377,10 +3416,10 @@
         <v>42</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J54" s="23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" s="5" customFormat="1" spans="1:10">
@@ -3388,7 +3427,7 @@
         <v>474</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -3404,16 +3443,16 @@
         <v>543</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>13</v>
@@ -3423,7 +3462,7 @@
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J56" s="36"/>
     </row>
@@ -3432,16 +3471,16 @@
         <v>617</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>13</v>
@@ -3451,7 +3490,7 @@
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J57" s="23" t="s">
         <v>20</v>
@@ -3462,16 +3501,16 @@
         <v>654</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>13</v>
@@ -3481,7 +3520,7 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J58" s="1"/>
     </row>
@@ -3490,16 +3529,16 @@
         <v>824</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
@@ -3509,7 +3548,7 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J59" s="36"/>
     </row>
@@ -3518,10 +3557,10 @@
         <v>832</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
@@ -3537,7 +3576,7 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J60" s="27"/>
     </row>
@@ -3546,16 +3585,16 @@
         <v>867</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3565,7 +3604,7 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J61" s="1"/>
     </row>
@@ -3574,16 +3613,16 @@
         <v>868</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
@@ -3593,7 +3632,7 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J62" s="36"/>
     </row>
@@ -3602,16 +3641,16 @@
         <v>997</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
@@ -3621,10 +3660,10 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
@@ -3632,16 +3671,16 @@
         <v>998</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
@@ -3651,10 +3690,10 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
@@ -3662,10 +3701,10 @@
         <v>999</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>23</v>
@@ -3690,16 +3729,16 @@
         <v>1047</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
@@ -3709,7 +3748,7 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J66" s="27"/>
     </row>
@@ -3718,16 +3757,16 @@
         <v>1052</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>13</v>
@@ -3737,7 +3776,7 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J67" s="36"/>
     </row>
@@ -3746,10 +3785,10 @@
         <v>1603</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>23</v>
@@ -3786,10 +3825,10 @@
         <v>289</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>11</v>
@@ -3801,11 +3840,11 @@
         <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J75" s="36"/>
     </row>
@@ -3814,10 +3853,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
@@ -3829,11 +3868,11 @@
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J76" s="36"/>
     </row>
@@ -3842,26 +3881,26 @@
         <v>208</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J77" s="36"/>
     </row>
@@ -3870,26 +3909,26 @@
         <v>648</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J78" s="36"/>
     </row>
@@ -3898,26 +3937,26 @@
         <v>720</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J79" s="36"/>
     </row>
@@ -3926,10 +3965,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>11</v>
@@ -3941,7 +3980,7 @@
         <v>13</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
@@ -4027,6 +4066,7 @@
     <hyperlink ref="B42" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
     <hyperlink ref="B43" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
     <hyperlink ref="B20" r:id="rId67" display="不同路径" tooltip="https://leetcode-cn.com/problems/unique-paths/"/>
+    <hyperlink ref="B22" r:id="rId68" display="将字符串翻转到单调递增" tooltip="https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$70</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -175,106 +175,106 @@
     <t>快慢指针</t>
   </si>
   <si>
+    <t>搜索插入位置</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>全排列</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations/</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>简单排列</t>
+  </si>
+  <si>
+    <t>全排列 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/permutations-ii/</t>
+  </si>
+  <si>
+    <t>排列去重</t>
+  </si>
+  <si>
+    <t>连续子数组最大和</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
+  </si>
+  <si>
+    <t>动态规划、分治、线段树</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
+  </si>
+  <si>
+    <t>螺旋矩阵</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix/</t>
+  </si>
+  <si>
+    <t>数组</t>
+  </si>
+  <si>
+    <t>1.判断边界 2.避免重复</t>
+  </si>
+  <si>
+    <t>螺旋矩阵 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/spiral-matrix-ii/</t>
+  </si>
+  <si>
+    <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
+  </si>
+  <si>
+    <t>不同路径</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/unique-paths/</t>
+  </si>
+  <si>
+    <t>动态规划</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>①动态规划 ②存储优化 ③记忆化递归</t>
+  </si>
+  <si>
+    <t>爬楼梯</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
+  </si>
+  <si>
+    <t>将字符串翻转到单调递增</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/</t>
+  </si>
+  <si>
+    <t>①遍历分割点 ②动态规划 ③存储优化 ④记忆化递归</t>
+  </si>
+  <si>
     <t>移除元素</t>
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/remove-element/</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>交换or前移</t>
-  </si>
-  <si>
-    <t>搜索插入位置</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/search-insert-position/</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>全排列</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/permutations/</t>
-  </si>
-  <si>
-    <t>简单排列</t>
-  </si>
-  <si>
-    <t>全排列 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/permutations-ii/</t>
-  </si>
-  <si>
-    <t>排列去重</t>
-  </si>
-  <si>
-    <t>连续子数组最大和</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-subarray/</t>
-  </si>
-  <si>
-    <t>动态规划、分治、线段树</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③分治（简易线段树）</t>
-  </si>
-  <si>
-    <t>螺旋矩阵</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/spiral-matrix/</t>
-  </si>
-  <si>
-    <t>数组</t>
-  </si>
-  <si>
-    <t>1.判断边界 2.避免重复</t>
-  </si>
-  <si>
-    <t>螺旋矩阵 II</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/spiral-matrix-ii/</t>
-  </si>
-  <si>
-    <t>①逐圈扫描 ②逐圈扫描 ③维护访问状态</t>
-  </si>
-  <si>
-    <t>不同路径</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/unique-paths/</t>
-  </si>
-  <si>
-    <t>动态规划</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>①动态规划 ②存储优化 ③记忆化递归</t>
-  </si>
-  <si>
-    <t>爬楼梯</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/climbing-stairs/</t>
-  </si>
-  <si>
-    <t>将字符串翻转到单调递增</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/</t>
-  </si>
-  <si>
-    <t>①遍历分割点 ②动态规划 ③存储优化 ④记忆化递归</t>
+    <t>①前移 ②交换</t>
   </si>
   <si>
     <t>搜索二维矩阵</t>
@@ -1915,7 +1915,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -2253,41 +2253,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:9">
-      <c r="A13" s="1">
-        <v>27</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
     <row r="14" spans="1:10">
       <c r="A14" s="6">
         <v>35</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>23</v>
@@ -2299,7 +2273,7 @@
         <v>13</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -2310,10 +2284,10 @@
         <v>46</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>11</v>
@@ -2325,10 +2299,10 @@
         <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J15" s="25"/>
     </row>
@@ -2337,10 +2311,10 @@
         <v>47</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>11</v>
@@ -2352,10 +2326,10 @@
         <v>13</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J16" s="26"/>
     </row>
@@ -2364,16 +2338,16 @@
         <v>53</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -2382,7 +2356,7 @@
         <v>42</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J17" s="26"/>
     </row>
@@ -2391,25 +2365,25 @@
         <v>54</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J18" s="27"/>
     </row>
@@ -2418,16 +2392,16 @@
         <v>59</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
@@ -2436,7 +2410,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J19" s="27"/>
     </row>
@@ -2445,28 +2419,28 @@
         <v>62</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H20" s="15">
         <v>44305</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J20" s="28"/>
     </row>
@@ -2475,28 +2449,28 @@
         <v>70</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H21" s="15">
         <v>44305</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J21" s="28"/>
     </row>
@@ -2505,97 +2479,101 @@
         <v>926</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H22" s="15">
         <v>44305</v>
       </c>
       <c r="I22" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="28"/>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:10">
+      <c r="A23" s="13">
+        <v>27</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="15">
+        <v>44305</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="J22" s="28"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:10">
-      <c r="A23" s="7">
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:10">
+      <c r="A24" s="7">
         <v>74</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B24" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7" t="s">
+      <c r="F24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J23" s="29"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:10">
-      <c r="A24" s="5">
-        <v>82</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="30"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:10">
       <c r="A25" s="5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>27</v>
@@ -2607,47 +2585,46 @@
         <v>42</v>
       </c>
       <c r="H25" s="5"/>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="5"/>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:10">
+      <c r="A26" s="5">
+        <v>83</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J25" s="30"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:10">
-      <c r="A26" s="1">
+      <c r="J26" s="30"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:10">
+      <c r="A27" s="1">
         <v>102</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B27" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:9">
-      <c r="A27" s="1">
-        <v>103</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>11</v>
@@ -2662,21 +2639,22 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:10">
+        <v>97</v>
+      </c>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:9">
       <c r="A28" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>96</v>
@@ -2688,79 +2666,78 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J28" s="27"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:10">
       <c r="A29" s="1">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>42</v>
+      <c r="G29" s="1">
+        <v>1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="J29" s="27"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:10">
       <c r="A30" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="1">
-        <v>2</v>
+      <c r="G30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J30" s="27"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:10">
       <c r="A31" s="1">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -2769,25 +2746,25 @@
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J31" s="26"/>
+        <v>109</v>
+      </c>
+      <c r="J31" s="27"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:10">
       <c r="A32" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
@@ -2796,247 +2773,244 @@
         <v>2</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J32" s="27"/>
+        <v>113</v>
+      </c>
+      <c r="J32" s="26"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:10">
       <c r="A33" s="1">
+        <v>132</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:10">
+      <c r="A34" s="1">
         <v>144</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B34" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I33" s="27"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:10">
-      <c r="A34" s="4">
+      <c r="I34" s="27"/>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:10">
+      <c r="A35" s="4">
         <v>150</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B35" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4" t="s">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="6">
+      <c r="J35" s="31"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="6">
         <v>190</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B36" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6" t="s">
+      <c r="F36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J35" s="24"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4">
+      <c r="J36" s="24"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4">
         <v>191</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B37" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4" t="s">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="32"/>
-    </row>
-    <row r="37" s="3" customFormat="1" spans="1:10">
-      <c r="A37" s="19">
+      <c r="J37" s="32"/>
+    </row>
+    <row r="38" s="3" customFormat="1" spans="1:10">
+      <c r="A38" s="19">
         <v>198</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B38" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C38" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D38" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="19" t="s">
+      <c r="E38" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:10">
-      <c r="A38" s="6">
+      <c r="H38" s="19"/>
+      <c r="I38" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="33"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:10">
+      <c r="A39" s="6">
         <v>199</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B39" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E39" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6" t="s">
+      <c r="F39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J38" s="34"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:10">
-      <c r="A39" s="13">
-        <v>200</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H39" s="15">
-        <v>44301</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="J39" s="28"/>
+      <c r="J39" s="34"/>
     </row>
     <row r="40" s="2" customFormat="1" spans="1:10">
       <c r="A40" s="13">
-        <v>463</v>
+        <v>200</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H40" s="15">
         <v>44301</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J40" s="28"/>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:10">
       <c r="A41" s="13">
-        <v>695</v>
+        <v>463</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>143</v>
@@ -3045,40 +3019,40 @@
         <v>13</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H41" s="15">
         <v>44301</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J41" s="28"/>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:10">
       <c r="A42" s="13">
-        <v>827</v>
+        <v>695</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H42" s="15">
-        <v>44302</v>
+        <v>44301</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>140</v>
@@ -3087,16 +3061,16 @@
     </row>
     <row r="43" s="2" customFormat="1" spans="1:10">
       <c r="A43" s="13">
-        <v>130</v>
+        <v>827</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>139</v>
@@ -3105,7 +3079,7 @@
         <v>13</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H43" s="15">
         <v>44302</v>
@@ -3115,73 +3089,76 @@
       </c>
       <c r="J43" s="28"/>
     </row>
-    <row r="44" s="1" customFormat="1" spans="1:10">
-      <c r="A44" s="1">
+    <row r="44" s="2" customFormat="1" spans="1:10">
+      <c r="A44" s="13">
+        <v>130</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="15">
+        <v>44302</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="28"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:10">
+      <c r="A45" s="1">
         <v>206</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B45" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="1">
-        <v>225</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="1">
-        <v>2</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="G45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="27"/>
       <c r="J45" s="27"/>
     </row>
-    <row r="46" s="4" customFormat="1" spans="1:10">
+    <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>13</v>
@@ -3189,27 +3166,26 @@
       <c r="G46" s="1">
         <v>2</v>
       </c>
-      <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J46" s="27"/>
     </row>
     <row r="47" s="4" customFormat="1" spans="1:10">
       <c r="A47" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>13</v>
@@ -3219,25 +3195,25 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J47" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="J47" s="27"/>
     </row>
     <row r="48" s="4" customFormat="1" spans="1:10">
       <c r="A48" s="1">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>13</v>
@@ -3251,107 +3227,107 @@
       </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="5">
+    <row r="49" s="4" customFormat="1" spans="1:10">
+      <c r="A49" s="1">
+        <v>232</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="5">
         <v>235</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B50" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="5" t="s">
+      <c r="F50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5" t="s">
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J49" s="23" t="s">
+      <c r="J50" s="23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" s="5" customFormat="1" spans="1:10">
-      <c r="A50" s="7">
+    <row r="51" s="5" customFormat="1" spans="1:10">
+      <c r="A51" s="7">
         <v>240</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B51" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D51" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E51" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7" t="s">
+      <c r="F51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J50" s="35"/>
-    </row>
-    <row r="51" s="5" customFormat="1" spans="1:10">
-      <c r="A51" s="1">
-        <v>303</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J51" s="36"/>
+      <c r="J51" s="35"/>
     </row>
     <row r="52" s="5" customFormat="1" spans="1:10">
       <c r="A52" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>13</v>
@@ -3361,25 +3337,25 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J52" s="36"/>
     </row>
     <row r="53" s="5" customFormat="1" spans="1:10">
       <c r="A53" s="1">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>13</v>
@@ -3389,184 +3365,184 @@
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J53" s="36"/>
+    </row>
+    <row r="54" s="5" customFormat="1" spans="1:10">
+      <c r="A54" s="1">
+        <v>338</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J53" s="36"/>
-    </row>
-    <row r="54" s="5" customFormat="1" spans="1:10">
-      <c r="A54" s="5">
+      <c r="J54" s="36"/>
+    </row>
+    <row r="55" s="5" customFormat="1" spans="1:10">
+      <c r="A55" s="5">
         <v>405</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B55" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="F55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="J54" s="23" t="s">
+      <c r="J55" s="23" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="55" s="5" customFormat="1" spans="1:10">
-      <c r="A55" s="1">
+    <row r="56" s="5" customFormat="1" spans="1:10">
+      <c r="A56" s="1">
         <v>474</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="1:10">
-      <c r="A56" s="1">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" s="6" customFormat="1" spans="1:10">
+      <c r="A57" s="1">
         <v>543</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="F57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1" t="s">
+      <c r="H57" s="1"/>
+      <c r="I57" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J56" s="36"/>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="1:10">
-      <c r="A57" s="5">
+      <c r="J57" s="36"/>
+    </row>
+    <row r="58" s="6" customFormat="1" spans="1:10">
+      <c r="A58" s="5">
         <v>617</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B58" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="5" t="s">
+      <c r="F58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5" t="s">
+      <c r="H58" s="5"/>
+      <c r="I58" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="J57" s="23" t="s">
+      <c r="J58" s="23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="58" s="6" customFormat="1" spans="1:10">
-      <c r="A58" s="1">
-        <v>654</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J58" s="1"/>
     </row>
     <row r="59" s="6" customFormat="1" spans="1:10">
       <c r="A59" s="1">
-        <v>824</v>
+        <v>654</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
+      <c r="G59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J59" s="36"/>
+        <v>195</v>
+      </c>
+      <c r="J59" s="1"/>
     </row>
     <row r="60" s="6" customFormat="1" spans="1:10">
       <c r="A60" s="1">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>13</v>
@@ -3576,25 +3552,25 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J60" s="27"/>
-    </row>
-    <row r="61" s="7" customFormat="1" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="J60" s="36"/>
+    </row>
+    <row r="61" s="6" customFormat="1" spans="1:10">
       <c r="A61" s="1">
-        <v>867</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>202</v>
+        <v>832</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>13</v>
@@ -3604,19 +3580,19 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J61" s="1"/>
+        <v>201</v>
+      </c>
+      <c r="J61" s="27"/>
     </row>
     <row r="62" s="7" customFormat="1" spans="1:10">
       <c r="A62" s="1">
-        <v>868</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>206</v>
+        <v>867</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>23</v>
@@ -3632,55 +3608,53 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J62" s="36"/>
-    </row>
-    <row r="63" s="8" customFormat="1" spans="1:10">
+        <v>205</v>
+      </c>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" s="7" customFormat="1" spans="1:10">
       <c r="A63" s="1">
-        <v>997</v>
+        <v>868</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>42</v>
+      <c r="G63" s="1">
+        <v>1</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>213</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="J63" s="36"/>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:10">
       <c r="A64" s="1">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>13</v>
@@ -3690,7 +3664,7 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>213</v>
@@ -3698,19 +3672,19 @@
     </row>
     <row r="65" s="8" customFormat="1" spans="1:10">
       <c r="A65" s="1">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
@@ -3720,143 +3694,145 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J65" s="27"/>
+        <v>195</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:10">
       <c r="A66" s="1">
-        <v>1047</v>
+        <v>999</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1">
-        <v>2</v>
+      <c r="G66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="J66" s="27"/>
     </row>
     <row r="67" s="8" customFormat="1" spans="1:10">
       <c r="A67" s="1">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J67" s="36"/>
+        <v>220</v>
+      </c>
+      <c r="J67" s="27"/>
     </row>
     <row r="68" s="8" customFormat="1" spans="1:10">
       <c r="A68" s="1">
-        <v>1603</v>
+        <v>1052</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>42</v>
+      <c r="G68" s="1">
+        <v>1</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J68" s="36"/>
+    </row>
+    <row r="69" s="8" customFormat="1" spans="1:10">
+      <c r="A69" s="1">
+        <v>1603</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J68" s="36"/>
-    </row>
-    <row r="69" s="8" customFormat="1" spans="1:10">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-    </row>
-    <row r="75" s="8" customFormat="1" spans="1:10">
-      <c r="A75" s="1">
-        <v>289</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="J75" s="36"/>
+      <c r="J69" s="36"/>
+    </row>
+    <row r="70" s="8" customFormat="1" spans="1:10">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:10">
       <c r="A76" s="1">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>11</v>
@@ -3872,25 +3848,25 @@
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J76" s="36"/>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:10">
       <c r="A77" s="1">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>235</v>
+        <v>231</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>236</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
@@ -3900,19 +3876,19 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J77" s="36"/>
     </row>
     <row r="78" s="8" customFormat="1" spans="1:10">
       <c r="A78" s="1">
-        <v>648</v>
+        <v>208</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>239</v>
+        <v>234</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>235</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>11</v>
@@ -3928,22 +3904,22 @@
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J78" s="36"/>
     </row>
     <row r="79" s="8" customFormat="1" spans="1:10">
       <c r="A79" s="1">
-        <v>720</v>
+        <v>648</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>239</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>236</v>
@@ -3956,25 +3932,25 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J79" s="36"/>
     </row>
     <row r="80" s="8" customFormat="1" spans="1:10">
       <c r="A80" s="1">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>46</v>
+        <v>236</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>13</v>
@@ -3984,87 +3960,115 @@
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="J80" s="36"/>
+    </row>
+    <row r="81" s="8" customFormat="1" spans="1:10">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J80" s="36"/>
+      <c r="J81" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J69">
-    <sortState ref="A1:J69">
+  <autoFilter ref="A1:J70">
+    <sortState ref="A1:J70">
       <sortCondition ref="B1" sortBy="cellColor" dxfId="0"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B67" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
-    <hyperlink ref="B60" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
-    <hyperlink ref="B59" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
-    <hyperlink ref="C56" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
-    <hyperlink ref="C61" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
-    <hyperlink ref="B62" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
-    <hyperlink ref="B51" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
-    <hyperlink ref="B52" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
-    <hyperlink ref="B26" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
-    <hyperlink ref="B27" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="C27" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
-    <hyperlink ref="B28" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
-    <hyperlink ref="B53" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
+    <hyperlink ref="B68" r:id="rId1" display="爱生气的书店老板" tooltip="https://leetcode-cn.com/problems/grumpy-bookstore-owner/"/>
+    <hyperlink ref="B61" r:id="rId2" display="翻转图像" tooltip="https://leetcode-cn.com/problems/flipping-an-image/"/>
+    <hyperlink ref="B60" r:id="rId3" display="山羊拉丁文" tooltip="https://leetcode-cn.com/problems/goat-latin/"/>
+    <hyperlink ref="C57" r:id="rId4" display="https://leetcode-cn.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="C62" r:id="rId5" display="https://leetcode-cn.com/problems/transpose-matrix/"/>
+    <hyperlink ref="B63" r:id="rId6" display="二进制间距" tooltip="https://leetcode-cn.com/problems/binary-gap/"/>
+    <hyperlink ref="B52" r:id="rId7" display="区域和检索 - 数组不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-immutable/"/>
+    <hyperlink ref="B53" r:id="rId8" display="二维区域和检索 - 矩阵不可变" tooltip="https://leetcode-cn.com/problems/range-sum-query-2d-immutable/"/>
+    <hyperlink ref="B27" r:id="rId9" display="二叉树的层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="B28" r:id="rId10" display="二叉树的锯齿形层序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="C28" r:id="rId10" display="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/" tooltip="https://leetcode-cn.com/problems/binary-tree-zigzag-level-order-traversal/"/>
+    <hyperlink ref="B29" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="B54" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B12" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B48" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
-    <hyperlink ref="B31" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
-    <hyperlink ref="B30" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
-    <hyperlink ref="B66" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
+    <hyperlink ref="B49" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B32" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
+    <hyperlink ref="B31" r:id="rId16" display="验证回文串" tooltip="https://leetcode-cn.com/problems/valid-palindrome/"/>
+    <hyperlink ref="B67" r:id="rId17" display="删除字符串中的所有相邻重复项" tooltip="https://leetcode-cn.com/problems/remove-all-adjacent-duplicates-in-string/"/>
     <hyperlink ref="B6" r:id="rId18" display="旋转链表" tooltip="https://leetcode-cn.com/problems/rotate-list/"/>
-    <hyperlink ref="B47" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
-    <hyperlink ref="B46" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
-    <hyperlink ref="B45" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
+    <hyperlink ref="B48" r:id="rId19" display="基本计算器 II" tooltip="https://leetcode-cn.com/problems/basic-calculator-ii/"/>
+    <hyperlink ref="B47" r:id="rId20" display="翻转二叉树" tooltip="https://leetcode-cn.com/problems/invert-binary-tree/"/>
+    <hyperlink ref="B46" r:id="rId21" display="用队列实现栈" tooltip="https://leetcode-cn.com/problems/implement-stack-using-queues/"/>
     <hyperlink ref="B18" r:id="rId22" display="螺旋矩阵" tooltip="https://leetcode-cn.com/problems/spiral-matrix/"/>
     <hyperlink ref="B15" r:id="rId23" display="全排列" tooltip="https://leetcode-cn.com/problems/permutations/"/>
     <hyperlink ref="B16" r:id="rId24" display="全排列 II" tooltip="https://leetcode-cn.com/problems/permutations-ii/"/>
-    <hyperlink ref="B13" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
+    <hyperlink ref="B23" r:id="rId25" display="移除元素" tooltip="https://leetcode-cn.com/problems/remove-element/"/>
     <hyperlink ref="B10" r:id="rId26" display="两数相加" tooltip="https://leetcode-cn.com/problems/add-two-numbers/"/>
     <hyperlink ref="B19" r:id="rId27" display="螺旋矩阵 II" tooltip="https://leetcode-cn.com/problems/spiral-matrix-ii/"/>
     <hyperlink ref="B17" r:id="rId28" display="连续子数组最大和" tooltip="https://leetcode-cn.com/problems/maximum-subarray/"/>
-    <hyperlink ref="B29" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
-    <hyperlink ref="B44" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
-    <hyperlink ref="B33" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
-    <hyperlink ref="B68" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
-    <hyperlink ref="B65" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
-    <hyperlink ref="B58" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
-    <hyperlink ref="B64" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
-    <hyperlink ref="B36" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
-    <hyperlink ref="B76" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
-    <hyperlink ref="B34" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
+    <hyperlink ref="B30" r:id="rId29" display="买卖股票的最佳时机" tooltip="https://leetcode-cn.com/problems/best-time-to-buy-and-sell-stock/"/>
+    <hyperlink ref="B45" r:id="rId30" display="反转链表" tooltip="https://leetcode-cn.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="B34" r:id="rId31" display="二叉树的前序遍历" tooltip="https://leetcode-cn.com/problems/binary-tree-preorder-traversal/"/>
+    <hyperlink ref="B69" r:id="rId32" display="设计停车系统" tooltip="https://leetcode-cn.com/problems/design-parking-system/"/>
+    <hyperlink ref="B66" r:id="rId33" display="可以被一步捕获的棋子数" tooltip="https://leetcode-cn.com/problems/available-captures-for-rook/"/>
+    <hyperlink ref="B59" r:id="rId34" display="最大二叉树" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree/"/>
+    <hyperlink ref="B65" r:id="rId35" display="最大二叉树 II" tooltip="https://leetcode-cn.com/problems/maximum-binary-tree-ii/"/>
+    <hyperlink ref="B37" r:id="rId36" display="位1的个数" tooltip="https://leetcode-cn.com/problems/number-of-1-bits/"/>
+    <hyperlink ref="B77" r:id="rId37" display="矩阵置零" tooltip="https://leetcode-cn.com/problems/set-matrix-zeroes/"/>
+    <hyperlink ref="B35" r:id="rId38" display="逆波兰表达式求值" tooltip="https://leetcode-cn.com/problems/evaluate-reverse-polish-notation/"/>
     <hyperlink ref="B3" r:id="rId39" display="整数转罗马数字" tooltip="https://leetcode-cn.com/problems/integer-to-roman/"/>
-    <hyperlink ref="B54" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
-    <hyperlink ref="B49" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
-    <hyperlink ref="B57" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
+    <hyperlink ref="B55" r:id="rId40" display="数字转换为十六进制数" tooltip="https://leetcode-cn.com/problems/convert-a-number-to-hexadecimal/"/>
+    <hyperlink ref="B50" r:id="rId41" display="二叉搜索树的最近公共祖先" tooltip="https://leetcode-cn.com/problems/lowest-common-ancestor-of-a-binary-search-tree/"/>
+    <hyperlink ref="B58" r:id="rId42" display="合并二叉树" tooltip="https://leetcode-cn.com/problems/merge-two-binary-trees/"/>
     <hyperlink ref="B11" r:id="rId43" display="电话号码的字母组合" tooltip="https://leetcode-cn.com/problems/letter-combinations-of-a-phone-number/"/>
-    <hyperlink ref="B25" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
-    <hyperlink ref="B24" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
-    <hyperlink ref="B35" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
-    <hyperlink ref="B37" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
-    <hyperlink ref="B38" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
-    <hyperlink ref="B39" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
+    <hyperlink ref="B26" r:id="rId44" display="删除排序链表中的重复元素" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list/"/>
+    <hyperlink ref="B25" r:id="rId45" display="删除排序链表中的重复元素 II" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-list-ii/"/>
+    <hyperlink ref="B36" r:id="rId46" display="颠倒二进制位" tooltip="https://leetcode-cn.com/problems/reverse-bits/"/>
+    <hyperlink ref="B38" r:id="rId47" display="打家劫舍" tooltip="https://leetcode-cn.com/problems/house-robber/"/>
+    <hyperlink ref="B39" r:id="rId48" display="二叉树的右视图" tooltip="https://leetcode-cn.com/problems/binary-tree-right-side-view/"/>
+    <hyperlink ref="B40" r:id="rId49" display="岛屿数量" tooltip="https://leetcode-cn.com/problems/number-of-islands/"/>
     <hyperlink ref="B14" r:id="rId50" display="搜索插入位置" tooltip="https://leetcode-cn.com/problems/search-insert-position/"/>
-    <hyperlink ref="B23" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
-    <hyperlink ref="B50" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="B24" r:id="rId51" display="搜索二维矩阵" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix/"/>
+    <hyperlink ref="B51" r:id="rId52" display="搜索二维矩阵 II" tooltip="https://leetcode-cn.com/problems/search-a-2d-matrix-ii/"/>
     <hyperlink ref="B7" r:id="rId53" display="寻找旋转排序数组中的最小值" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array/"/>
     <hyperlink ref="B8" r:id="rId54" display="寻找旋转排序数组中的最小值 II" tooltip="https://leetcode-cn.com/problems/find-minimum-in-rotated-sorted-array-ii/"/>
     <hyperlink ref="B9" r:id="rId55" display="链表中倒数第k个节点" tooltip="https://leetcode-cn.com/problems/lian-biao-zhong-dao-shu-di-kge-jie-dian-lcof/"/>
     <hyperlink ref="B2" r:id="rId56" display="盛最多水的容器" tooltip="https://leetcode-cn.com/problems/container-with-most-water/"/>
     <hyperlink ref="B4" r:id="rId57" display="罗马数字转整数" tooltip="https://leetcode-cn.com/problems/roman-to-integer/"/>
-    <hyperlink ref="B75" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
-    <hyperlink ref="B77" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B78" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C78" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
-    <hyperlink ref="C77" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
-    <hyperlink ref="B79" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
-    <hyperlink ref="B80" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
-    <hyperlink ref="B40" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
-    <hyperlink ref="B41" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
-    <hyperlink ref="B42" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
-    <hyperlink ref="B43" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
+    <hyperlink ref="B76" r:id="rId58" display="生命游戏" tooltip="https://leetcode-cn.com/problems/game-of-life/"/>
+    <hyperlink ref="B78" r:id="rId59" display="实现 Trie (前缀树)" tooltip="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B79" r:id="rId60" display="单词替换" tooltip="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C79" r:id="rId60" display="https://leetcode-cn.com/problems/replace-words/"/>
+    <hyperlink ref="C78" r:id="rId59" display="https://leetcode-cn.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="B80" r:id="rId61" display="词典中最长的单词" tooltip="https://leetcode-cn.com/problems/longest-word-in-dictionary/"/>
+    <hyperlink ref="B81" r:id="rId62" display="单词搜索" tooltip="https://leetcode-cn.com/problems/word-search/"/>
+    <hyperlink ref="B41" r:id="rId63" display="岛屿的周长" tooltip="https://leetcode-cn.com/problems/island-perimeter/"/>
+    <hyperlink ref="B42" r:id="rId64" display="岛屿的最大面积" tooltip="https://leetcode-cn.com/problems/max-area-of-island/"/>
+    <hyperlink ref="B43" r:id="rId65" display="最大人工岛" tooltip="https://leetcode-cn.com/problems/making-a-large-island/"/>
+    <hyperlink ref="B44" r:id="rId66" display="被围绕的区域" tooltip="https://leetcode-cn.com/problems/surrounded-regions/"/>
     <hyperlink ref="B20" r:id="rId67" display="不同路径" tooltip="https://leetcode-cn.com/problems/unique-paths/"/>
     <hyperlink ref="B22" r:id="rId68" display="将字符串翻转到单调递增" tooltip="https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/"/>
   </hyperlinks>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="255">
   <si>
     <t>编号</t>
   </si>
@@ -770,6 +770,18 @@
   </si>
   <si>
     <t>https://leetcode-cn.com/problems/word-search/</t>
+  </si>
+  <si>
+    <t>链表中的下一个更大节点</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/next-greater-node-in-linked-list/</t>
+  </si>
+  <si>
+    <t>单调栈</t>
+  </si>
+  <si>
+    <t>①单调栈（一） ①单调栈（二）</t>
   </si>
 </sst>
 </file>
@@ -1939,7 +1951,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -4103,6 +4115,36 @@
         <v>66</v>
       </c>
       <c r="J82" s="39"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:10">
+      <c r="A86" s="9">
+        <v>1019</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" s="11">
+        <v>44306</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J86" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J71">
@@ -4185,6 +4227,7 @@
     <hyperlink ref="B11" r:id="rId68" display="将字符串翻转到单调递增" tooltip="https://leetcode-cn.com/problems/flip-string-to-monotone-increasing/"/>
     <hyperlink ref="B3" r:id="rId69" display="实现 strStr()" tooltip="https://leetcode-cn.com/problems/implement-strstr/"/>
     <hyperlink ref="B73" r:id="rId70" display="两整数之和" tooltip="https://leetcode-cn.com/problems/sum-of-two-integers/"/>
+    <hyperlink ref="B86" r:id="rId71" display="链表中的下一个更大节点" tooltip="https://leetcode-cn.com/problems/next-greater-node-in-linked-list/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="258">
   <si>
     <t>编号</t>
   </si>
@@ -782,6 +782,15 @@
   </si>
   <si>
     <t>①单调栈（一） ①单调栈（二）</t>
+  </si>
+  <si>
+    <t>每日温度</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/daily-temperatures/</t>
+  </si>
+  <si>
+    <t>①单调栈</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
@@ -4145,6 +4154,36 @@
         <v>254</v>
       </c>
       <c r="J86" s="27"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:10">
+      <c r="A87" s="9">
+        <v>739</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="11">
+        <v>44306</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="J87" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J71">
@@ -4228,6 +4267,7 @@
     <hyperlink ref="B3" r:id="rId69" display="实现 strStr()" tooltip="https://leetcode-cn.com/problems/implement-strstr/"/>
     <hyperlink ref="B73" r:id="rId70" display="两整数之和" tooltip="https://leetcode-cn.com/problems/sum-of-two-integers/"/>
     <hyperlink ref="B86" r:id="rId71" display="链表中的下一个更大节点" tooltip="https://leetcode-cn.com/problems/next-greater-node-in-linked-list/"/>
+    <hyperlink ref="B87" r:id="rId72" display="每日温度" tooltip="https://leetcode-cn.com/problems/daily-temperatures/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/刷题清单.xlsx
+++ b/notes/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="264">
   <si>
     <t>编号</t>
   </si>
@@ -791,6 +791,24 @@
   </si>
   <si>
     <t>①单调栈</t>
+  </si>
+  <si>
+    <t>整数拆分</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/integer-break/</t>
+  </si>
+  <si>
+    <t>动态规划、数学</t>
+  </si>
+  <si>
+    <t>①动态规划 ②降维动态规划 ③记忆化递归 ④数学</t>
+  </si>
+  <si>
+    <t>反转字符串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/reverse-string/</t>
   </si>
 </sst>
 </file>
@@ -798,8 +816,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
@@ -854,15 +872,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -878,6 +895,44 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -906,16 +961,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -929,31 +977,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -961,20 +986,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1025,31 +1043,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1061,19 +1073,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,7 +1097,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1109,31 +1163,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1145,61 +1193,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1228,17 +1234,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1248,15 +1248,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1276,13 +1267,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1302,26 +1297,37 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1333,10 +1339,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment v